--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44977</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44740</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>44992</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45565</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>46050</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44872</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>45387</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         <v>45827</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>44599</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>44578</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>44984</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45103</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45580</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45001</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>44729</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45646</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45322</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45406</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>44489</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>45182</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45546</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>46086</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>45461</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>45341</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>44992</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>46213</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4946,7 +4946,7 @@
         <v>45387</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45330</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45467</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>45153</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45555</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45890</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>46056</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>44888</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>44557</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44732</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>44841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>44875</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6044,7 +6044,7 @@
         <v>44620</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>44620</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>44813</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6273,7 +6273,7 @@
         <v>44508</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>44875</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>44460</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         <v>44539</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6565,7 +6565,7 @@
         <v>44755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>44713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6711,7 +6711,7 @@
         <v>44489</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6784,7 +6784,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>44813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7003,7 +7003,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7076,7 +7076,7 @@
         <v>44533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7149,7 +7149,7 @@
         <v>44575</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>44819</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         <v>44461</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>44570</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7514,7 +7514,7 @@
         <v>44641</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7587,7 +7587,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>44690</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7733,7 +7733,7 @@
         <v>44470</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>44610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>44865</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>44791</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8025,7 +8025,7 @@
         <v>44644</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44603</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44627</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44804</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44467</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44508</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44722</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44511</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44460</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44839</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44879</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>44791</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44875</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>44532</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44879</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>44595</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44494</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>44466</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>44489</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44529</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>44631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44798</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44648</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44608</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>44620</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44620</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44481</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44636</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>44519</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44791</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>44748</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>44888</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>44820</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>44463</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44474</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>44494</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>44509</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44533</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>44522</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>44722</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44468</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>44698</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>44631</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44523</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44680</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>44749</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>44711</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11763,7 +11763,7 @@
         <v>44753</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11836,7 +11836,7 @@
         <v>44540</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11909,7 +11909,7 @@
         <v>44676</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11982,7 +11982,7 @@
         <v>44620</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12055,7 +12055,7 @@
         <v>44540</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44875</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>44698</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44685</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12347,7 +12347,7 @@
         <v>44641</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12420,7 +12420,7 @@
         <v>44539</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>44631</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>44523</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>44753</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>44712</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>44596</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>45075</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>45274</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>45775</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13082,7 +13082,7 @@
         <v>45477</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>44967</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>44586</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45395</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13379,7 +13379,7 @@
         <v>45377</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13452,7 +13452,7 @@
         <v>44728</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>44676</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13598,7 +13598,7 @@
         <v>45147</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13671,7 +13671,7 @@
         <v>45615</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44965</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44895</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13890,7 +13890,7 @@
         <v>45362</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>45082</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>45107</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>44631</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45631</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>45617</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>45110</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>45399</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45310</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45635</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45086</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45574</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45089</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45091</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44991</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44939</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45034</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45637</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>45117</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15287,7 +15287,7 @@
         <v>45117</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15360,7 +15360,7 @@
         <v>44971</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>45188</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45033</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45303</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44545</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>44967</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>45701</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45107</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>45019</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>44904</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45306</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>44473</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>45344</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>45359</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>45553</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>45155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16528,7 +16528,7 @@
         <v>45608</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45466</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>44540</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16747,7 +16747,7 @@
         <v>45272</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16820,7 +16820,7 @@
         <v>44928</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16893,7 +16893,7 @@
         <v>45155</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16966,7 +16966,7 @@
         <v>45155</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44529</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>44570</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17185,7 +17185,7 @@
         <v>45447</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17258,7 +17258,7 @@
         <v>45247</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17331,7 +17331,7 @@
         <v>44930</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17404,7 +17404,7 @@
         <v>44558</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>45164</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45164</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>44509</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45107</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44928</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>44490</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17920,7 +17920,7 @@
         <v>45071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45246</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45167</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>44481</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44804</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>44804</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45244</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>44683</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>44522</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>44749</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>45033</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45701</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>45244</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45580</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45610</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>45279</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45362</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45461</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19239,7 +19239,7 @@
         <v>45014</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>44818</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19385,7 +19385,7 @@
         <v>44900</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45366</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>44971</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45455</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>45323</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>45475</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>45181</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>45710</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>44950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>44937</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>45574</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>44617</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>45173</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>45274</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45029</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45702</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>44753</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45394</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45327</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>44483</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45085</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>45176</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45394</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>44883</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>44984</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45194</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45152</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21361,7 +21361,7 @@
         <v>45097</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>44938</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45034</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>44951</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21653,7 +21653,7 @@
         <v>45036</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21726,7 +21726,7 @@
         <v>44881</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21799,7 +21799,7 @@
         <v>44545</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21872,7 +21872,7 @@
         <v>45203</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21945,7 +21945,7 @@
         <v>44691</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45154</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>44993</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>45107</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22237,7 +22237,7 @@
         <v>44481</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>44945</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>44949</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22529,7 +22529,7 @@
         <v>45709</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45349</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45170</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>45238</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45036</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45103</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>45247</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45887</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>46031</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45722</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45897</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45183</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45183</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45240</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45250</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45890</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45903</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45553</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45474</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24004,7 +24004,7 @@
         <v>45897</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>45742</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24150,7 +24150,7 @@
         <v>44964</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24223,7 +24223,7 @@
         <v>45260</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24296,7 +24296,7 @@
         <v>45834</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45908</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45933</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45755</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45671</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>44631</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44936</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>44936</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>44728</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45727</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>46035</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>44489</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44852</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45467</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45467</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45467</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45267</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45884</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45329</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25688,7 +25688,7 @@
         <v>45082</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25761,7 +25761,7 @@
         <v>45082</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25834,7 +25834,7 @@
         <v>45981</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25907,7 +25907,7 @@
         <v>45803</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -25980,7 +25980,7 @@
         <v>45896</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26053,7 +26053,7 @@
         <v>46136</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>45180</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>44634</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26272,7 +26272,7 @@
         <v>45299</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>45035</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>44462</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45443</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>45646</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45992</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>46010</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>46010</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26856,7 +26856,7 @@
         <v>46136</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26929,7 +26929,7 @@
         <v>45904</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45553</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45924</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45711</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         <v>45905</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27299,7 +27299,7 @@
         <v>45445</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27372,7 +27372,7 @@
         <v>45792</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27445,7 +27445,7 @@
         <v>45789</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27518,7 +27518,7 @@
         <v>45908</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27591,7 +27591,7 @@
         <v>44459</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27664,7 +27664,7 @@
         <v>45342</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>44991</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         <v>45278</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27883,7 +27883,7 @@
         <v>44904</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -27956,7 +27956,7 @@
         <v>45062</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28029,7 +28029,7 @@
         <v>44964</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         <v>45758</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>45904</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28253,7 +28253,7 @@
         <v>45012</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45162</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45412</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28472,7 +28472,7 @@
         <v>44909</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28545,7 +28545,7 @@
         <v>44928</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28618,7 +28618,7 @@
         <v>45211</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>44965</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>45923</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>44790</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>45923</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45548</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45264</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>44888</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45093</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>44895</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45107</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>45069</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29499,7 +29499,7 @@
         <v>45574</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29572,7 +29572,7 @@
         <v>44935</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29645,7 +29645,7 @@
         <v>45631</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29718,7 +29718,7 @@
         <v>45933</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45002</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45408</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45229</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>45191</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>45547</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>44518</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45264</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30302,7 +30302,7 @@
         <v>45264</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30375,7 +30375,7 @@
         <v>45938</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30448,7 +30448,7 @@
         <v>45106</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>46148</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>45618</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45407</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>45539</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>44967</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>44967</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>46148</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>46149</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31110,7 +31110,7 @@
         <v>45950</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31183,7 +31183,7 @@
         <v>44930</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31256,7 +31256,7 @@
         <v>45097</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45331</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31402,7 +31402,7 @@
         <v>44950</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31475,7 +31475,7 @@
         <v>45953</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31548,7 +31548,7 @@
         <v>44599</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31621,7 +31621,7 @@
         <v>45439</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44988</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31767,7 +31767,7 @@
         <v>45688</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>45432</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31913,7 +31913,7 @@
         <v>45727</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -31986,7 +31986,7 @@
         <v>45412</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32059,7 +32059,7 @@
         <v>45771</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32132,7 +32132,7 @@
         <v>44756</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         <v>44953</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>44599</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>45002</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45964</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>45700</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32570,7 +32570,7 @@
         <v>45533</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>44993</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45735</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>45735</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32862,7 +32862,7 @@
         <v>45568</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32935,7 +32935,7 @@
         <v>45325</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33008,7 +33008,7 @@
         <v>44930</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33081,7 +33081,7 @@
         <v>45434</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33154,7 +33154,7 @@
         <v>45117</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33227,7 +33227,7 @@
         <v>45117</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33300,7 +33300,7 @@
         <v>45395</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33373,7 +33373,7 @@
         <v>45972</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45173</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45090</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45082</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>45201</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45552</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>44657</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33884,7 +33884,7 @@
         <v>45629</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -33957,7 +33957,7 @@
         <v>45062</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34030,7 +34030,7 @@
         <v>45077</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45978</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>44769</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>45979</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>46043</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45600</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34473,7 +34473,7 @@
         <v>45331</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34546,7 +34546,7 @@
         <v>45980</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34619,7 +34619,7 @@
         <v>44916</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45002</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45002</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45902</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>46154</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>45982</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35057,7 +35057,7 @@
         <v>45462</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35130,7 +35130,7 @@
         <v>45439</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35203,7 +35203,7 @@
         <v>44470</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35276,7 +35276,7 @@
         <v>44995</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35349,7 +35349,7 @@
         <v>45117</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35422,7 +35422,7 @@
         <v>45129</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35495,7 +35495,7 @@
         <v>45547</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35568,7 +35568,7 @@
         <v>46160</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35641,7 +35641,7 @@
         <v>45121</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45574</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>44930</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35860,7 +35860,7 @@
         <v>45635</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -35938,7 +35938,7 @@
         <v>44930</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36011,7 +36011,7 @@
         <v>45005</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36084,7 +36084,7 @@
         <v>45005</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36157,7 +36157,7 @@
         <v>45574</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36230,7 +36230,7 @@
         <v>45330</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>46162</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>44550</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36449,7 +36449,7 @@
         <v>46162</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36522,7 +36522,7 @@
         <v>45261</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>44495</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45993</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36741,7 +36741,7 @@
         <v>45429</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>44545</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36887,7 +36887,7 @@
         <v>45691</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>45469</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37038,7 +37038,7 @@
         <v>45106</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37111,7 +37111,7 @@
         <v>45261</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37184,7 +37184,7 @@
         <v>46167</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>44705</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>46000</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37403,7 +37403,7 @@
         <v>46000</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37476,7 +37476,7 @@
         <v>46000</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37549,7 +37549,7 @@
         <v>45609</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37622,7 +37622,7 @@
         <v>46167</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37695,7 +37695,7 @@
         <v>44831</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37768,7 +37768,7 @@
         <v>44831</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37841,7 +37841,7 @@
         <v>44960</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45356</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -37992,7 +37992,7 @@
         <v>46167</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>46167</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38138,7 +38138,7 @@
         <v>46007</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38216,7 +38216,7 @@
         <v>45197</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45726</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38362,7 +38362,7 @@
         <v>45007</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45408</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>44627</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38581,7 +38581,7 @@
         <v>45601</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38654,7 +38654,7 @@
         <v>46168</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45546</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38800,7 +38800,7 @@
         <v>45307</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>46168</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -38951,7 +38951,7 @@
         <v>46168</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39024,7 +39024,7 @@
         <v>45540</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39097,7 +39097,7 @@
         <v>45540</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>44463</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39243,7 +39243,7 @@
         <v>45300</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39316,7 +39316,7 @@
         <v>44939</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39389,7 +39389,7 @@
         <v>44895</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>44916</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39535,7 +39535,7 @@
         <v>44655</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39608,7 +39608,7 @@
         <v>46031</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>44936</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39754,7 +39754,7 @@
         <v>44936</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39827,7 +39827,7 @@
         <v>45160</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39900,7 +39900,7 @@
         <v>46031</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -39973,7 +39973,7 @@
         <v>45401</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40046,7 +40046,7 @@
         <v>44748</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40119,7 +40119,7 @@
         <v>45139</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>46171</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>44820</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45078</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>45078</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>46036</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40567,7 +40567,7 @@
         <v>45106</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40640,7 +40640,7 @@
         <v>45215</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>45109</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>44673</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40859,7 +40859,7 @@
         <v>46038</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40932,7 +40932,7 @@
         <v>46038</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41005,7 +41005,7 @@
         <v>46038</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41078,7 +41078,7 @@
         <v>44945</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41151,7 +41151,7 @@
         <v>44728</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41224,7 +41224,7 @@
         <v>45007</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41297,7 +41297,7 @@
         <v>45629</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41370,7 +41370,7 @@
         <v>44907</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>45684</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41516,7 +41516,7 @@
         <v>46044</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41594,7 +41594,7 @@
         <v>46044</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>46175</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46048</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46175</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>46176</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45063</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45644</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45302</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>44820</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>45215</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>45245</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>44963</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45155</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>46177</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45085</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>46063</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>46063</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>45439</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42913,7 +42913,7 @@
         <v>46063</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>46182</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>45034</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>45394</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43205,7 +43205,7 @@
         <v>46182</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43278,7 +43278,7 @@
         <v>46182</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43351,7 +43351,7 @@
         <v>44624</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43424,7 +43424,7 @@
         <v>44928</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43497,7 +43497,7 @@
         <v>45267</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43570,7 +43570,7 @@
         <v>45264</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45314</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>46175</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43789,7 +43789,7 @@
         <v>46181</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43862,7 +43862,7 @@
         <v>46147</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43935,7 +43935,7 @@
         <v>44875</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44008,7 +44008,7 @@
         <v>44505</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44081,7 +44081,7 @@
         <v>46078</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44154,7 +44154,7 @@
         <v>45614</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44227,7 +44227,7 @@
         <v>44620</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44305,7 +44305,7 @@
         <v>45261</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44378,7 +44378,7 @@
         <v>46184</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44451,7 +44451,7 @@
         <v>46135</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>46146</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44597,7 +44597,7 @@
         <v>45384</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44670,7 +44670,7 @@
         <v>46184</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44743,7 +44743,7 @@
         <v>46184</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44816,7 +44816,7 @@
         <v>45436</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44889,7 +44889,7 @@
         <v>46083</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -44962,7 +44962,7 @@
         <v>45394</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45035,7 +45035,7 @@
         <v>46083</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>46083</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45181,7 +45181,7 @@
         <v>46083</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45254,7 +45254,7 @@
         <v>44911</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45327,7 +45327,7 @@
         <v>46086</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45400,7 +45400,7 @@
         <v>45113</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45473,7 +45473,7 @@
         <v>46188</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45546,7 +45546,7 @@
         <v>45099</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45619,7 +45619,7 @@
         <v>46090</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45155</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45765,7 +45765,7 @@
         <v>45547</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45838,7 +45838,7 @@
         <v>46190</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45911,7 +45911,7 @@
         <v>45579</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -45984,7 +45984,7 @@
         <v>45568</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>45772</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>44838</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>46086</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45674</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>45637</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46432,7 +46432,7 @@
         <v>45637</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>44700</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>46189</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46656,7 +46656,7 @@
         <v>46098</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>46100</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45424</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>45240</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>44524</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45226</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47094,7 +47094,7 @@
         <v>46104</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>46101</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>45314</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45009</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>46104</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45540</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>46101</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>46106</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46198</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>44949</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>46197</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45236</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>46108</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48058,7 +48058,7 @@
         <v>46108</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48131,7 +48131,7 @@
         <v>46108</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48204,7 +48204,7 @@
         <v>45614</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48277,7 +48277,7 @@
         <v>46108</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48350,7 +48350,7 @@
         <v>46197</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48423,7 +48423,7 @@
         <v>45110</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48496,7 +48496,7 @@
         <v>44994</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48569,7 +48569,7 @@
         <v>46244</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>44621</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48715,7 +48715,7 @@
         <v>44903</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48788,7 +48788,7 @@
         <v>44489</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>46199</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -48934,7 +48934,7 @@
         <v>45201</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49007,7 +49007,7 @@
         <v>46113</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49080,7 +49080,7 @@
         <v>46120</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49153,7 +49153,7 @@
         <v>46120</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49226,7 +49226,7 @@
         <v>46119</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49299,7 +49299,7 @@
         <v>45436</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49372,7 +49372,7 @@
         <v>45386</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49445,7 +49445,7 @@
         <v>45439</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49518,7 +49518,7 @@
         <v>44628</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49591,7 +49591,7 @@
         <v>45418</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49669,7 +49669,7 @@
         <v>45426</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49742,7 +49742,7 @@
         <v>44614</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49815,7 +49815,7 @@
         <v>45119</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49888,7 +49888,7 @@
         <v>45152</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -49961,7 +49961,7 @@
         <v>46120</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50034,7 +50034,7 @@
         <v>45680</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50107,7 +50107,7 @@
         <v>45574</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50180,7 +50180,7 @@
         <v>45215</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50253,7 +50253,7 @@
         <v>45547</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50326,7 +50326,7 @@
         <v>46105</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50399,7 +50399,7 @@
         <v>44795</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>45449</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>45449</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50618,7 +50618,7 @@
         <v>45240</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50691,7 +50691,7 @@
         <v>45240</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50764,7 +50764,7 @@
         <v>45166</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>46133</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50910,7 +50910,7 @@
         <v>44984</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -50983,7 +50983,7 @@
         <v>46133</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51056,7 +51056,7 @@
         <v>45155</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>46132</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51202,7 +51202,7 @@
         <v>45112</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51275,7 +51275,7 @@
         <v>46132</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51348,7 +51348,7 @@
         <v>44960</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51421,7 +51421,7 @@
         <v>44620</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51494,7 +51494,7 @@
         <v>44867</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51567,7 +51567,7 @@
         <v>45188</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51640,7 +51640,7 @@
         <v>45370</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51713,7 +51713,7 @@
         <v>45411</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>45782</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>46134</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -51937,7 +51937,7 @@
         <v>45559</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52010,7 +52010,7 @@
         <v>46204</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52088,7 +52088,7 @@
         <v>46204</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>46204</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52244,7 +52244,7 @@
         <v>45902</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52317,7 +52317,7 @@
         <v>45992</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52390,7 +52390,7 @@
         <v>45596</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52463,7 +52463,7 @@
         <v>46204</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52536,7 +52536,7 @@
         <v>45821</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52609,7 +52609,7 @@
         <v>45329</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52687,7 +52687,7 @@
         <v>45873</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52760,7 +52760,7 @@
         <v>45406</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>45755</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>46003</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -52979,7 +52979,7 @@
         <v>45841</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53052,7 +53052,7 @@
         <v>45091</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53125,7 +53125,7 @@
         <v>45546</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53198,7 +53198,7 @@
         <v>45926</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53271,7 +53271,7 @@
         <v>45063</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53344,7 +53344,7 @@
         <v>45264</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53417,7 +53417,7 @@
         <v>45474</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53490,7 +53490,7 @@
         <v>46203</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53563,7 +53563,7 @@
         <v>44698</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53636,7 +53636,7 @@
         <v>46204</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53709,7 +53709,7 @@
         <v>44627</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
         <v>44602</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>45176</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53928,7 +53928,7 @@
         <v>44904</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54001,7 +54001,7 @@
         <v>45051</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54074,7 +54074,7 @@
         <v>46251</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54152,7 +54152,7 @@
         <v>46205</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54225,7 +54225,7 @@
         <v>46206</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>46206</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>44685</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54464,7 +54464,7 @@
         <v>44685</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54537,7 +54537,7 @@
         <v>46206</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54610,7 +54610,7 @@
         <v>45035</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54683,7 +54683,7 @@
         <v>44949</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54756,7 +54756,7 @@
         <v>45138</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54829,7 +54829,7 @@
         <v>44984</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54902,7 +54902,7 @@
         <v>45062</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -54975,7 +54975,7 @@
         <v>44712</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55048,7 +55048,7 @@
         <v>45176</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45252</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55194,7 +55194,7 @@
         <v>45252</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55267,7 +55267,7 @@
         <v>45331</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>45331</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55413,7 +55413,7 @@
         <v>45331</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55486,7 +55486,7 @@
         <v>45005</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55559,7 +55559,7 @@
         <v>46212</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55632,7 +55632,7 @@
         <v>45117</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55705,7 +55705,7 @@
         <v>44657</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55778,7 +55778,7 @@
         <v>45303</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55851,7 +55851,7 @@
         <v>44972</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>45109</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>44575</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56070,7 +56070,7 @@
         <v>45071</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56143,7 +56143,7 @@
         <v>45071</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56216,7 +56216,7 @@
         <v>45392</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56289,7 +56289,7 @@
         <v>45183</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56362,7 +56362,7 @@
         <v>44950</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56435,7 +56435,7 @@
         <v>46213</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56508,7 +56508,7 @@
         <v>44988</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56581,7 +56581,7 @@
         <v>45071</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56654,7 +56654,7 @@
         <v>45096</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56727,7 +56727,7 @@
         <v>46213</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56800,7 +56800,7 @@
         <v>44967</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56878,7 +56878,7 @@
         <v>46213</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>44901</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57024,7 +57024,7 @@
         <v>44901</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57097,7 +57097,7 @@
         <v>46189</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57170,7 +57170,7 @@
         <v>45386</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57243,7 +57243,7 @@
         <v>46260</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57316,7 +57316,7 @@
         <v>45082</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57389,7 +57389,7 @@
         <v>45182</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57462,7 +57462,7 @@
         <v>46260</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57535,7 +57535,7 @@
         <v>46260</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57608,7 +57608,7 @@
         <v>46045</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57686,7 +57686,7 @@
         <v>46202</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57759,7 +57759,7 @@
         <v>45674</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57832,7 +57832,7 @@
         <v>46262</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57905,7 +57905,7 @@
         <v>45601</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -57978,7 +57978,7 @@
         <v>44998</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58051,7 +58051,7 @@
         <v>45188</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58124,7 +58124,7 @@
         <v>45371</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58197,7 +58197,7 @@
         <v>46209</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58275,7 +58275,7 @@
         <v>46262</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58348,7 +58348,7 @@
         <v>45572</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58421,7 +58421,7 @@
         <v>46266</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58494,7 +58494,7 @@
         <v>45327</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58572,7 +58572,7 @@
         <v>44620</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58650,7 +58650,7 @@
         <v>45755</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58723,7 +58723,7 @@
         <v>45607</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45713</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58869,7 +58869,7 @@
         <v>45124</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58942,7 +58942,7 @@
         <v>45616</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59015,7 +59015,7 @@
         <v>45275</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59088,7 +59088,7 @@
         <v>45175</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59161,7 +59161,7 @@
         <v>45338</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59234,7 +59234,7 @@
         <v>44748</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59307,7 +59307,7 @@
         <v>45646</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59380,7 +59380,7 @@
         <v>46195</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59453,7 +59453,7 @@
         <v>46195</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59526,7 +59526,7 @@
         <v>46195</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59599,7 +59599,7 @@
         <v>45574</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59672,7 +59672,7 @@
         <v>45562</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59745,7 +59745,7 @@
         <v>45615</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59818,7 +59818,7 @@
         <v>45419</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59891,7 +59891,7 @@
         <v>45519</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59964,7 +59964,7 @@
         <v>45089</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60037,7 +60037,7 @@
         <v>46191</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60110,7 +60110,7 @@
         <v>45670</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60183,7 +60183,7 @@
         <v>45602</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60256,7 +60256,7 @@
         <v>45553</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60329,7 +60329,7 @@
         <v>45432</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60407,7 +60407,7 @@
         <v>45782</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60480,7 +60480,7 @@
         <v>45546</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60553,7 +60553,7 @@
         <v>46120</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60626,7 +60626,7 @@
         <v>46274</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>45784</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60777,7 +60777,7 @@
         <v>45709</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60850,7 +60850,7 @@
         <v>45784</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60923,7 +60923,7 @@
         <v>45176</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -60996,7 +60996,7 @@
         <v>44783</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>45266</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61147,7 +61147,7 @@
         <v>45712</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61220,7 +61220,7 @@
         <v>45679</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>45789</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61366,7 +61366,7 @@
         <v>45679</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61439,7 +61439,7 @@
         <v>45230</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61512,7 +61512,7 @@
         <v>44783</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61585,7 +61585,7 @@
         <v>45568</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61658,7 +61658,7 @@
         <v>45511</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61731,7 +61731,7 @@
         <v>46279</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61804,7 +61804,7 @@
         <v>45636</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61882,7 +61882,7 @@
         <v>45345</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61955,7 +61955,7 @@
         <v>45252</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62028,7 +62028,7 @@
         <v>45594</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62101,7 +62101,7 @@
         <v>45345</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
         <v>45562</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62247,7 +62247,7 @@
         <v>45590</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62320,7 +62320,7 @@
         <v>45597</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62393,7 +62393,7 @@
         <v>45637</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62471,7 +62471,7 @@
         <v>45576</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62544,7 +62544,7 @@
         <v>45565</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62617,7 +62617,7 @@
         <v>45524</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62690,7 +62690,7 @@
         <v>45670</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62763,7 +62763,7 @@
         <v>45793</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>45793</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>45793</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -62982,7 +62982,7 @@
         <v>45793</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63055,7 +63055,7 @@
         <v>45477</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63128,7 +63128,7 @@
         <v>45533</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63201,7 +63201,7 @@
         <v>45692</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63274,7 +63274,7 @@
         <v>45478</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>45684</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63420,7 +63420,7 @@
         <v>45637</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63498,7 +63498,7 @@
         <v>45727</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63571,7 +63571,7 @@
         <v>45811</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63644,7 +63644,7 @@
         <v>45793</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63717,7 +63717,7 @@
         <v>45820</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63790,7 +63790,7 @@
         <v>45827</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63863,7 +63863,7 @@
         <v>45831</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -63936,7 +63936,7 @@
         <v>45831</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64009,7 +64009,7 @@
         <v>45832</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>44609</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64160,7 +64160,7 @@
         <v>45838</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64233,7 +64233,7 @@
         <v>45839</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64306,7 +64306,7 @@
         <v>45434</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64379,7 +64379,7 @@
         <v>45841</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64452,7 +64452,7 @@
         <v>45677</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64530,7 +64530,7 @@
         <v>45841</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64603,7 +64603,7 @@
         <v>45751</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64676,7 +64676,7 @@
         <v>45684</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64749,7 +64749,7 @@
         <v>45090</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64822,7 +64822,7 @@
         <v>45644</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -64895,7 +64895,7 @@
         <v>45873</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -64968,7 +64968,7 @@
         <v>45873</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65041,7 +65041,7 @@
         <v>45873</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65114,7 +65114,7 @@
         <v>45874</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65187,7 +65187,7 @@
         <v>45877</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65260,7 +65260,7 @@
         <v>45881</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65333,7 +65333,7 @@
         <v>45881</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65406,7 +65406,7 @@
         <v>45387</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65479,7 +65479,7 @@
         <v>45387</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65552,7 +65552,7 @@
         <v>45456</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65625,7 +65625,7 @@
         <v>45602</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65698,7 +65698,7 @@
         <v>44894</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65771,7 +65771,7 @@
         <v>45443</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65844,7 +65844,7 @@
         <v>44672</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -65917,7 +65917,7 @@
         <v>44888</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -65990,7 +65990,7 @@
         <v>44900</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66063,7 +66063,7 @@
         <v>45359</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66136,7 +66136,7 @@
         <v>45359</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66209,7 +66209,7 @@
         <v>44722</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66282,7 +66282,7 @@
         <v>45387</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66355,7 +66355,7 @@
         <v>45128</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66428,7 +66428,7 @@
         <v>45387</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66501,7 +66501,7 @@
         <v>45362</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66574,7 +66574,7 @@
         <v>45534</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66647,7 +66647,7 @@
         <v>44901</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66720,7 +66720,7 @@
         <v>44792</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66798,7 +66798,7 @@
         <v>45362</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66871,7 +66871,7 @@
         <v>45330</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -66944,7 +66944,7 @@
         <v>44883</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67017,7 +67017,7 @@
         <v>45330</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -67090,7 +67090,7 @@
         <v>44928</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -67163,7 +67163,7 @@
         <v>45477</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -67236,7 +67236,7 @@
         <v>44971</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -67309,7 +67309,7 @@
         <v>44900</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -67382,7 +67382,7 @@
         <v>44971</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -67455,7 +67455,7 @@
         <v>45230</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -67528,7 +67528,7 @@
         <v>45730</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -67601,7 +67601,7 @@
         <v>45665</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -67674,7 +67674,7 @@
         <v>45727</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -67747,7 +67747,7 @@
         <v>45665</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -67820,7 +67820,7 @@
         <v>45807</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -67893,7 +67893,7 @@
         <v>45807</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -67966,7 +67966,7 @@
         <v>46038</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -68039,7 +68039,7 @@
         <v>46042</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -68112,7 +68112,7 @@
         <v>46042</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -68185,7 +68185,7 @@
         <v>46042</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -68258,7 +68258,7 @@
         <v>46042</v>
       </c>
       <c r="E902" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -68331,7 +68331,7 @@
         <v>46045</v>
       </c>
       <c r="E903" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -68404,7 +68404,7 @@
         <v>46132</v>
       </c>
       <c r="E904" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -68477,7 +68477,7 @@
         <v>46181</v>
       </c>
       <c r="E905" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -68550,7 +68550,7 @@
         <v>46188</v>
       </c>
       <c r="E906" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
@@ -68623,7 +68623,7 @@
         <v>46213</v>
       </c>
       <c r="E907" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44977</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44740</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45565</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>44992</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46050</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>44872</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>45387</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>44599</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>44578</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45461</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45646</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45001</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46086</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44729</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45580</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45103</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>44489</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>45546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>46289</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>44984</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>45341</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45322</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45387</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45330</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>45467</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45555</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>45890</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>46056</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44732</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44620</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44620</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44813</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44508</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44875</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44539</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44489</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44575</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44819</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44570</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44494</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44641</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44692</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44690</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44470</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44610</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44865</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44791</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44603</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44644</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44627</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44804</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44467</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44789</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44508</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44546</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44867</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>44879</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44791</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44875</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44532</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44879</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>44494</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>44466</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>44489</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44529</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44648</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>44631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44620</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>44620</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>44481</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>44636</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44519</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44791</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>44748</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44888</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44474</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>44494</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44509</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44522</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>44533</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44722</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44468</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44698</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>44680</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44631</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>44523</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>44749</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>44711</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>44676</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44753</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>44540</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>44620</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44540</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44875</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44698</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44685</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44641</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44539</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>44631</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>44523</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>44753</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44712</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44596</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>45553</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>45362</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>45173</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44769</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44490</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>44820</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44875</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>45338</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>45395</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45411</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45412</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45097</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45091</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45702</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44481</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45252</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45300</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>45449</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45449</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44883</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45394</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>45089</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45439</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45117</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45117</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45467</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45467</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45467</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45455</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44928</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45085</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>45793</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45445</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45477</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>45533</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44903</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45793</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45329</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>45793</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44728</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44489</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45154</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45436</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>45152</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>44545</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45793</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45310</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45475</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45180</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>46031</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>46031</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>45436</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45240</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45005</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45671</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45887</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>46036</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>44936</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44936</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45246</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>46038</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46038</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>46038</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45644</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45394</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45896</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45329</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45692</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>44895</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>46044</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45540</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>44481</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>46044</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>46048</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45362</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45646</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45443</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45904</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44907</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45792</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45789</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45905</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45908</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44599</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45478</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45533</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45477</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44930</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44995</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45155</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45637</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>46063</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>46063</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44928</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>46063</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45007</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>44971</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45684</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45923</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45727</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45923</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45012</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45014</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44676</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44950</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>44945</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45264</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45264</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45029</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45548</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45240</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>44936</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46078</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45568</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46083</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44617</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>46083</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>46083</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>46083</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45155</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45155</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44620</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45933</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45614</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45439</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>46086</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45637</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>46090</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45938</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>44928</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>45071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45344</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44470</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>44928</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>46098</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45162</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44963</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45811</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>46101</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45091</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>46101</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>46100</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>46104</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>44685</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44685</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44993</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45182</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>46104</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45077</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>45950</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44673</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>46106</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45614</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45107</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44620</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>46108</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45953</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>46108</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46108</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>46108</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45034</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>46113</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>46119</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45579</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45574</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45574</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>46120</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45580</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44984</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45307</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>46120</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45964</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45007</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45608</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45972</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45461</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>44545</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45119</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>46120</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>46132</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45062</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45009</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>44993</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45096</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45610</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>46105</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>45674</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>46132</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>46133</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>45979</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44998</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>46134</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45547</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>46133</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45462</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45982</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45782</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44951</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45897</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45992</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45553</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45803</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45552</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45897</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45924</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45596</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45755</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>46010</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45742</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45908</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45884</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45474</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45933</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>45981</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>46136</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45629</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>44748</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45834</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>45701</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45841</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>45099</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>46003</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45711</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>46010</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45469</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45617</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45926</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45890</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45121</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45299</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45993</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45722</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>45902</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>44994</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>46000</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>44495</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>45903</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44505</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45062</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45063</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>46000</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45873</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45078</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45036</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45992</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>46136</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45035</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45820</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>44529</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45793</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>46007</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>45821</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>46035</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44930</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>45167</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45188</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45710</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>45726</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44937</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>45188</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45772</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45755</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44991</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>44991</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45247</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45247</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44988</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45113</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>45110</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45244</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>45278</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45063</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>46031</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>45002</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44930</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45904</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44627</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45264</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>45071</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>45071</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45071</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45260</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34009,7 +34009,7 @@
         <v>45827</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45758</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>44631</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45112</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45735</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45735</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>45831</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34525,7 +34525,7 @@
         <v>45466</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44473</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>44790</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34744,7 +34744,7 @@
         <v>45082</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45082</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34890,7 +34890,7 @@
         <v>44609</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34968,7 +34968,7 @@
         <v>45106</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>44916</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>46148</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>45261</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>45709</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>46148</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>45831</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>45439</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>45832</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46149</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>46154</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>45229</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>45407</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>46043</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>45075</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45902</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45110</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45107</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>45700</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36370,7 +36370,7 @@
         <v>45261</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45838</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>45434</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45103</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>45183</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>46160</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44483</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>45839</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45034</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>45170</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45841</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45574</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45841</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46162</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>44895</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>45330</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>45677</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>44960</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>46162</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44967</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>46167</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>46167</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45370</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>46168</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45240</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>46168</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>46168</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45751</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>46167</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>46167</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>44953</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>44904</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45325</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45107</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>46171</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45629</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>44949</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>44949</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45002</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45314</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45684</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45090</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45392</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>46175</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45069</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45275</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>44838</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>44545</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>46175</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44945</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>44524</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>44881</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45424</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45019</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44930</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>45644</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45049</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45097</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>45546</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>46176</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>46177</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44964</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>46175</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>46181</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>45250</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>45166</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>46182</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45546</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>46146</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46135</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>46182</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>46184</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>46184</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>46182</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44558</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44540</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>46184</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45873</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45873</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45342</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>44575</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>44620</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45160</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45274</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>46188</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45155</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45155</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45635</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45540</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45874</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45631</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>46190</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45873</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>46189</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>44795</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45877</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>46197</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45033</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>46197</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>44570</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>44550</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45107</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>44586</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45631</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>45426</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45152</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45418</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45881</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45881</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>46198</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>46199</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>46204</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45078</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45727</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>46203</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>46204</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>46204</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>46204</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>44489</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44683</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45618</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>46205</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45408</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45175</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46204</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45267</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45203</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45082</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>46251</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45191</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>45106</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>46206</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>45085</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>46206</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45107</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>44627</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>44624</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>45547</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>45176</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>45215</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45609</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44621</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>44614</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>45210</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>46212</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45215</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45147</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>46213</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45138</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45713</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45090</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>44820</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45635</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>46213</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47760,7 +47760,7 @@
         <v>45244</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>46213</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45574</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47979,7 +47979,7 @@
         <v>45245</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45211</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>44657</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>46260</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45684</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>46260</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>46260</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>45183</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>45183</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45117</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>44749</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>46189</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>44728</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44728</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>45173</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>44655</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45226</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>44700</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45181</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>44705</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>46209</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>46262</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>44852</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>46045</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>44753</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>46262</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>45164</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45164</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45197</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>45264</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>45117</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45236</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45331</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45303</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45238</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>45109</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>45109</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50690,7 +50690,7 @@
         <v>45302</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>46266</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>45775</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>44804</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45306</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>46195</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>46195</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51201,7 +51201,7 @@
         <v>46195</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>45314</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
         <v>44804</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>46191</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51493,7 +51493,7 @@
         <v>45176</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45366</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>44756</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>44901</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>44901</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>45267</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
         <v>45399</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>46274</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>44904</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>44867</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52228,7 +52228,7 @@
         <v>44950</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>44831</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>44831</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52447,7 +52447,7 @@
         <v>44522</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45082</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45432</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>46120</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45327</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45272</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45264</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45201</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53046,7 +53046,7 @@
         <v>44748</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>46279</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>44691</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>45303</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53338,7 +53338,7 @@
         <v>45616</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45429</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45201</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>45574</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53630,7 +53630,7 @@
         <v>45386</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45412</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>44984</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>45371</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>45406</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>44602</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>44657</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>44967</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45572</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>46202</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>44628</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54433,7 +54433,7 @@
         <v>46244</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>44967</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>44939</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>44988</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54730,7 +54730,7 @@
         <v>45568</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>46287</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>45188</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45062</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>45395</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>45002</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45600</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>44938</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>44909</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
         <v>44698</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>45331</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>45331</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45331</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55679,7 +55679,7 @@
         <v>45155</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>44509</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45176</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45359</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>45036</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56044,7 +56044,7 @@
         <v>46147</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45384</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>45447</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
         <v>44818</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>44930</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>45978</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>44631</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>44900</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>45474</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>44904</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45261</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>44967</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>44967</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>44518</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45607</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57144,7 +57144,7 @@
         <v>45547</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45086</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>45674</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57363,7 +57363,7 @@
         <v>45005</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>45005</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>45252</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57582,7 +57582,7 @@
         <v>45701</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>45547</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45106</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>44965</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>44964</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57947,7 +57947,7 @@
         <v>44712</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>45051</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
         <v>44599</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45033</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45129</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58312,7 +58312,7 @@
         <v>44895</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58385,7 +58385,7 @@
         <v>44916</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>44972</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45601</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45680</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45139</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>45117</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>45117</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58896,7 +58896,7 @@
         <v>45082</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58969,7 +58969,7 @@
         <v>45646</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59042,7 +59042,7 @@
         <v>44888</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59115,7 +59115,7 @@
         <v>45377</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59188,7 +59188,7 @@
         <v>45215</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59261,7 +59261,7 @@
         <v>45394</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59334,7 +59334,7 @@
         <v>45035</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59407,7 +59407,7 @@
         <v>45401</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59480,7 +59480,7 @@
         <v>44984</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59553,7 +59553,7 @@
         <v>45688</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59626,7 +59626,7 @@
         <v>45279</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59699,7 +59699,7 @@
         <v>45331</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>45771</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59845,7 +59845,7 @@
         <v>45240</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59918,7 +59918,7 @@
         <v>44949</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59991,7 +59991,7 @@
         <v>44971</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60064,7 +60064,7 @@
         <v>45601</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>45574</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45356</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60288,7 +60288,7 @@
         <v>45755</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60361,7 +60361,7 @@
         <v>45727</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60434,7 +60434,7 @@
         <v>44935</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45034</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>45002</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60653,7 +60653,7 @@
         <v>45124</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60726,7 +60726,7 @@
         <v>44960</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>45553</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>44634</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>45394</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>45439</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61091,7 +61091,7 @@
         <v>45691</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
         <v>45559</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>45637</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>45637</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>45615</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61471,7 +61471,7 @@
         <v>45540</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61544,7 +61544,7 @@
         <v>45386</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>45194</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61690,7 +61690,7 @@
         <v>44950</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61763,7 +61763,7 @@
         <v>45327</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61841,7 +61841,7 @@
         <v>45432</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61914,7 +61914,7 @@
         <v>45434</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>45408</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62060,7 +62060,7 @@
         <v>45349</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62133,7 +62133,7 @@
         <v>45274</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62206,7 +62206,7 @@
         <v>45670</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62279,7 +62279,7 @@
         <v>45562</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62352,7 +62352,7 @@
         <v>45419</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62425,7 +62425,7 @@
         <v>45519</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62498,7 +62498,7 @@
         <v>45574</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62571,7 +62571,7 @@
         <v>45089</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62644,7 +62644,7 @@
         <v>45602</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62717,7 +62717,7 @@
         <v>45615</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62790,7 +62790,7 @@
         <v>45782</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62863,7 +62863,7 @@
         <v>45784</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -62936,7 +62936,7 @@
         <v>45553</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63009,7 +63009,7 @@
         <v>45784</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63082,7 +63082,7 @@
         <v>45594</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63155,7 +63155,7 @@
         <v>45252</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63228,7 +63228,7 @@
         <v>45590</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45546</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63374,7 +63374,7 @@
         <v>45679</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63447,7 +63447,7 @@
         <v>45709</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63520,7 +63520,7 @@
         <v>45176</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63593,7 +63593,7 @@
         <v>45670</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         <v>45679</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>44783</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63812,7 +63812,7 @@
         <v>45568</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>45562</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -63958,7 +63958,7 @@
         <v>45511</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64031,7 +64031,7 @@
         <v>45636</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64109,7 +64109,7 @@
         <v>45597</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64182,7 +64182,7 @@
         <v>45524</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64255,7 +64255,7 @@
         <v>45576</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64328,7 +64328,7 @@
         <v>45565</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64401,7 +64401,7 @@
         <v>44783</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64474,7 +64474,7 @@
         <v>45230</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64547,7 +64547,7 @@
         <v>45266</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45789</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64698,7 +64698,7 @@
         <v>45712</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64771,7 +64771,7 @@
         <v>45345</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64844,7 +64844,7 @@
         <v>45637</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -64922,7 +64922,7 @@
         <v>45345</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -64995,7 +64995,7 @@
         <v>44672</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65068,7 +65068,7 @@
         <v>44722</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65141,7 +65141,7 @@
         <v>45387</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65214,7 +65214,7 @@
         <v>45387</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65287,7 +65287,7 @@
         <v>45456</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65360,7 +65360,7 @@
         <v>45602</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65433,7 +65433,7 @@
         <v>44894</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         <v>45443</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>44888</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65652,7 +65652,7 @@
         <v>44900</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65725,7 +65725,7 @@
         <v>45359</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65798,7 +65798,7 @@
         <v>45359</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65871,7 +65871,7 @@
         <v>45387</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -65944,7 +65944,7 @@
         <v>45128</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66017,7 +66017,7 @@
         <v>45387</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66090,7 +66090,7 @@
         <v>45362</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66163,7 +66163,7 @@
         <v>45534</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66236,7 +66236,7 @@
         <v>44901</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66309,7 +66309,7 @@
         <v>44792</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66387,7 +66387,7 @@
         <v>45362</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66460,7 +66460,7 @@
         <v>45330</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66533,7 +66533,7 @@
         <v>44883</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66606,7 +66606,7 @@
         <v>45330</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66679,7 +66679,7 @@
         <v>44928</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66752,7 +66752,7 @@
         <v>45477</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66825,7 +66825,7 @@
         <v>44971</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66898,7 +66898,7 @@
         <v>44900</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -66971,7 +66971,7 @@
         <v>44971</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67044,7 +67044,7 @@
         <v>45230</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -67117,7 +67117,7 @@
         <v>45730</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -67190,7 +67190,7 @@
         <v>45665</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -67263,7 +67263,7 @@
         <v>45727</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -67336,7 +67336,7 @@
         <v>45665</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -67409,7 +67409,7 @@
         <v>45807</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -67482,7 +67482,7 @@
         <v>45807</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -67555,7 +67555,7 @@
         <v>46038</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -67628,7 +67628,7 @@
         <v>46042</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -67701,7 +67701,7 @@
         <v>46042</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -67774,7 +67774,7 @@
         <v>46042</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -67847,7 +67847,7 @@
         <v>46042</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -67920,7 +67920,7 @@
         <v>46045</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -67993,7 +67993,7 @@
         <v>46132</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -68066,7 +68066,7 @@
         <v>46181</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -68139,7 +68139,7 @@
         <v>46188</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -68212,7 +68212,7 @@
         <v>46213</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44977</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44740</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45565</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>44992</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46050</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>44872</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45099</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>45387</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>44599</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>44578</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>45461</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
         <v>44992</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45646</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45001</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46086</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>44729</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45580</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45103</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>44489</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>45546</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>46213</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>46289</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>44984</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>45341</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45322</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         <v>45387</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5156,7 +5156,7 @@
         <v>45330</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>45467</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5364,7 +5364,7 @@
         <v>45153</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>45555</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>45890</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>46056</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5784,7 +5784,7 @@
         <v>44888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5857,7 +5857,7 @@
         <v>44557</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5930,7 +5930,7 @@
         <v>44841</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         <v>44732</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
         <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44620</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>44620</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6305,7 +6305,7 @@
         <v>44813</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6378,7 +6378,7 @@
         <v>44508</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>44875</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44539</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6597,7 +6597,7 @@
         <v>44755</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44713</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44489</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         <v>44813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6962,7 +6962,7 @@
         <v>44865</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7035,7 +7035,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>44533</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7181,7 +7181,7 @@
         <v>44575</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7254,7 +7254,7 @@
         <v>44819</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>44570</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         <v>44494</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44641</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44692</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44690</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44470</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44610</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44865</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44791</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44603</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44644</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44627</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44804</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44467</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8349,7 +8349,7 @@
         <v>44789</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>44508</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8495,7 +8495,7 @@
         <v>44546</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8568,7 +8568,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8641,7 +8641,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8714,7 +8714,7 @@
         <v>44867</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>44879</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>44839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44791</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44875</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44532</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44879</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>44494</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>44466</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>44489</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44529</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9668,7 +9668,7 @@
         <v>44798</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44648</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         <v>44631</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>44608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9960,7 +9960,7 @@
         <v>44620</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>44620</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>44481</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>44636</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>44519</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10335,7 +10335,7 @@
         <v>44791</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>44748</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>44888</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44820</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10627,7 +10627,7 @@
         <v>44474</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10700,7 +10700,7 @@
         <v>44494</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10773,7 +10773,7 @@
         <v>44509</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
         <v>44522</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10919,7 +10919,7 @@
         <v>44533</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10992,7 +10992,7 @@
         <v>44722</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44468</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11138,7 +11138,7 @@
         <v>44698</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11211,7 +11211,7 @@
         <v>44680</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44631</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>44523</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11430,7 +11430,7 @@
         <v>44749</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11503,7 +11503,7 @@
         <v>44711</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11576,7 +11576,7 @@
         <v>44676</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>44753</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>44540</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>44620</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11868,7 +11868,7 @@
         <v>44540</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44875</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44698</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44685</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44641</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12233,7 +12233,7 @@
         <v>44539</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12306,7 +12306,7 @@
         <v>44631</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>44523</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12452,7 +12452,7 @@
         <v>44753</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44712</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12598,7 +12598,7 @@
         <v>44596</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12671,7 +12671,7 @@
         <v>45553</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12744,7 +12744,7 @@
         <v>45362</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>45173</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12890,7 +12890,7 @@
         <v>44769</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44490</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13041,7 +13041,7 @@
         <v>44820</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44875</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>45338</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13260,7 +13260,7 @@
         <v>45395</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>45411</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>45412</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>45097</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>45091</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45702</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44481</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45252</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45300</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>45449</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45449</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44883</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45394</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>45089</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45439</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14360,7 +14360,7 @@
         <v>45117</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14433,7 +14433,7 @@
         <v>45117</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14506,7 +14506,7 @@
         <v>45467</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14579,7 +14579,7 @@
         <v>45467</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14652,7 +14652,7 @@
         <v>45467</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45455</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14798,7 +14798,7 @@
         <v>44928</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45085</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>45793</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15017,7 +15017,7 @@
         <v>45445</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45477</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>45533</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>44903</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15309,7 +15309,7 @@
         <v>45793</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15382,7 +15382,7 @@
         <v>45329</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>45793</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>44728</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
         <v>44489</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>45154</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15752,7 +15752,7 @@
         <v>45436</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15825,7 +15825,7 @@
         <v>45152</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>44545</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15971,7 +15971,7 @@
         <v>45793</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45310</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16117,7 +16117,7 @@
         <v>45475</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16190,7 +16190,7 @@
         <v>45180</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>46031</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>46031</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16409,7 +16409,7 @@
         <v>45436</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45240</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45005</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>45671</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16701,7 +16701,7 @@
         <v>45887</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16774,7 +16774,7 @@
         <v>46036</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16852,7 +16852,7 @@
         <v>44936</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>44936</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
         <v>45246</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17071,7 +17071,7 @@
         <v>46038</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>46038</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17217,7 +17217,7 @@
         <v>46038</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>45644</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17363,7 +17363,7 @@
         <v>45394</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17436,7 +17436,7 @@
         <v>45896</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>44911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17582,7 +17582,7 @@
         <v>45329</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45692</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>44895</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>46044</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17884,7 +17884,7 @@
         <v>45540</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>44481</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         <v>46044</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>46048</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45362</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45646</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45443</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18400,7 +18400,7 @@
         <v>45904</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18478,7 +18478,7 @@
         <v>44907</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18551,7 +18551,7 @@
         <v>45539</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18624,7 +18624,7 @@
         <v>45792</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18697,7 +18697,7 @@
         <v>45789</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18770,7 +18770,7 @@
         <v>45905</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18843,7 +18843,7 @@
         <v>45908</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18916,7 +18916,7 @@
         <v>44599</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>45478</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>45533</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19135,7 +19135,7 @@
         <v>45477</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19208,7 +19208,7 @@
         <v>44930</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19281,7 +19281,7 @@
         <v>44995</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19354,7 +19354,7 @@
         <v>45155</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45637</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19505,7 +19505,7 @@
         <v>46063</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19578,7 +19578,7 @@
         <v>46063</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>44928</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19724,7 +19724,7 @@
         <v>46063</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19797,7 +19797,7 @@
         <v>45007</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19870,7 +19870,7 @@
         <v>44971</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>45684</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45923</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>45727</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45923</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45012</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45014</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44676</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44950</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>44965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>44945</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45264</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45264</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>44939</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45029</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45548</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>45240</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>44936</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44936</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46078</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21335,7 +21335,7 @@
         <v>45568</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21408,7 +21408,7 @@
         <v>46083</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21481,7 +21481,7 @@
         <v>44617</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>46083</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
         <v>46083</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21700,7 +21700,7 @@
         <v>46083</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21773,7 +21773,7 @@
         <v>45155</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21846,7 +21846,7 @@
         <v>45155</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44620</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45933</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45614</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
         <v>45439</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22216,7 +22216,7 @@
         <v>46086</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22289,7 +22289,7 @@
         <v>45637</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>46090</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>45938</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>44928</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>45071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45344</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44470</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>44928</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>46098</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45162</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>44963</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45811</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>46101</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45091</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>46101</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>46100</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>46104</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>44685</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>44685</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>44993</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45182</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>46104</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45077</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>45950</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>44673</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>46106</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45614</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24275,7 +24275,7 @@
         <v>45107</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24348,7 +24348,7 @@
         <v>44620</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24421,7 +24421,7 @@
         <v>46108</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24494,7 +24494,7 @@
         <v>45953</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>46108</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>46108</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>46108</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45034</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>46113</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>46119</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>45579</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45574</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45574</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>46120</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25297,7 +25297,7 @@
         <v>45580</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>44984</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>45323</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45307</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>46120</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45964</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45007</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45608</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45972</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45461</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>44545</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45119</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>46120</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>46132</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45062</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45009</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>44993</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>45096</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26621,7 +26621,7 @@
         <v>45610</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>46105</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26767,7 +26767,7 @@
         <v>45674</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>46132</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45093</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>46133</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>45979</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>44998</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>46134</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45980</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45547</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>46133</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45462</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45982</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45782</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44951</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45897</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45992</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         <v>45553</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>45803</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28086,7 +28086,7 @@
         <v>45552</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28159,7 +28159,7 @@
         <v>45897</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28232,7 +28232,7 @@
         <v>45924</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45596</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28378,7 +28378,7 @@
         <v>45755</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28451,7 +28451,7 @@
         <v>46010</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28524,7 +28524,7 @@
         <v>45742</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>45908</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28670,7 +28670,7 @@
         <v>45884</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28743,7 +28743,7 @@
         <v>45474</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28816,7 +28816,7 @@
         <v>45933</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28889,7 +28889,7 @@
         <v>45981</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>46136</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45629</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>44748</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         <v>45834</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29254,7 +29254,7 @@
         <v>45701</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45841</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>45099</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>46003</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45711</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>46010</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29692,7 +29692,7 @@
         <v>45469</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45617</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>45926</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29911,7 +29911,7 @@
         <v>45890</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -29984,7 +29984,7 @@
         <v>45121</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>45299</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>45993</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30203,7 +30203,7 @@
         <v>45722</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>45902</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30349,7 +30349,7 @@
         <v>44994</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30422,7 +30422,7 @@
         <v>46000</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30495,7 +30495,7 @@
         <v>44495</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>45903</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>44505</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30719,7 +30719,7 @@
         <v>46000</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30792,7 +30792,7 @@
         <v>45062</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30865,7 +30865,7 @@
         <v>45063</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>46000</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31011,7 +31011,7 @@
         <v>45873</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45078</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31157,7 +31157,7 @@
         <v>45036</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31230,7 +31230,7 @@
         <v>45992</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31303,7 +31303,7 @@
         <v>46136</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>45035</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45820</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>44529</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>45793</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>46007</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31746,7 +31746,7 @@
         <v>45821</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31819,7 +31819,7 @@
         <v>46035</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>44930</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>45167</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45188</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45710</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>45726</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>44937</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>45188</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>45772</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32476,7 +32476,7 @@
         <v>45755</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>44991</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32622,7 +32622,7 @@
         <v>44991</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32695,7 +32695,7 @@
         <v>45247</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32768,7 +32768,7 @@
         <v>45247</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>44988</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32914,7 +32914,7 @@
         <v>45113</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -32987,7 +32987,7 @@
         <v>45110</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>45244</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33133,7 +33133,7 @@
         <v>45278</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45063</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33279,7 +33279,7 @@
         <v>46031</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33352,7 +33352,7 @@
         <v>45002</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33425,7 +33425,7 @@
         <v>44930</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33498,7 +33498,7 @@
         <v>45904</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>44627</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>45264</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33717,7 +33717,7 @@
         <v>45071</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33790,7 +33790,7 @@
         <v>45071</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33863,7 +33863,7 @@
         <v>45071</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33936,7 +33936,7 @@
         <v>45260</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34009,7 +34009,7 @@
         <v>45827</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34082,7 +34082,7 @@
         <v>45758</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>44631</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34233,7 +34233,7 @@
         <v>45112</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34306,7 +34306,7 @@
         <v>45735</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45735</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34452,7 +34452,7 @@
         <v>45831</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34525,7 +34525,7 @@
         <v>45466</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44473</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34671,7 +34671,7 @@
         <v>44790</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34744,7 +34744,7 @@
         <v>45082</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34817,7 +34817,7 @@
         <v>45082</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34890,7 +34890,7 @@
         <v>44609</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -34968,7 +34968,7 @@
         <v>45106</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35041,7 +35041,7 @@
         <v>44916</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35114,7 +35114,7 @@
         <v>46148</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35187,7 +35187,7 @@
         <v>45261</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35260,7 +35260,7 @@
         <v>45709</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35338,7 +35338,7 @@
         <v>46148</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35411,7 +35411,7 @@
         <v>45831</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35484,7 +35484,7 @@
         <v>45439</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35557,7 +35557,7 @@
         <v>45832</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35630,7 +35630,7 @@
         <v>46149</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35703,7 +35703,7 @@
         <v>46154</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35776,7 +35776,7 @@
         <v>45229</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>45407</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35922,7 +35922,7 @@
         <v>46043</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36000,7 +36000,7 @@
         <v>45075</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36078,7 +36078,7 @@
         <v>45902</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45110</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36224,7 +36224,7 @@
         <v>45107</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36297,7 +36297,7 @@
         <v>45700</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36370,7 +36370,7 @@
         <v>45261</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36443,7 +36443,7 @@
         <v>45838</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>45434</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36589,7 +36589,7 @@
         <v>45103</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>45183</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>46160</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44483</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>45839</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>45034</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>45170</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45841</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45574</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45841</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>46162</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>44895</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>45330</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>45677</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>44960</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>46162</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>44967</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37840,7 +37840,7 @@
         <v>46167</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37913,7 +37913,7 @@
         <v>46167</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -37986,7 +37986,7 @@
         <v>45370</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38059,7 +38059,7 @@
         <v>46168</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38132,7 +38132,7 @@
         <v>45240</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>46168</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>46168</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45751</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>46167</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>46167</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>44953</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>44904</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45325</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45107</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>46171</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45629</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>44949</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>44949</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45002</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45314</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39305,7 +39305,7 @@
         <v>45684</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39378,7 +39378,7 @@
         <v>45090</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39451,7 +39451,7 @@
         <v>45392</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39524,7 +39524,7 @@
         <v>46175</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45069</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39670,7 +39670,7 @@
         <v>45275</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>44838</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39816,7 +39816,7 @@
         <v>44545</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>46175</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>44945</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40035,7 +40035,7 @@
         <v>44524</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40108,7 +40108,7 @@
         <v>44881</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40181,7 +40181,7 @@
         <v>45424</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40254,7 +40254,7 @@
         <v>45019</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40327,7 +40327,7 @@
         <v>44930</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>45644</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>45049</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45097</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>45546</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>46176</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>46177</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>44964</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>46175</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>46181</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>45250</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>45166</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41203,7 +41203,7 @@
         <v>46182</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41276,7 +41276,7 @@
         <v>45546</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>46146</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46135</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41495,7 +41495,7 @@
         <v>46182</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41568,7 +41568,7 @@
         <v>46184</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41641,7 +41641,7 @@
         <v>46184</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41714,7 +41714,7 @@
         <v>46182</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41787,7 +41787,7 @@
         <v>44558</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>44540</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>46184</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>45873</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45873</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42152,7 +42152,7 @@
         <v>45342</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42225,7 +42225,7 @@
         <v>44575</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42298,7 +42298,7 @@
         <v>44620</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>45160</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42449,7 +42449,7 @@
         <v>45274</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42522,7 +42522,7 @@
         <v>46188</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42595,7 +42595,7 @@
         <v>45155</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
         <v>45155</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42741,7 +42741,7 @@
         <v>45635</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42819,7 +42819,7 @@
         <v>45540</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42892,7 +42892,7 @@
         <v>45874</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45631</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43038,7 +43038,7 @@
         <v>46190</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43111,7 +43111,7 @@
         <v>45873</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>46189</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43257,7 +43257,7 @@
         <v>44795</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>45877</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43403,7 +43403,7 @@
         <v>46197</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43476,7 +43476,7 @@
         <v>45033</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43549,7 +43549,7 @@
         <v>46197</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43622,7 +43622,7 @@
         <v>44570</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43695,7 +43695,7 @@
         <v>44550</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43768,7 +43768,7 @@
         <v>45107</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>44586</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43914,7 +43914,7 @@
         <v>45631</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>45426</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44060,7 +44060,7 @@
         <v>45152</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45418</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44211,7 +44211,7 @@
         <v>45881</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44284,7 +44284,7 @@
         <v>45881</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>46198</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>46199</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44503,7 +44503,7 @@
         <v>46204</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>45078</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44649,7 +44649,7 @@
         <v>45727</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44722,7 +44722,7 @@
         <v>46203</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>46204</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>46204</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>46204</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>44489</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45102,7 +45102,7 @@
         <v>44683</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45175,7 +45175,7 @@
         <v>45618</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>46205</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45408</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45175</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46204</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>45267</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45203</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45686,7 +45686,7 @@
         <v>45082</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>46251</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>45191</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45910,7 +45910,7 @@
         <v>45106</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>46206</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46056,7 +46056,7 @@
         <v>46206</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>45085</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>46206</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>45107</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>44627</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>44624</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>45547</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>45176</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>45215</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>45609</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>44621</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>44614</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>45210</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>46212</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45215</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47171,7 +47171,7 @@
         <v>45147</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47244,7 +47244,7 @@
         <v>46213</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>45138</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>45713</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>45090</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47536,7 +47536,7 @@
         <v>44820</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47609,7 +47609,7 @@
         <v>45635</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47687,7 +47687,7 @@
         <v>46213</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47760,7 +47760,7 @@
         <v>45244</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47833,7 +47833,7 @@
         <v>46213</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45574</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -47979,7 +47979,7 @@
         <v>45245</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48052,7 +48052,7 @@
         <v>45211</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48125,7 +48125,7 @@
         <v>44657</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>46260</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>45684</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48344,7 +48344,7 @@
         <v>46260</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48417,7 +48417,7 @@
         <v>46260</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48490,7 +48490,7 @@
         <v>45183</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48563,7 +48563,7 @@
         <v>45183</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48636,7 +48636,7 @@
         <v>45117</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>44749</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>46189</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48855,7 +48855,7 @@
         <v>44728</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48928,7 +48928,7 @@
         <v>44728</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49001,7 +49001,7 @@
         <v>45173</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49074,7 +49074,7 @@
         <v>44655</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49147,7 +49147,7 @@
         <v>45226</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49220,7 +49220,7 @@
         <v>44700</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49293,7 +49293,7 @@
         <v>45181</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>44705</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>46209</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49517,7 +49517,7 @@
         <v>46262</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>44852</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>46045</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49741,7 +49741,7 @@
         <v>44753</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>46262</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49887,7 +49887,7 @@
         <v>45164</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49960,7 +49960,7 @@
         <v>45164</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50033,7 +50033,7 @@
         <v>45197</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50106,7 +50106,7 @@
         <v>45264</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50179,7 +50179,7 @@
         <v>45117</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50252,7 +50252,7 @@
         <v>45236</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45331</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50398,7 +50398,7 @@
         <v>45303</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45238</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50544,7 +50544,7 @@
         <v>45109</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50617,7 +50617,7 @@
         <v>45109</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50690,7 +50690,7 @@
         <v>45302</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>46266</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>45775</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>44804</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45306</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>46195</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>46195</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51201,7 +51201,7 @@
         <v>46195</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>45314</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
         <v>44804</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51420,7 +51420,7 @@
         <v>46191</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51493,7 +51493,7 @@
         <v>45176</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45366</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51639,7 +51639,7 @@
         <v>44756</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51712,7 +51712,7 @@
         <v>44901</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>44901</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51858,7 +51858,7 @@
         <v>45267</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51931,7 +51931,7 @@
         <v>45399</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52004,7 +52004,7 @@
         <v>46274</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52082,7 +52082,7 @@
         <v>44904</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52155,7 +52155,7 @@
         <v>44867</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52228,7 +52228,7 @@
         <v>44950</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52301,7 +52301,7 @@
         <v>44831</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52374,7 +52374,7 @@
         <v>44831</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52447,7 +52447,7 @@
         <v>44522</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52525,7 +52525,7 @@
         <v>45082</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52598,7 +52598,7 @@
         <v>45432</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52676,7 +52676,7 @@
         <v>46120</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52749,7 +52749,7 @@
         <v>45327</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52827,7 +52827,7 @@
         <v>45272</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52900,7 +52900,7 @@
         <v>45264</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -52973,7 +52973,7 @@
         <v>45201</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53046,7 +53046,7 @@
         <v>44748</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53119,7 +53119,7 @@
         <v>46279</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53192,7 +53192,7 @@
         <v>44691</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53265,7 +53265,7 @@
         <v>45303</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53338,7 +53338,7 @@
         <v>45616</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53411,7 +53411,7 @@
         <v>45429</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>45201</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>45574</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53630,7 +53630,7 @@
         <v>45386</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45412</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53776,7 +53776,7 @@
         <v>44984</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53849,7 +53849,7 @@
         <v>45371</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>45406</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -53995,7 +53995,7 @@
         <v>44602</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54068,7 +54068,7 @@
         <v>44657</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54141,7 +54141,7 @@
         <v>44967</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45572</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>46202</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54360,7 +54360,7 @@
         <v>44628</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54433,7 +54433,7 @@
         <v>46244</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54506,7 +54506,7 @@
         <v>44967</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54584,7 +54584,7 @@
         <v>44939</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54657,7 +54657,7 @@
         <v>44988</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54730,7 +54730,7 @@
         <v>45568</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54803,7 +54803,7 @@
         <v>46287</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54876,7 +54876,7 @@
         <v>45188</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>45062</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55022,7 +55022,7 @@
         <v>45395</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55095,7 +55095,7 @@
         <v>45002</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55168,7 +55168,7 @@
         <v>45600</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55241,7 +55241,7 @@
         <v>44938</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55314,7 +55314,7 @@
         <v>44909</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55387,7 +55387,7 @@
         <v>44698</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55460,7 +55460,7 @@
         <v>45331</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>45331</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55606,7 +55606,7 @@
         <v>45331</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55679,7 +55679,7 @@
         <v>45155</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55752,7 +55752,7 @@
         <v>44509</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55825,7 +55825,7 @@
         <v>45176</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55898,7 +55898,7 @@
         <v>45359</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -55971,7 +55971,7 @@
         <v>45036</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56044,7 +56044,7 @@
         <v>46147</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56117,7 +56117,7 @@
         <v>45384</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56190,7 +56190,7 @@
         <v>45447</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56263,7 +56263,7 @@
         <v>44818</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56336,7 +56336,7 @@
         <v>44930</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56409,7 +56409,7 @@
         <v>45978</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>44631</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>44900</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56628,7 +56628,7 @@
         <v>45474</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>44904</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>45261</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56847,7 +56847,7 @@
         <v>44967</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56920,7 +56920,7 @@
         <v>44967</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>44518</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45607</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57144,7 +57144,7 @@
         <v>45547</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>45086</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>45674</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57363,7 +57363,7 @@
         <v>45005</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57436,7 +57436,7 @@
         <v>45005</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57509,7 +57509,7 @@
         <v>45252</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57582,7 +57582,7 @@
         <v>45701</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57655,7 +57655,7 @@
         <v>45547</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57728,7 +57728,7 @@
         <v>45106</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57801,7 +57801,7 @@
         <v>44965</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57874,7 +57874,7 @@
         <v>44964</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57947,7 +57947,7 @@
         <v>44712</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58020,7 +58020,7 @@
         <v>45051</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58093,7 +58093,7 @@
         <v>44599</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58166,7 +58166,7 @@
         <v>45033</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58239,7 +58239,7 @@
         <v>45129</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58312,7 +58312,7 @@
         <v>44895</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58385,7 +58385,7 @@
         <v>44916</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>44972</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58531,7 +58531,7 @@
         <v>45601</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58604,7 +58604,7 @@
         <v>45680</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58677,7 +58677,7 @@
         <v>45139</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>45117</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>45117</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58896,7 +58896,7 @@
         <v>45082</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -58969,7 +58969,7 @@
         <v>45646</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59042,7 +59042,7 @@
         <v>44888</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59115,7 +59115,7 @@
         <v>45377</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59188,7 +59188,7 @@
         <v>45215</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59261,7 +59261,7 @@
         <v>45394</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59334,7 +59334,7 @@
         <v>45035</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59407,7 +59407,7 @@
         <v>45401</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59480,7 +59480,7 @@
         <v>44984</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59553,7 +59553,7 @@
         <v>45688</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59626,7 +59626,7 @@
         <v>45279</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59699,7 +59699,7 @@
         <v>45331</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59772,7 +59772,7 @@
         <v>45771</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59845,7 +59845,7 @@
         <v>45240</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59918,7 +59918,7 @@
         <v>44949</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -59991,7 +59991,7 @@
         <v>44971</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60064,7 +60064,7 @@
         <v>45601</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60137,7 +60137,7 @@
         <v>45574</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60210,7 +60210,7 @@
         <v>45356</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60288,7 +60288,7 @@
         <v>45755</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60361,7 +60361,7 @@
         <v>45727</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60434,7 +60434,7 @@
         <v>44935</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60507,7 +60507,7 @@
         <v>45034</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60580,7 +60580,7 @@
         <v>45002</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60653,7 +60653,7 @@
         <v>45124</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60726,7 +60726,7 @@
         <v>44960</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60799,7 +60799,7 @@
         <v>45553</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>44634</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60945,7 +60945,7 @@
         <v>45394</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61018,7 +61018,7 @@
         <v>45439</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61091,7 +61091,7 @@
         <v>45691</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61169,7 +61169,7 @@
         <v>45559</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61242,7 +61242,7 @@
         <v>45637</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61320,7 +61320,7 @@
         <v>45637</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61398,7 +61398,7 @@
         <v>45615</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61471,7 +61471,7 @@
         <v>45540</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61544,7 +61544,7 @@
         <v>45386</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61617,7 +61617,7 @@
         <v>45194</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61690,7 +61690,7 @@
         <v>44950</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61763,7 +61763,7 @@
         <v>45327</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61841,7 +61841,7 @@
         <v>45432</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61914,7 +61914,7 @@
         <v>45434</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -61987,7 +61987,7 @@
         <v>45408</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62060,7 +62060,7 @@
         <v>45349</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62133,7 +62133,7 @@
         <v>45274</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62206,7 +62206,7 @@
         <v>45670</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62279,7 +62279,7 @@
         <v>45562</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62352,7 +62352,7 @@
         <v>45419</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62425,7 +62425,7 @@
         <v>45519</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62498,7 +62498,7 @@
         <v>45574</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62571,7 +62571,7 @@
         <v>45089</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62644,7 +62644,7 @@
         <v>45602</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62717,7 +62717,7 @@
         <v>45615</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62790,7 +62790,7 @@
         <v>45782</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62863,7 +62863,7 @@
         <v>45784</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -62936,7 +62936,7 @@
         <v>45553</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63009,7 +63009,7 @@
         <v>45784</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63082,7 +63082,7 @@
         <v>45594</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63155,7 +63155,7 @@
         <v>45252</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63228,7 +63228,7 @@
         <v>45590</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63301,7 +63301,7 @@
         <v>45546</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63374,7 +63374,7 @@
         <v>45679</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63447,7 +63447,7 @@
         <v>45709</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63520,7 +63520,7 @@
         <v>45176</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63593,7 +63593,7 @@
         <v>45670</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63666,7 +63666,7 @@
         <v>45679</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63739,7 +63739,7 @@
         <v>44783</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63812,7 +63812,7 @@
         <v>45568</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63885,7 +63885,7 @@
         <v>45562</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -63958,7 +63958,7 @@
         <v>45511</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64031,7 +64031,7 @@
         <v>45636</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64109,7 +64109,7 @@
         <v>45597</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64182,7 +64182,7 @@
         <v>45524</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64255,7 +64255,7 @@
         <v>45576</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64328,7 +64328,7 @@
         <v>45565</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64401,7 +64401,7 @@
         <v>44783</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64474,7 +64474,7 @@
         <v>45230</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64547,7 +64547,7 @@
         <v>45266</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45789</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64698,7 +64698,7 @@
         <v>45712</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64771,7 +64771,7 @@
         <v>45345</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64844,7 +64844,7 @@
         <v>45637</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -64922,7 +64922,7 @@
         <v>45345</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -64995,7 +64995,7 @@
         <v>44672</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65068,7 +65068,7 @@
         <v>44722</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65141,7 +65141,7 @@
         <v>45387</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65214,7 +65214,7 @@
         <v>45387</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65287,7 +65287,7 @@
         <v>45456</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65360,7 +65360,7 @@
         <v>45602</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65433,7 +65433,7 @@
         <v>44894</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65506,7 +65506,7 @@
         <v>45443</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65579,7 +65579,7 @@
         <v>44888</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65652,7 +65652,7 @@
         <v>44900</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65725,7 +65725,7 @@
         <v>45359</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65798,7 +65798,7 @@
         <v>45359</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65871,7 +65871,7 @@
         <v>45387</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -65944,7 +65944,7 @@
         <v>45128</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66017,7 +66017,7 @@
         <v>45387</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66090,7 +66090,7 @@
         <v>45362</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66163,7 +66163,7 @@
         <v>45534</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66236,7 +66236,7 @@
         <v>44901</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66309,7 +66309,7 @@
         <v>44792</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66387,7 +66387,7 @@
         <v>45362</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66460,7 +66460,7 @@
         <v>45330</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66533,7 +66533,7 @@
         <v>44883</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66606,7 +66606,7 @@
         <v>45330</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66679,7 +66679,7 @@
         <v>44928</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66752,7 +66752,7 @@
         <v>45477</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66825,7 +66825,7 @@
         <v>44971</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66898,7 +66898,7 @@
         <v>44900</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -66971,7 +66971,7 @@
         <v>44971</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67044,7 +67044,7 @@
         <v>45230</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -67117,7 +67117,7 @@
         <v>45730</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -67190,7 +67190,7 @@
         <v>45665</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -67263,7 +67263,7 @@
         <v>45727</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -67336,7 +67336,7 @@
         <v>45665</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -67409,7 +67409,7 @@
         <v>45807</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -67482,7 +67482,7 @@
         <v>45807</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -67555,7 +67555,7 @@
         <v>46038</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -67628,7 +67628,7 @@
         <v>46042</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -67701,7 +67701,7 @@
         <v>46042</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -67774,7 +67774,7 @@
         <v>46042</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -67847,7 +67847,7 @@
         <v>46042</v>
       </c>
       <c r="E896" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
@@ -67920,7 +67920,7 @@
         <v>46045</v>
       </c>
       <c r="E897" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
@@ -67993,7 +67993,7 @@
         <v>46132</v>
       </c>
       <c r="E898" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
@@ -68066,7 +68066,7 @@
         <v>46181</v>
       </c>
       <c r="E899" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -68139,7 +68139,7 @@
         <v>46188</v>
       </c>
       <c r="E900" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -68212,7 +68212,7 @@
         <v>46213</v>
       </c>
       <c r="E901" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44977</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44740</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>44992</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45565</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46050</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45810</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>44872</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>45387</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>44599</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>44578</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>44984</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45103</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45646</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45580</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46086</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>44729</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45322</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>45406</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45546</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>46289</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>46293</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>45461</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45341</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44992</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>45387</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45330</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>45467</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45153</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45555</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45890</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>46056</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>44557</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44732</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44620</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44620</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44841</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44813</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44508</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44875</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44539</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44755</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44865</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44533</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44819</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44570</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44641</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44690</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44865</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44791</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44644</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44603</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44627</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44804</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44789</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44508</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44546</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44722</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44867</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44511</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44879</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44791</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44875</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>44532</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44879</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44494</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44489</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44529</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44631</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>44648</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44608</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44620</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44620</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44481</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>44636</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44519</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44791</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44748</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>44888</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44820</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44494</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44474</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44509</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44522</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44722</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44631</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44680</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44523</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44749</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44711</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44753</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44540</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44676</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44620</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44540</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44875</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44698</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44685</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44641</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44523</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>44712</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44596</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45075</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45395</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45775</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45477</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44728</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45147</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45615</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45362</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45082</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45631</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44967</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44586</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>44631</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45617</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45399</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45310</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45107</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45635</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>45377</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45086</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45574</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44676</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44939</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44991</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45637</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45110</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45089</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45091</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45117</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45117</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45033</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45188</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45303</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45107</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45511</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45636</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44545</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45345</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45252</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45594</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45345</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44971</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45562</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>44540</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45590</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45597</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>45637</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45576</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45565</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45524</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>44967</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45701</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45019</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45306</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44473</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45344</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45359</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45180</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45670</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45553</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45887</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45155</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45240</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>46007</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45726</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45608</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45466</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45272</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44928</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44529</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45447</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45247</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>44930</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45155</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45155</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45671</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>44570</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>44558</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>46031</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>45164</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45164</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44509</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45896</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45107</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44490</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>46031</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44928</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45071</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>45793</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45793</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>45646</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>44804</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>46036</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44804</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45904</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>44481</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45244</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45905</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>46038</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46038</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45246</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>46038</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45792</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45789</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45908</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45167</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44683</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>44522</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>44749</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>46044</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46044</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45701</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>46048</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45477</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45533</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45692</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45478</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45684</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45637</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45194</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45727</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45033</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45580</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45279</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45923</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45610</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45362</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45923</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44818</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45548</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45366</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44971</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45461</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45014</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44900</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45455</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>46063</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45323</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46063</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>46063</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>44950</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45475</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45933</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45710</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44937</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45181</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44617</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45938</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45574</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45173</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45274</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45811</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44753</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45394</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45029</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45702</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45327</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46078</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45950</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>44483</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45394</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45176</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>46083</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46083</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>46083</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45097</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45953</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44883</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>46083</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45152</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>46086</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>44984</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45034</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>46090</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>44938</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44881</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45964</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44951</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45036</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>44545</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45203</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44691</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45154</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>44993</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45107</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>46098</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45972</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45247</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46104</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>46101</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45049</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45709</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46104</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45349</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45170</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44481</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>46101</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>44945</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>44949</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>46106</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45979</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>46108</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>46108</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>46108</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45793</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>46108</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45982</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45238</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45036</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45820</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45462</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45103</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46120</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>46119</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45722</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45210</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45183</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45183</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45250</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45993</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45474</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>46120</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>44964</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45260</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>46105</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>46000</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>46000</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>46000</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46133</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45831</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>46132</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>44631</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45831</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>46132</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44936</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>44936</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45832</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45727</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44609</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44852</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45467</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45467</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45467</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45782</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>46134</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45902</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45992</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45596</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45821</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45873</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45082</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45082</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45755</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>46003</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45838</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45839</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45434</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45841</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45841</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45926</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45063</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>44634</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45035</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45474</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>46031</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45897</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45677</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45553</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45445</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45890</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45903</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45841</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45553</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45897</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45742</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45834</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45342</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45751</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44991</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45908</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44904</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>45062</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>45933</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>44964</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45755</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45012</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45162</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>45412</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44909</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44928</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45211</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>46035</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>44965</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>45884</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>44790</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45981</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>45803</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>46136</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45264</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44888</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45093</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45299</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45992</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>44895</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>46010</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>46010</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45107</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45924</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45711</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45069</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45574</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44935</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45631</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45002</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45408</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45278</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45229</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45191</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45684</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45090</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45547</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>44518</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45758</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45264</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45264</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45106</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45904</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45618</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45644</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45407</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45539</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44967</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44967</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44930</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45873</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45873</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45097</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45873</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45331</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>44950</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>44599</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>46148</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45439</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>44988</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>45688</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45432</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45727</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>46148</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>46149</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45412</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>44756</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>44953</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>44599</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45002</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>45700</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>45533</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>44993</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45735</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>45735</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45568</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>46043</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45325</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45902</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46154</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>44930</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>45434</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45117</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45117</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>46160</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>45395</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45874</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45173</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45090</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45082</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45201</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45574</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>45552</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>46162</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>44657</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45629</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45062</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>46162</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45077</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45877</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44769</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>46167</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45600</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>46167</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45331</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46167</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46167</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>44916</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45002</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45002</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45439</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>46168</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46168</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>46168</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45881</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45881</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>44995</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45117</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>45129</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45547</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>46171</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45121</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42991,7 +42991,7 @@
         <v>45574</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45629</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>44930</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45635</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>46175</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>44930</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>46175</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45005</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45005</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>46176</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>44728</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>44489</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45267</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45330</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>45329</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>46177</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>44550</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>46182</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45261</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>44495</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>46182</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>46182</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>46175</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>46181</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45429</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>44545</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45691</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45469</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45106</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45261</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>46184</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>46135</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46146</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>46184</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>46184</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>46188</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44705</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45609</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>46190</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>44831</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>44831</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>44960</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>45356</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>46189</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>45197</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>45007</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>45408</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>44627</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45601</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>46198</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>46197</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45546</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45307</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>46197</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45540</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45540</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45300</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46199</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45418</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45426</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>44939</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>44895</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>44916</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>44655</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46204</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>46204</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>46204</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>46204</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>44936</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44936</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45160</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>46203</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>46204</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45401</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>44748</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>45139</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48584,7 +48584,7 @@
         <v>44820</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>46205</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48730,7 +48730,7 @@
         <v>46206</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46206</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45078</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>45078</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>46206</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45106</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>45215</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45109</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>44673</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>44945</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>44728</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45007</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>46212</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>44907</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>45684</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>46213</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>46213</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>46213</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>46189</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>46260</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>45063</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45644</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45302</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>46260</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>46260</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>44820</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50648,7 +50648,7 @@
         <v>46045</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45215</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45245</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>46262</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>44963</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45155</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51091,7 +51091,7 @@
         <v>46209</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>46262</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>45085</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>45439</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>46266</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45034</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45394</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>44624</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>44928</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45267</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45264</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>46195</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>46195</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46195</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45314</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>46191</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>44875</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>44505</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>45432</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45614</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>44620</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52639,7 +52639,7 @@
         <v>45261</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>46120</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>45384</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45436</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>46274</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45394</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>46279</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53155,7 +53155,7 @@
         <v>44911</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53228,7 +53228,7 @@
         <v>45113</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45099</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>45155</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45547</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45579</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         <v>45568</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45772</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>44838</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>45674</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>45637</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53963,7 +53963,7 @@
         <v>45637</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>44700</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54114,7 +54114,7 @@
         <v>45424</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54187,7 +54187,7 @@
         <v>45240</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>44524</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         <v>45226</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54406,7 +54406,7 @@
         <v>45314</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45009</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54557,7 +54557,7 @@
         <v>45540</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54630,7 +54630,7 @@
         <v>44949</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>46287</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>45236</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54849,7 +54849,7 @@
         <v>45614</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         <v>45110</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>44994</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>46244</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>46202</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>44621</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>44903</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>44489</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45201</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45436</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55579,7 +55579,7 @@
         <v>45386</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>45439</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55725,7 +55725,7 @@
         <v>44628</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>44614</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>46147</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55944,7 +55944,7 @@
         <v>45119</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56017,7 +56017,7 @@
         <v>45152</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45680</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56163,7 +56163,7 @@
         <v>45574</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56236,7 +56236,7 @@
         <v>45215</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45547</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>44795</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>46293</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45978</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56601,7 +56601,7 @@
         <v>45449</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56674,7 +56674,7 @@
         <v>45449</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45240</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56820,7 +56820,7 @@
         <v>45240</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45166</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>44984</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         <v>45155</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57112,7 +57112,7 @@
         <v>46293</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57185,7 +57185,7 @@
         <v>46293</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57258,7 +57258,7 @@
         <v>45112</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>44960</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>44620</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57477,7 +57477,7 @@
         <v>44867</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>45188</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>45370</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57696,7 +57696,7 @@
         <v>45411</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57774,7 +57774,7 @@
         <v>45559</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45329</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57925,7 +57925,7 @@
         <v>45406</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57998,7 +57998,7 @@
         <v>45091</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58071,7 +58071,7 @@
         <v>46294</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45546</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>46251</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45264</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58368,7 +58368,7 @@
         <v>44698</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58441,7 +58441,7 @@
         <v>44627</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>44602</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58587,7 +58587,7 @@
         <v>45176</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58660,7 +58660,7 @@
         <v>44904</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58733,7 +58733,7 @@
         <v>45051</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>46120</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58879,7 +58879,7 @@
         <v>46293</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>44685</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59025,7 +59025,7 @@
         <v>44685</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>45035</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59171,7 +59171,7 @@
         <v>44949</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59244,7 +59244,7 @@
         <v>45138</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>44984</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
         <v>45062</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>44712</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>45176</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45252</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45252</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>45331</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59828,7 +59828,7 @@
         <v>45331</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45331</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59974,7 +59974,7 @@
         <v>45005</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>45117</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>44657</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60193,7 +60193,7 @@
         <v>45303</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60266,7 +60266,7 @@
         <v>44972</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60339,7 +60339,7 @@
         <v>45109</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60412,7 +60412,7 @@
         <v>44575</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60485,7 +60485,7 @@
         <v>45071</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60558,7 +60558,7 @@
         <v>45071</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60631,7 +60631,7 @@
         <v>45392</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>45183</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60777,7 +60777,7 @@
         <v>44950</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60850,7 +60850,7 @@
         <v>44988</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60923,7 +60923,7 @@
         <v>45071</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60996,7 +60996,7 @@
         <v>45096</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>44967</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61147,7 +61147,7 @@
         <v>44901</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61220,7 +61220,7 @@
         <v>44901</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>45386</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61366,7 +61366,7 @@
         <v>45082</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61439,7 +61439,7 @@
         <v>45182</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61512,7 +61512,7 @@
         <v>45674</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61585,7 +61585,7 @@
         <v>45601</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61658,7 +61658,7 @@
         <v>44998</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61731,7 +61731,7 @@
         <v>45188</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61804,7 +61804,7 @@
         <v>45371</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>45572</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>45327</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62028,7 +62028,7 @@
         <v>44620</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62106,7 +62106,7 @@
         <v>45755</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62179,7 +62179,7 @@
         <v>45607</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62252,7 +62252,7 @@
         <v>45713</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62325,7 +62325,7 @@
         <v>45124</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62398,7 +62398,7 @@
         <v>45616</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62471,7 +62471,7 @@
         <v>45275</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62544,7 +62544,7 @@
         <v>45175</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62617,7 +62617,7 @@
         <v>45338</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62690,7 +62690,7 @@
         <v>44748</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62763,7 +62763,7 @@
         <v>45646</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>45574</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>45562</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -62982,7 +62982,7 @@
         <v>45615</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63055,7 +63055,7 @@
         <v>45419</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63128,7 +63128,7 @@
         <v>45519</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63201,7 +63201,7 @@
         <v>45089</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63274,7 +63274,7 @@
         <v>45670</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>45602</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63420,7 +63420,7 @@
         <v>45553</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>45782</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63566,7 +63566,7 @@
         <v>45546</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>45784</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>45709</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63785,7 +63785,7 @@
         <v>45784</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>45176</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>44783</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -64004,7 +64004,7 @@
         <v>45266</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45712</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>45679</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>45789</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>45679</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>45230</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64447,7 +64447,7 @@
         <v>44783</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64520,7 +64520,7 @@
         <v>45568</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>45387</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>45387</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>45456</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>45602</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>44894</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -64958,7 +64958,7 @@
         <v>45443</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -65031,7 +65031,7 @@
         <v>44672</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>44888</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65177,7 +65177,7 @@
         <v>44900</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>45359</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65323,7 +65323,7 @@
         <v>45359</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65396,7 +65396,7 @@
         <v>44722</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65469,7 +65469,7 @@
         <v>45387</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65542,7 +65542,7 @@
         <v>45128</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65615,7 +65615,7 @@
         <v>45387</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65688,7 +65688,7 @@
         <v>45362</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65761,7 +65761,7 @@
         <v>45534</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65834,7 +65834,7 @@
         <v>44901</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65907,7 +65907,7 @@
         <v>44792</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -65985,7 +65985,7 @@
         <v>45362</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45330</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66131,7 +66131,7 @@
         <v>44883</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>45330</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66277,7 +66277,7 @@
         <v>44928</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66350,7 +66350,7 @@
         <v>45477</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66423,7 +66423,7 @@
         <v>44971</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66496,7 +66496,7 @@
         <v>44900</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66569,7 +66569,7 @@
         <v>44971</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66642,7 +66642,7 @@
         <v>45230</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66715,7 +66715,7 @@
         <v>45730</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66788,7 +66788,7 @@
         <v>45665</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66861,7 +66861,7 @@
         <v>45727</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66934,7 +66934,7 @@
         <v>45665</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -67007,7 +67007,7 @@
         <v>45807</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67080,7 +67080,7 @@
         <v>45807</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -67153,7 +67153,7 @@
         <v>46038</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -67226,7 +67226,7 @@
         <v>46042</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -67299,7 +67299,7 @@
         <v>46042</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -67372,7 +67372,7 @@
         <v>46042</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -67445,7 +67445,7 @@
         <v>46042</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -67518,7 +67518,7 @@
         <v>46045</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -67591,7 +67591,7 @@
         <v>46132</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -67664,7 +67664,7 @@
         <v>46181</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -67737,7 +67737,7 @@
         <v>46188</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -67810,7 +67810,7 @@
         <v>46213</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44977</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44740</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>44992</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45565</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>46050</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45810</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>44872</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>45387</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>44756</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>44599</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3028,7 +3028,7 @@
         <v>44756</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>44578</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>44984</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>45103</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>45646</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3571,7 +3571,7 @@
         <v>45580</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         <v>46086</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3781,7 +3781,7 @@
         <v>45001</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>44729</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>45322</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         <v>45406</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
         <v>45546</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>46213</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4626,7 +4626,7 @@
         <v>46289</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4731,7 +4731,7 @@
         <v>46293</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>45461</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4950,7 +4950,7 @@
         <v>45341</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>44992</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         <v>45387</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5265,7 +5265,7 @@
         <v>45330</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5370,7 +5370,7 @@
         <v>45467</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>45153</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45555</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45890</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>46056</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         <v>44557</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         <v>44732</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>44875</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>44620</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44620</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>44841</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>44813</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         <v>44508</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>44875</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>44539</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>44755</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>44713</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6852,7 +6852,7 @@
         <v>44524</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6925,7 +6925,7 @@
         <v>44813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44753</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44865</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         <v>44533</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44819</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44570</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44641</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44690</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44865</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44791</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44644</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44603</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44627</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44804</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44789</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44508</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>44546</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8531,7 +8531,7 @@
         <v>44722</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8604,7 +8604,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>44867</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         <v>44511</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8823,7 +8823,7 @@
         <v>44839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44879</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44791</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44875</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9120,7 +9120,7 @@
         <v>44532</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44879</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9266,7 +9266,7 @@
         <v>44595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9339,7 +9339,7 @@
         <v>44494</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9412,7 +9412,7 @@
         <v>44489</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9485,7 +9485,7 @@
         <v>44529</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44631</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>44648</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44608</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44620</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44620</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44481</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>44636</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>44519</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44791</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>44748</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10371,7 +10371,7 @@
         <v>44888</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44820</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
         <v>44494</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>44474</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10663,7 +10663,7 @@
         <v>44509</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
         <v>44522</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>44533</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10882,7 +10882,7 @@
         <v>44722</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
         <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11028,7 +11028,7 @@
         <v>44631</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11101,7 +11101,7 @@
         <v>44680</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>44523</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>44749</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44711</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>44753</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44540</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>44676</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11612,7 +11612,7 @@
         <v>44620</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>44540</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11758,7 +11758,7 @@
         <v>44875</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11831,7 +11831,7 @@
         <v>44698</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44685</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>44641</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44523</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>44712</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44596</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45075</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12639,7 +12639,7 @@
         <v>45395</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12712,7 +12712,7 @@
         <v>45775</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12785,7 +12785,7 @@
         <v>45477</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12858,7 +12858,7 @@
         <v>44728</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>45147</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>45615</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         <v>45362</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45082</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13223,7 +13223,7 @@
         <v>45631</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13296,7 +13296,7 @@
         <v>44895</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13369,7 +13369,7 @@
         <v>44967</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13447,7 +13447,7 @@
         <v>44586</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13520,7 +13520,7 @@
         <v>44631</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13593,7 +13593,7 @@
         <v>44965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13666,7 +13666,7 @@
         <v>45617</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13739,7 +13739,7 @@
         <v>45399</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13812,7 +13812,7 @@
         <v>45310</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13885,7 +13885,7 @@
         <v>45107</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13958,7 +13958,7 @@
         <v>45635</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14036,7 +14036,7 @@
         <v>45377</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45086</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45574</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14255,7 +14255,7 @@
         <v>44676</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14328,7 +14328,7 @@
         <v>44939</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14401,7 +14401,7 @@
         <v>44991</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14474,7 +14474,7 @@
         <v>45034</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14547,7 +14547,7 @@
         <v>45637</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45110</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45089</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45091</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>45117</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>45117</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>45033</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45188</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45303</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45107</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45511</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>45636</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15433,7 +15433,7 @@
         <v>44545</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15506,7 +15506,7 @@
         <v>45345</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45252</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>45594</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15725,7 +15725,7 @@
         <v>45345</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>44971</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>45562</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>44540</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45590</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>45597</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16163,7 +16163,7 @@
         <v>45637</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16241,7 +16241,7 @@
         <v>45576</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16314,7 +16314,7 @@
         <v>45565</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>45524</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16460,7 +16460,7 @@
         <v>44967</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45701</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>45019</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44904</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>45306</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>44473</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>45344</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>45359</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>45180</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17117,7 +17117,7 @@
         <v>45670</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45553</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>45887</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17336,7 +17336,7 @@
         <v>45155</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17409,7 +17409,7 @@
         <v>45240</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>46007</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>45726</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45608</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>45466</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>45272</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17852,7 +17852,7 @@
         <v>44928</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>44529</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
         <v>45447</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18071,7 +18071,7 @@
         <v>45247</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18144,7 +18144,7 @@
         <v>44930</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
         <v>45155</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18290,7 +18290,7 @@
         <v>45155</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18363,7 +18363,7 @@
         <v>45671</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>44570</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18509,7 +18509,7 @@
         <v>44558</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18582,7 +18582,7 @@
         <v>46031</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18655,7 +18655,7 @@
         <v>45164</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18728,7 +18728,7 @@
         <v>45164</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18801,7 +18801,7 @@
         <v>44509</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45896</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45107</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44490</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>46031</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         <v>44928</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45071</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>45793</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45793</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>45443</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>45646</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>44804</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>46036</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>44804</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45904</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19911,7 +19911,7 @@
         <v>44481</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
         <v>45244</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20057,7 +20057,7 @@
         <v>45905</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>46038</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>46038</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20276,7 +20276,7 @@
         <v>45246</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>46038</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45792</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45789</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>45908</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>45167</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20714,7 +20714,7 @@
         <v>44683</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20787,7 +20787,7 @@
         <v>44522</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>44749</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
         <v>46044</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46044</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21094,7 +21094,7 @@
         <v>45701</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21167,7 +21167,7 @@
         <v>46048</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45477</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21313,7 +21313,7 @@
         <v>45533</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45692</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45478</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21532,7 +21532,7 @@
         <v>45684</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21605,7 +21605,7 @@
         <v>45637</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45194</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45727</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45033</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45244</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45580</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45279</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>45923</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45610</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45362</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45923</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44818</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45548</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>45366</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44971</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45461</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>45014</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>44900</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45455</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>46063</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45323</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46063</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>46063</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>44950</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45475</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45933</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>45710</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>44937</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45181</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>44617</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45938</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45574</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45173</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>45274</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45811</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24165,7 +24165,7 @@
         <v>44753</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45394</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24311,7 +24311,7 @@
         <v>45029</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45702</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>45327</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46078</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45950</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>44483</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>45085</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45394</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45176</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>46083</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46083</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>46083</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45097</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45953</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>44883</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>46083</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45152</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>46086</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>44984</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>45034</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>46090</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>44938</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44881</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45964</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>44951</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45036</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>44545</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>45203</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44691</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45154</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>44993</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>45107</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>46098</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45972</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45247</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46104</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>46101</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45049</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>45709</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>46104</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45349</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27319,7 +27319,7 @@
         <v>45170</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27392,7 +27392,7 @@
         <v>44481</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>46101</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27538,7 +27538,7 @@
         <v>44945</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>44949</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>46106</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27762,7 +27762,7 @@
         <v>45979</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>46108</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27908,7 +27908,7 @@
         <v>46108</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27981,7 +27981,7 @@
         <v>46108</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28054,7 +28054,7 @@
         <v>45980</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>45793</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>46108</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45982</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>45238</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45036</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45820</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45462</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>45103</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46120</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>46119</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45722</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45210</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45183</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45183</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>45250</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29222,7 +29222,7 @@
         <v>45993</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29295,7 +29295,7 @@
         <v>45474</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29368,7 +29368,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29441,7 +29441,7 @@
         <v>46120</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29514,7 +29514,7 @@
         <v>44964</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45260</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29660,7 +29660,7 @@
         <v>46105</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29733,7 +29733,7 @@
         <v>46000</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29806,7 +29806,7 @@
         <v>46000</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>46000</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29952,7 +29952,7 @@
         <v>46133</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45831</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>46132</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>44631</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45831</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>46132</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>44936</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30463,7 +30463,7 @@
         <v>44936</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30536,7 +30536,7 @@
         <v>45832</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30609,7 +30609,7 @@
         <v>45727</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>44609</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30760,7 +30760,7 @@
         <v>44852</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30833,7 +30833,7 @@
         <v>45467</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45467</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45467</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>45782</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31125,7 +31125,7 @@
         <v>46134</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31198,7 +31198,7 @@
         <v>45902</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31271,7 +31271,7 @@
         <v>45992</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31344,7 +31344,7 @@
         <v>45596</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45821</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45873</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31563,7 +31563,7 @@
         <v>45082</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31636,7 +31636,7 @@
         <v>45082</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31709,7 +31709,7 @@
         <v>45755</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>46003</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45838</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>45839</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>45434</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45841</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45841</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>45926</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>45063</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>44634</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>45035</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45474</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>46031</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>45897</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45677</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32809,7 +32809,7 @@
         <v>45553</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45445</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45890</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>45903</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33106,7 +33106,7 @@
         <v>45841</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33179,7 +33179,7 @@
         <v>45553</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33257,7 +33257,7 @@
         <v>45897</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33330,7 +33330,7 @@
         <v>45742</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45834</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33476,7 +33476,7 @@
         <v>45342</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33549,7 +33549,7 @@
         <v>45751</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>44991</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>45908</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>44904</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33841,7 +33841,7 @@
         <v>45062</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33914,7 +33914,7 @@
         <v>45933</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -33987,7 +33987,7 @@
         <v>44964</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34060,7 +34060,7 @@
         <v>45755</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34133,7 +34133,7 @@
         <v>45012</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34206,7 +34206,7 @@
         <v>45162</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34279,7 +34279,7 @@
         <v>45412</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>44909</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34425,7 +34425,7 @@
         <v>44928</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45211</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34571,7 +34571,7 @@
         <v>46035</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34644,7 +34644,7 @@
         <v>44965</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34722,7 +34722,7 @@
         <v>45884</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34795,7 +34795,7 @@
         <v>44790</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45981</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>45803</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35014,7 +35014,7 @@
         <v>46136</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45264</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35160,7 +35160,7 @@
         <v>44888</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>45093</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>45299</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45992</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>44895</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>46010</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35598,7 +35598,7 @@
         <v>46010</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>45107</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35744,7 +35744,7 @@
         <v>45924</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35817,7 +35817,7 @@
         <v>45711</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>45069</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45574</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>44935</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45631</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45002</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45408</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45278</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45229</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45191</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>45684</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36620,7 +36620,7 @@
         <v>45090</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36693,7 +36693,7 @@
         <v>45547</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36766,7 +36766,7 @@
         <v>44518</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45758</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45264</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45264</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45106</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45904</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>45618</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45644</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45407</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45539</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>44967</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>44967</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37652,7 +37652,7 @@
         <v>44930</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37725,7 +37725,7 @@
         <v>45873</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37798,7 +37798,7 @@
         <v>45873</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37871,7 +37871,7 @@
         <v>45097</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45873</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38017,7 +38017,7 @@
         <v>45331</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>44950</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>44599</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>46148</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45439</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>44988</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>45688</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45432</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>45727</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>46148</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>46149</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45412</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>44756</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>44953</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>44599</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39112,7 +39112,7 @@
         <v>45002</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39185,7 +39185,7 @@
         <v>45700</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>45533</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39331,7 +39331,7 @@
         <v>44993</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39404,7 +39404,7 @@
         <v>45735</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39477,7 +39477,7 @@
         <v>45735</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45568</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39623,7 +39623,7 @@
         <v>46043</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45325</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>45902</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46154</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>44930</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>45434</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45117</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45117</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>46160</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>45395</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>45874</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45173</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45090</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45082</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>45201</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>45574</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>45552</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>46162</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>44657</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45629</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45062</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>46162</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>45077</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45877</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>44769</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>46167</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>45600</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>46167</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45331</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>46167</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41818,7 +41818,7 @@
         <v>46167</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41891,7 +41891,7 @@
         <v>44916</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45002</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42037,7 +42037,7 @@
         <v>45002</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42110,7 +42110,7 @@
         <v>45439</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42183,7 +42183,7 @@
         <v>46168</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42256,7 +42256,7 @@
         <v>46168</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42329,7 +42329,7 @@
         <v>46168</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42402,7 +42402,7 @@
         <v>45881</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45881</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42548,7 +42548,7 @@
         <v>44995</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>45117</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>45129</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45547</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42840,7 +42840,7 @@
         <v>46171</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42918,7 +42918,7 @@
         <v>45121</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -42991,7 +42991,7 @@
         <v>45574</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43064,7 +43064,7 @@
         <v>45629</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>44930</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>45635</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>46175</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>44930</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>46175</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45005</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45005</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>46176</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>44728</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>44489</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45267</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>45330</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44018,7 +44018,7 @@
         <v>45329</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44096,7 +44096,7 @@
         <v>46177</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44169,7 +44169,7 @@
         <v>44550</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>46182</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44315,7 +44315,7 @@
         <v>45261</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44388,7 +44388,7 @@
         <v>44495</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>46182</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44534,7 +44534,7 @@
         <v>46182</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>46175</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44680,7 +44680,7 @@
         <v>46181</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44753,7 +44753,7 @@
         <v>45429</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44826,7 +44826,7 @@
         <v>44545</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45691</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>45469</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>45106</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45123,7 +45123,7 @@
         <v>45261</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45196,7 +45196,7 @@
         <v>46184</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>46135</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45342,7 +45342,7 @@
         <v>46146</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>46184</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45488,7 +45488,7 @@
         <v>46184</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45561,7 +45561,7 @@
         <v>46188</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45634,7 +45634,7 @@
         <v>44705</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>45609</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45780,7 +45780,7 @@
         <v>46190</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45853,7 +45853,7 @@
         <v>44831</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>44831</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -45999,7 +45999,7 @@
         <v>44960</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46072,7 +46072,7 @@
         <v>45356</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46150,7 +46150,7 @@
         <v>46189</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46223,7 +46223,7 @@
         <v>45197</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>45007</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46369,7 +46369,7 @@
         <v>45408</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>44627</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>45601</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>46198</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46661,7 +46661,7 @@
         <v>46197</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46734,7 +46734,7 @@
         <v>45546</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46807,7 +46807,7 @@
         <v>45307</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46885,7 +46885,7 @@
         <v>46197</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -46958,7 +46958,7 @@
         <v>45540</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>45540</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45300</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>46199</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45418</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>45426</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>44939</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47474,7 +47474,7 @@
         <v>44895</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>44916</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47620,7 +47620,7 @@
         <v>44655</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46204</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>46204</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>46204</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>46204</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>44936</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>44936</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45160</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>46203</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>46204</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>45401</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>44748</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>45139</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48584,7 +48584,7 @@
         <v>44820</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>46205</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48730,7 +48730,7 @@
         <v>46206</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>46206</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48896,7 +48896,7 @@
         <v>45078</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>45078</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49042,7 +49042,7 @@
         <v>46206</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49115,7 +49115,7 @@
         <v>45106</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49188,7 +49188,7 @@
         <v>45215</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49261,7 +49261,7 @@
         <v>45109</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49334,7 +49334,7 @@
         <v>44673</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49407,7 +49407,7 @@
         <v>44945</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49480,7 +49480,7 @@
         <v>44728</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45007</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>46212</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>44907</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>45684</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>46213</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49918,7 +49918,7 @@
         <v>46213</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -49991,7 +49991,7 @@
         <v>46213</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50064,7 +50064,7 @@
         <v>46189</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50137,7 +50137,7 @@
         <v>46260</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50210,7 +50210,7 @@
         <v>45063</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50283,7 +50283,7 @@
         <v>45644</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50356,7 +50356,7 @@
         <v>45302</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50429,7 +50429,7 @@
         <v>46260</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50502,7 +50502,7 @@
         <v>46260</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50575,7 +50575,7 @@
         <v>44820</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50648,7 +50648,7 @@
         <v>46045</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50726,7 +50726,7 @@
         <v>45215</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50799,7 +50799,7 @@
         <v>45245</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50872,7 +50872,7 @@
         <v>46262</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50945,7 +50945,7 @@
         <v>44963</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51018,7 +51018,7 @@
         <v>45155</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51091,7 +51091,7 @@
         <v>46209</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>46262</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>45085</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51315,7 +51315,7 @@
         <v>45439</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>46266</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45034</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51534,7 +51534,7 @@
         <v>45394</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51607,7 +51607,7 @@
         <v>44624</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51680,7 +51680,7 @@
         <v>44928</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>45267</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>45264</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51899,7 +51899,7 @@
         <v>46195</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51972,7 +51972,7 @@
         <v>46195</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52045,7 +52045,7 @@
         <v>46195</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52118,7 +52118,7 @@
         <v>45314</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52191,7 +52191,7 @@
         <v>46191</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52264,7 +52264,7 @@
         <v>44875</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52337,7 +52337,7 @@
         <v>44505</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52410,7 +52410,7 @@
         <v>45432</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52488,7 +52488,7 @@
         <v>45614</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52561,7 +52561,7 @@
         <v>44620</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52639,7 +52639,7 @@
         <v>45261</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52712,7 +52712,7 @@
         <v>46120</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52785,7 +52785,7 @@
         <v>45384</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45436</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52931,7 +52931,7 @@
         <v>46274</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45394</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53082,7 +53082,7 @@
         <v>46279</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53155,7 +53155,7 @@
         <v>44911</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53228,7 +53228,7 @@
         <v>45113</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53301,7 +53301,7 @@
         <v>45099</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53374,7 +53374,7 @@
         <v>45155</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53447,7 +53447,7 @@
         <v>45547</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53520,7 +53520,7 @@
         <v>45579</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53593,7 +53593,7 @@
         <v>45568</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53666,7 +53666,7 @@
         <v>45772</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53739,7 +53739,7 @@
         <v>44838</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>45674</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>45637</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53963,7 +53963,7 @@
         <v>45637</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54041,7 +54041,7 @@
         <v>44700</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54114,7 +54114,7 @@
         <v>45424</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54187,7 +54187,7 @@
         <v>45240</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54260,7 +54260,7 @@
         <v>44524</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54333,7 +54333,7 @@
         <v>45226</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54406,7 +54406,7 @@
         <v>45314</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54479,7 +54479,7 @@
         <v>45009</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54557,7 +54557,7 @@
         <v>45540</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54630,7 +54630,7 @@
         <v>44949</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>46287</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>45236</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54849,7 +54849,7 @@
         <v>45614</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54922,7 +54922,7 @@
         <v>45110</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -54995,7 +54995,7 @@
         <v>44994</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55068,7 +55068,7 @@
         <v>46244</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55141,7 +55141,7 @@
         <v>46202</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55214,7 +55214,7 @@
         <v>44621</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55287,7 +55287,7 @@
         <v>44903</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55360,7 +55360,7 @@
         <v>44489</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55433,7 +55433,7 @@
         <v>45201</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55506,7 +55506,7 @@
         <v>45436</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55579,7 +55579,7 @@
         <v>45386</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55652,7 +55652,7 @@
         <v>45439</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55725,7 +55725,7 @@
         <v>44628</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55798,7 +55798,7 @@
         <v>44614</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55871,7 +55871,7 @@
         <v>46147</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55944,7 +55944,7 @@
         <v>45119</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56017,7 +56017,7 @@
         <v>45152</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56090,7 +56090,7 @@
         <v>45680</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56163,7 +56163,7 @@
         <v>45574</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56236,7 +56236,7 @@
         <v>45215</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56309,7 +56309,7 @@
         <v>45547</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56382,7 +56382,7 @@
         <v>44795</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>46293</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56528,7 +56528,7 @@
         <v>45978</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56601,7 +56601,7 @@
         <v>45449</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56674,7 +56674,7 @@
         <v>45449</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56747,7 +56747,7 @@
         <v>45240</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56820,7 +56820,7 @@
         <v>45240</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56893,7 +56893,7 @@
         <v>45166</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>44984</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         <v>45155</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57112,7 +57112,7 @@
         <v>46293</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57185,7 +57185,7 @@
         <v>46293</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57258,7 +57258,7 @@
         <v>45112</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57331,7 +57331,7 @@
         <v>44960</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57404,7 +57404,7 @@
         <v>44620</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57477,7 +57477,7 @@
         <v>44867</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57550,7 +57550,7 @@
         <v>45188</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57623,7 +57623,7 @@
         <v>45370</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57696,7 +57696,7 @@
         <v>45411</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57774,7 +57774,7 @@
         <v>45559</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57847,7 +57847,7 @@
         <v>45329</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57925,7 +57925,7 @@
         <v>45406</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -57998,7 +57998,7 @@
         <v>45091</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58071,7 +58071,7 @@
         <v>46294</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58144,7 +58144,7 @@
         <v>45546</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58217,7 +58217,7 @@
         <v>46251</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>45264</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58368,7 +58368,7 @@
         <v>44698</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58441,7 +58441,7 @@
         <v>44627</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>44602</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58587,7 +58587,7 @@
         <v>45176</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58660,7 +58660,7 @@
         <v>44904</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58733,7 +58733,7 @@
         <v>45051</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>46120</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58879,7 +58879,7 @@
         <v>46293</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58952,7 +58952,7 @@
         <v>44685</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59025,7 +59025,7 @@
         <v>44685</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>45035</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59171,7 +59171,7 @@
         <v>44949</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59244,7 +59244,7 @@
         <v>45138</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59317,7 +59317,7 @@
         <v>44984</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59390,7 +59390,7 @@
         <v>45062</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59463,7 +59463,7 @@
         <v>44712</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>45176</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59609,7 +59609,7 @@
         <v>45252</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59682,7 +59682,7 @@
         <v>45252</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59755,7 +59755,7 @@
         <v>45331</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59828,7 +59828,7 @@
         <v>45331</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59901,7 +59901,7 @@
         <v>45331</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59974,7 +59974,7 @@
         <v>45005</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60047,7 +60047,7 @@
         <v>45117</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60120,7 +60120,7 @@
         <v>44657</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60193,7 +60193,7 @@
         <v>45303</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60266,7 +60266,7 @@
         <v>44972</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60339,7 +60339,7 @@
         <v>45109</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60412,7 +60412,7 @@
         <v>44575</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60485,7 +60485,7 @@
         <v>45071</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60558,7 +60558,7 @@
         <v>45071</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60631,7 +60631,7 @@
         <v>45392</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60704,7 +60704,7 @@
         <v>45183</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60777,7 +60777,7 @@
         <v>44950</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60850,7 +60850,7 @@
         <v>44988</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60923,7 +60923,7 @@
         <v>45071</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -60996,7 +60996,7 @@
         <v>45096</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61069,7 +61069,7 @@
         <v>44967</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61147,7 +61147,7 @@
         <v>44901</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61220,7 +61220,7 @@
         <v>44901</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61293,7 +61293,7 @@
         <v>45386</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61366,7 +61366,7 @@
         <v>45082</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61439,7 +61439,7 @@
         <v>45182</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61512,7 +61512,7 @@
         <v>45674</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61585,7 +61585,7 @@
         <v>45601</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61658,7 +61658,7 @@
         <v>44998</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61731,7 +61731,7 @@
         <v>45188</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61804,7 +61804,7 @@
         <v>45371</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>45572</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>45327</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62028,7 +62028,7 @@
         <v>44620</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62106,7 +62106,7 @@
         <v>45755</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62179,7 +62179,7 @@
         <v>45607</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62252,7 +62252,7 @@
         <v>45713</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62325,7 +62325,7 @@
         <v>45124</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62398,7 +62398,7 @@
         <v>45616</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62471,7 +62471,7 @@
         <v>45275</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62544,7 +62544,7 @@
         <v>45175</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62617,7 +62617,7 @@
         <v>45338</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62690,7 +62690,7 @@
         <v>44748</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62763,7 +62763,7 @@
         <v>45646</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62836,7 +62836,7 @@
         <v>45574</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>45562</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -62982,7 +62982,7 @@
         <v>45615</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63055,7 +63055,7 @@
         <v>45419</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63128,7 +63128,7 @@
         <v>45519</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63201,7 +63201,7 @@
         <v>45089</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63274,7 +63274,7 @@
         <v>45670</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>45602</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63420,7 +63420,7 @@
         <v>45553</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>45782</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63566,7 +63566,7 @@
         <v>45546</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63639,7 +63639,7 @@
         <v>45784</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63712,7 +63712,7 @@
         <v>45709</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63785,7 +63785,7 @@
         <v>45784</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63858,7 +63858,7 @@
         <v>45176</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63931,7 +63931,7 @@
         <v>44783</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -64004,7 +64004,7 @@
         <v>45266</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64082,7 +64082,7 @@
         <v>45712</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64155,7 +64155,7 @@
         <v>45679</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64228,7 +64228,7 @@
         <v>45789</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64301,7 +64301,7 @@
         <v>45679</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64374,7 +64374,7 @@
         <v>45230</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64447,7 +64447,7 @@
         <v>44783</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64520,7 +64520,7 @@
         <v>45568</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64593,7 +64593,7 @@
         <v>45387</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64666,7 +64666,7 @@
         <v>45387</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64739,7 +64739,7 @@
         <v>45456</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64812,7 +64812,7 @@
         <v>45602</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64885,7 +64885,7 @@
         <v>44894</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -64958,7 +64958,7 @@
         <v>45443</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -65031,7 +65031,7 @@
         <v>44672</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65104,7 +65104,7 @@
         <v>44888</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65177,7 +65177,7 @@
         <v>44900</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65250,7 +65250,7 @@
         <v>45359</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65323,7 +65323,7 @@
         <v>45359</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65396,7 +65396,7 @@
         <v>44722</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65469,7 +65469,7 @@
         <v>45387</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65542,7 +65542,7 @@
         <v>45128</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65615,7 +65615,7 @@
         <v>45387</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65688,7 +65688,7 @@
         <v>45362</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65761,7 +65761,7 @@
         <v>45534</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65834,7 +65834,7 @@
         <v>44901</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65907,7 +65907,7 @@
         <v>44792</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -65985,7 +65985,7 @@
         <v>45362</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45330</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66131,7 +66131,7 @@
         <v>44883</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66204,7 +66204,7 @@
         <v>45330</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66277,7 +66277,7 @@
         <v>44928</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66350,7 +66350,7 @@
         <v>45477</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66423,7 +66423,7 @@
         <v>44971</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66496,7 +66496,7 @@
         <v>44900</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66569,7 +66569,7 @@
         <v>44971</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66642,7 +66642,7 @@
         <v>45230</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66715,7 +66715,7 @@
         <v>45730</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66788,7 +66788,7 @@
         <v>45665</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66861,7 +66861,7 @@
         <v>45727</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66934,7 +66934,7 @@
         <v>45665</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -67007,7 +67007,7 @@
         <v>45807</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67080,7 +67080,7 @@
         <v>45807</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -67153,7 +67153,7 @@
         <v>46038</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -67226,7 +67226,7 @@
         <v>46042</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
@@ -67299,7 +67299,7 @@
         <v>46042</v>
       </c>
       <c r="E888" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
@@ -67372,7 +67372,7 @@
         <v>46042</v>
       </c>
       <c r="E889" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
@@ -67445,7 +67445,7 @@
         <v>46042</v>
       </c>
       <c r="E890" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -67518,7 +67518,7 @@
         <v>46045</v>
       </c>
       <c r="E891" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -67591,7 +67591,7 @@
         <v>46132</v>
       </c>
       <c r="E892" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
@@ -67664,7 +67664,7 @@
         <v>46181</v>
       </c>
       <c r="E893" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
@@ -67737,7 +67737,7 @@
         <v>46188</v>
       </c>
       <c r="E894" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -67810,7 +67810,7 @@
         <v>46213</v>
       </c>
       <c r="E895" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44977</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44740</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45565</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>44992</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44872</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45387</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45810</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>46050</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44599</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44756</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44578</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45322</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44489</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45461</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>44992</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45646</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45546</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45001</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>44729</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45580</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>44984</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>45341</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>46086</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>46213</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>46289</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>46293</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46301</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45330</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>45467</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45153</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>46056</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44888</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44557</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44620</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>44732</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44813</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44508</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44539</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44755</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44713</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44524</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44489</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44813</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44753</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44865</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44533</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44819</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44570</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44494</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44641</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44692</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44690</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44865</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44610</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44644</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44603</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44804</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44508</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44722</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>44867</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44879</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44532</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44875</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44879</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44494</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44820</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44676</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44489</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44620</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44529</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44631</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44648</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44798</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44540</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44608</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44698</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44680</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44631</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44523</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>44481</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44620</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44620</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44875</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44636</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44519</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44698</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>44685</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>44791</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44748</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44711</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44641</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44494</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44753</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44540</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44509</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44888</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44522</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44533</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44722</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44875</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>44753</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44523</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44712</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45439</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45680</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45395</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>45702</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45139</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44596</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45097</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45091</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45117</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45082</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45646</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>44888</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45229</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45377</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45338</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45411</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45412</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45252</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45407</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45075</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45110</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45107</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45553</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45261</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45215</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45103</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45394</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45183</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>45035</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45401</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45362</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45173</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44481</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45300</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>44984</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45688</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>44483</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45279</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>44820</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45331</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45034</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45170</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45449</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45449</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44883</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45394</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44490</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44895</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45240</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45330</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45089</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45117</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45117</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>44949</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>44960</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45439</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>44967</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45467</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45467</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45467</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45601</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45455</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45574</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44489</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45370</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45240</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44928</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45356</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44953</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45477</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45755</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45267</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45727</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45533</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44903</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45085</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45445</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45329</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44935</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>44728</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45002</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45124</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45180</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44904</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44960</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45240</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45325</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45553</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45671</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>44489</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45154</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45436</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45152</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>44634</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>44545</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45394</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45887</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44949</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44949</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45002</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45314</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45310</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45475</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45392</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45069</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45275</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>44838</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44545</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45439</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45691</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45559</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44524</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45637</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45637</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44881</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45424</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44930</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>45896</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45615</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45436</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>45005</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>45540</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45386</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44936</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45646</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45443</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45246</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45097</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45194</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44950</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45644</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45327</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45546</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45394</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45432</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45904</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44911</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45329</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45434</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>44895</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45792</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45408</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45789</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45905</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45908</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45540</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44481</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45349</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>44964</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45274</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45362</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45670</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45562</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45419</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45519</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45574</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45089</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45602</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45615</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45166</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44907</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45539</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45782</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45546</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45784</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44599</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45553</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45784</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>44558</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45594</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45252</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44540</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45590</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44930</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44995</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45155</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>45546</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45679</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45709</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45342</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45176</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44575</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45670</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45679</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>44783</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44620</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45568</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45160</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45562</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45511</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45274</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45636</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45597</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>45524</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>45576</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45565</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>44928</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>45155</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45155</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45635</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44783</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45230</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>45540</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45923</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45007</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44971</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45923</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45631</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45789</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45712</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45345</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45637</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45012</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45345</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45014</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44676</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>44950</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>44795</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44965</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44945</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45264</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>45264</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45548</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44939</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45029</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45033</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44570</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>44550</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45107</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45240</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>44586</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45793</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>44936</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>44936</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45568</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45631</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>44617</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45793</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45152</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45155</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45155</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44620</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45614</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45439</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45078</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45933</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45637</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>45727</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44928</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45071</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45692</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44683</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45618</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45344</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45478</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>45533</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45477</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45408</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>45175</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45203</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45637</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>44928</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45684</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45082</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45727</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45191</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45162</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>44963</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45106</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45938</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45091</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>44685</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>44685</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45085</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>44993</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45182</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45107</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45077</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44627</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45811</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>44673</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>44624</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45547</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45176</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45614</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45107</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44620</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45215</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45609</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44621</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>44614</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45210</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45215</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45147</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>45034</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45138</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45713</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45090</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>44820</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45820</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45635</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45793</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45579</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45574</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45574</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45580</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>44984</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>45323</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45307</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45244</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>45574</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45007</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45245</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45608</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45211</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44657</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45827</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45684</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45831</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>44609</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>45831</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45832</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45183</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45183</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45117</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44749</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45461</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45953</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>44728</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44728</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45173</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44545</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>44655</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45226</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45119</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>45062</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44700</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45181</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45009</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44993</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>44705</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45096</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45838</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45434</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45610</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45674</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>44852</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45093</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45839</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>44998</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>45547</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44753</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>45164</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45164</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>45197</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>44951</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45841</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>45841</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45552</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45972</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45677</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45264</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45117</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45629</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44748</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45236</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45331</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45701</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45099</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45303</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45469</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45238</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45617</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45109</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45109</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>45302</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45121</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45751</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45775</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45722</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>44994</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>44804</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>44495</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>44505</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>45306</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45684</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45090</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>45062</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45314</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>44804</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45644</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41956,7 +41956,7 @@
         <v>45176</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>45078</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>45036</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45366</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44756</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42321,7 +42321,7 @@
         <v>44901</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44901</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45035</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42540,7 +42540,7 @@
         <v>45267</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>44529</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>45399</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>45873</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45873</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>44904</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>44867</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>45979</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>44930</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>44950</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45167</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>45188</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>45710</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45874</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>44831</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>44831</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43708,7 +43708,7 @@
         <v>45980</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45873</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>44522</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45082</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45877</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>44937</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45188</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>45772</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>45327</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45462</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45272</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45264</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45881</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>45881</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>44991</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>44991</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45247</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44988</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>45110</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45178,7 +45178,7 @@
         <v>45244</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45201</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44748</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>45063</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45982</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>46098</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>44691</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45303</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>46101</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>45002</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45616</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>46101</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>44930</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>46104</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45429</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45201</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>44627</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45264</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>46106</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45071</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45071</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45071</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>45574</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45260</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45386</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>44631</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45112</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45735</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45735</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>46108</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>46108</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45412</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>45466</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>46108</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>44790</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>44984</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45371</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45406</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45082</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45082</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45106</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>44916</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>45261</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45709</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48400,7 +48400,7 @@
         <v>46119</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48473,7 +48473,7 @@
         <v>44602</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45993</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>46120</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>44657</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>46000</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>46120</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>46132</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>44967</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>45572</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>44628</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>44967</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>46105</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>46132</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>46134</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>44939</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>44988</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>45568</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45782</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49792,7 +49792,7 @@
         <v>45897</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>45992</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45553</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>45803</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45188</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45897</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45924</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45062</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>45395</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>45596</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45755</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>46010</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45742</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45908</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>45884</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45474</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45933</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>45002</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45981</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>46136</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51257,7 +51257,7 @@
         <v>46007</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45834</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45600</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45841</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>46003</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>44938</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>45711</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>44909</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51846,7 +51846,7 @@
         <v>46010</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>44698</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45331</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>45331</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52138,7 +52138,7 @@
         <v>45331</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45926</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52284,7 +52284,7 @@
         <v>45155</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52357,7 +52357,7 @@
         <v>45890</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45299</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>44509</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52576,7 +52576,7 @@
         <v>45726</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45176</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45359</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45036</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>45384</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>45447</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45902</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>44818</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>44930</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53233,7 +53233,7 @@
         <v>44631</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45903</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53384,7 +53384,7 @@
         <v>44900</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53457,7 +53457,7 @@
         <v>45474</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>44904</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45261</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53676,7 +53676,7 @@
         <v>45063</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53749,7 +53749,7 @@
         <v>44967</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>44967</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>44518</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45873</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54046,7 +54046,7 @@
         <v>46031</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>45607</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54192,7 +54192,7 @@
         <v>45992</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>45547</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45086</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54411,7 +54411,7 @@
         <v>45674</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54484,7 +54484,7 @@
         <v>45005</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54557,7 +54557,7 @@
         <v>45005</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54630,7 +54630,7 @@
         <v>46036</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45821</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54781,7 +54781,7 @@
         <v>46035</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54854,7 +54854,7 @@
         <v>45252</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54927,7 +54927,7 @@
         <v>45701</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         <v>45547</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55073,7 +55073,7 @@
         <v>46038</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55146,7 +55146,7 @@
         <v>46038</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55219,7 +55219,7 @@
         <v>46038</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45106</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55365,7 +55365,7 @@
         <v>44965</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55438,7 +55438,7 @@
         <v>44964</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55511,7 +55511,7 @@
         <v>44712</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55584,7 +55584,7 @@
         <v>45755</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>45051</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55730,7 +55730,7 @@
         <v>44599</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55803,7 +55803,7 @@
         <v>45033</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>46048</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55949,7 +55949,7 @@
         <v>45278</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45129</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>46031</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>44895</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56241,7 +56241,7 @@
         <v>44916</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>44972</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56387,7 +56387,7 @@
         <v>45601</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56460,7 +56460,7 @@
         <v>45904</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45758</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>46063</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>46063</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56757,7 +56757,7 @@
         <v>46148</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>46148</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>46149</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56976,7 +56976,7 @@
         <v>46154</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57049,7 +57049,7 @@
         <v>46078</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>46083</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57195,7 +57195,7 @@
         <v>46083</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57268,7 +57268,7 @@
         <v>46083</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>46083</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>46043</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57492,7 +57492,7 @@
         <v>45902</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57565,7 +57565,7 @@
         <v>45700</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>46086</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>46090</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57784,7 +57784,7 @@
         <v>46160</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45574</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57930,7 +57930,7 @@
         <v>46162</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>46162</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58076,7 +58076,7 @@
         <v>46167</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58149,7 +58149,7 @@
         <v>46167</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>46168</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>46168</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58368,7 +58368,7 @@
         <v>46168</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58441,7 +58441,7 @@
         <v>46167</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>46167</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58587,7 +58587,7 @@
         <v>46171</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58665,7 +58665,7 @@
         <v>45629</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58738,7 +58738,7 @@
         <v>46175</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         <v>46175</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58884,7 +58884,7 @@
         <v>46176</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58957,7 +58957,7 @@
         <v>46177</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59030,7 +59030,7 @@
         <v>46175</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59103,7 +59103,7 @@
         <v>46181</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59176,7 +59176,7 @@
         <v>46182</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>46146</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59322,7 +59322,7 @@
         <v>46135</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59395,7 +59395,7 @@
         <v>46182</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>46184</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59541,7 +59541,7 @@
         <v>46184</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>46182</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         <v>46188</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>46190</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>46189</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>46197</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>45426</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60052,7 +60052,7 @@
         <v>45418</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>46198</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60203,7 +60203,7 @@
         <v>46199</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>46204</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60349,7 +60349,7 @@
         <v>46203</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60422,7 +60422,7 @@
         <v>46204</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60500,7 +60500,7 @@
         <v>46204</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>46204</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>46206</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>46206</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60822,7 +60822,7 @@
         <v>46206</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>46212</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>46213</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>46213</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61114,7 +61114,7 @@
         <v>46213</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61187,7 +61187,7 @@
         <v>46189</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61260,7 +61260,7 @@
         <v>46209</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61338,7 +61338,7 @@
         <v>46045</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61416,7 +61416,7 @@
         <v>46266</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61489,7 +61489,7 @@
         <v>46195</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61562,7 +61562,7 @@
         <v>46195</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61635,7 +61635,7 @@
         <v>46195</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>46191</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61781,7 +61781,7 @@
         <v>46274</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61859,7 +61859,7 @@
         <v>45432</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61937,7 +61937,7 @@
         <v>46120</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>46279</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62083,7 +62083,7 @@
         <v>46202</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62156,7 +62156,7 @@
         <v>46244</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>46287</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62302,7 +62302,7 @@
         <v>46147</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
         <v>45978</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>46293</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>46293</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         <v>46293</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>46294</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62740,7 +62740,7 @@
         <v>46251</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>46300</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62891,7 +62891,7 @@
         <v>46120</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>46293</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -63037,7 +63037,7 @@
         <v>46301</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63110,7 +63110,7 @@
         <v>46044</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63188,7 +63188,7 @@
         <v>46303</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63261,7 +63261,7 @@
         <v>46031</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63334,7 +63334,7 @@
         <v>46303</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63407,7 +63407,7 @@
         <v>45113</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>46262</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63553,7 +63553,7 @@
         <v>46262</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63626,7 +63626,7 @@
         <v>46303</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>46260</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>46260</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>46260</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63918,7 +63918,7 @@
         <v>45950</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>46000</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -64064,7 +64064,7 @@
         <v>44672</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>44722</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45387</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>45387</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>45456</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>45602</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>44894</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64575,7 +64575,7 @@
         <v>45443</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64648,7 +64648,7 @@
         <v>44888</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64721,7 +64721,7 @@
         <v>44900</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64794,7 +64794,7 @@
         <v>45359</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64867,7 +64867,7 @@
         <v>45359</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64940,7 +64940,7 @@
         <v>45387</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -65013,7 +65013,7 @@
         <v>45128</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>45387</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45362</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65232,7 +65232,7 @@
         <v>45534</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65305,7 +65305,7 @@
         <v>44901</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65378,7 +65378,7 @@
         <v>44792</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         <v>45362</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         <v>45330</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65602,7 +65602,7 @@
         <v>44883</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65675,7 +65675,7 @@
         <v>45330</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65748,7 +65748,7 @@
         <v>44928</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>45477</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>44971</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>44900</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>44971</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>45230</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66186,7 +66186,7 @@
         <v>45730</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45665</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45727</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45665</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>45807</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45807</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46038</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>46042</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>46042</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>46042</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>46042</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>46045</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -67062,7 +67062,7 @@
         <v>46132</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67135,7 +67135,7 @@
         <v>46181</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -67208,7 +67208,7 @@
         <v>46188</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -67281,7 +67281,7 @@
         <v>46213</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44977</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44740</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>45565</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>44992</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>44872</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>45099</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45387</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>45810</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>46050</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44599</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44756</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44578</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45322</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>44489</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45461</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3792,7 +3792,7 @@
         <v>44992</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         <v>45646</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45546</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         <v>45001</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>44729</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4422,7 +4422,7 @@
         <v>45580</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4527,7 +4527,7 @@
         <v>45406</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4632,7 +4632,7 @@
         <v>44984</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4737,7 +4737,7 @@
         <v>45341</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>46086</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>46213</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>46289</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>46293</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46301</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45330</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>45467</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45153</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>46056</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44888</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44557</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44620</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         <v>44620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6552,7 +6552,7 @@
         <v>44732</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44813</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44508</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44539</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44755</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44713</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44524</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44489</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44813</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44753</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44865</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44533</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44819</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44570</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44494</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44641</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44692</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44690</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44865</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44610</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44644</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44603</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44804</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44508</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44722</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44511</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>44867</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44879</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44532</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44875</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44879</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44494</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44820</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44676</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44489</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44620</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44529</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44631</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44648</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>44798</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>44540</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>44608</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44698</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44680</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44631</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>44523</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10645,7 +10645,7 @@
         <v>44481</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44620</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>44620</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44875</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44636</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44519</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44698</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44749</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>44685</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>44791</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44748</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44711</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44641</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44494</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44753</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44540</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44509</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44888</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44522</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44533</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44722</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44875</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>44753</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44523</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>44712</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45439</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45680</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45395</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>45702</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>45139</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44596</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45097</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13137,7 +13137,7 @@
         <v>45117</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         <v>45091</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>45117</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13356,7 +13356,7 @@
         <v>45082</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13429,7 +13429,7 @@
         <v>45646</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13502,7 +13502,7 @@
         <v>44888</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>45229</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45377</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13721,7 +13721,7 @@
         <v>45338</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13794,7 +13794,7 @@
         <v>45411</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13872,7 +13872,7 @@
         <v>45412</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13945,7 +13945,7 @@
         <v>45252</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14018,7 +14018,7 @@
         <v>45407</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>45075</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45110</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>45107</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45553</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45261</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45215</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45103</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45394</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45183</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>45035</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45401</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45362</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45173</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>44481</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>45300</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>44769</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15264,7 +15264,7 @@
         <v>44984</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45688</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15410,7 +15410,7 @@
         <v>44483</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15483,7 +15483,7 @@
         <v>45279</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>44820</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45331</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45034</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15775,7 +15775,7 @@
         <v>45170</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15848,7 +15848,7 @@
         <v>45449</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45449</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44883</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45394</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>44490</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>44895</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45240</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45330</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45089</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>45117</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45117</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16656,7 +16656,7 @@
         <v>44949</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16729,7 +16729,7 @@
         <v>44960</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16802,7 +16802,7 @@
         <v>45439</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16875,7 +16875,7 @@
         <v>44967</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45467</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45467</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45467</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45601</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>45455</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45574</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44489</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45370</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45240</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>44928</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>45356</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>44953</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45477</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45755</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17980,7 +17980,7 @@
         <v>45267</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18053,7 +18053,7 @@
         <v>45727</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18126,7 +18126,7 @@
         <v>45533</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18199,7 +18199,7 @@
         <v>44903</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18272,7 +18272,7 @@
         <v>45085</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18345,7 +18345,7 @@
         <v>45445</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18418,7 +18418,7 @@
         <v>45329</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44935</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>44728</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45034</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45002</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45124</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45180</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44904</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>44960</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>45240</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45325</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45553</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45107</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45671</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>44489</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>45154</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45436</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45152</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>44634</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>44545</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45394</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45887</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44949</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44949</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>45002</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45314</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45310</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>45475</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>45392</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
         <v>45069</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20613,7 +20613,7 @@
         <v>45275</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20686,7 +20686,7 @@
         <v>44838</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20759,7 +20759,7 @@
         <v>44545</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
         <v>45439</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20905,7 +20905,7 @@
         <v>45691</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44945</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45559</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44524</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45637</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21280,7 +21280,7 @@
         <v>45637</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>44881</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>45424</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45019</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>44930</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>45896</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45615</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45436</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>45005</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>45540</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>45386</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22088,7 +22088,7 @@
         <v>44936</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>44936</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22234,7 +22234,7 @@
         <v>45646</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22307,7 +22307,7 @@
         <v>45443</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22380,7 +22380,7 @@
         <v>45246</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22453,7 +22453,7 @@
         <v>45049</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>45097</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45194</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>44950</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45644</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22818,7 +22818,7 @@
         <v>45327</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45546</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45394</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45432</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45904</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>44911</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23266,7 +23266,7 @@
         <v>45329</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45434</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>44895</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45792</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45408</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45789</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45905</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45908</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45540</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>44481</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45349</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>44964</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45274</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45362</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45670</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45562</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45419</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45519</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45574</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45089</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>45602</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45615</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>45166</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>44907</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45539</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45782</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>45546</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>45784</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>44599</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45553</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45784</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25534,7 +25534,7 @@
         <v>44558</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25607,7 +25607,7 @@
         <v>45594</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45252</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>44540</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45590</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>44930</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>44995</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45155</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>45546</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45679</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45709</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45342</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45176</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44575</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45670</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45679</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>44783</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>44620</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45568</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45160</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45562</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45511</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45274</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45636</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>45597</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27369,7 +27369,7 @@
         <v>45524</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27442,7 +27442,7 @@
         <v>45576</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45565</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27588,7 +27588,7 @@
         <v>44928</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>45155</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45155</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45635</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         <v>44783</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45230</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28031,7 +28031,7 @@
         <v>45540</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45923</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28177,7 +28177,7 @@
         <v>45007</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28250,7 +28250,7 @@
         <v>45266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28328,7 +28328,7 @@
         <v>44971</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45923</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45631</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28547,7 +28547,7 @@
         <v>45789</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28620,7 +28620,7 @@
         <v>45712</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28693,7 +28693,7 @@
         <v>45345</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28766,7 +28766,7 @@
         <v>45637</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28844,7 +28844,7 @@
         <v>45012</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>45345</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28990,7 +28990,7 @@
         <v>45014</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44676</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>44950</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29209,7 +29209,7 @@
         <v>44795</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29282,7 +29282,7 @@
         <v>44965</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29360,7 +29360,7 @@
         <v>44945</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29433,7 +29433,7 @@
         <v>45264</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29506,7 +29506,7 @@
         <v>45264</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45548</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>44939</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45029</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29798,7 +29798,7 @@
         <v>45033</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>44570</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>44550</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30017,7 +30017,7 @@
         <v>45107</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30090,7 +30090,7 @@
         <v>45240</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>44586</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30236,7 +30236,7 @@
         <v>45793</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>44936</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30382,7 +30382,7 @@
         <v>44936</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30455,7 +30455,7 @@
         <v>45568</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45631</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>44617</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>45793</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30747,7 +30747,7 @@
         <v>45152</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30820,7 +30820,7 @@
         <v>45155</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30893,7 +30893,7 @@
         <v>45155</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30966,7 +30966,7 @@
         <v>44620</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31044,7 +31044,7 @@
         <v>45614</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45439</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31190,7 +31190,7 @@
         <v>45078</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>45933</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45637</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31414,7 +31414,7 @@
         <v>45727</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44928</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31560,7 +31560,7 @@
         <v>45071</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31633,7 +31633,7 @@
         <v>45692</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31706,7 +31706,7 @@
         <v>44683</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31779,7 +31779,7 @@
         <v>45618</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31852,7 +31852,7 @@
         <v>45344</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31925,7 +31925,7 @@
         <v>45478</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>45533</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32071,7 +32071,7 @@
         <v>45477</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45408</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32217,7 +32217,7 @@
         <v>45175</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32290,7 +32290,7 @@
         <v>45203</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45637</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>44928</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32514,7 +32514,7 @@
         <v>45684</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45082</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45727</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32733,7 +32733,7 @@
         <v>45191</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45162</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32879,7 +32879,7 @@
         <v>44963</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>45106</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45938</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33098,7 +33098,7 @@
         <v>45091</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>44685</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33244,7 +33244,7 @@
         <v>44685</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45085</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>44993</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33463,7 +33463,7 @@
         <v>45182</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33536,7 +33536,7 @@
         <v>45107</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45077</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>44627</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45811</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33828,7 +33828,7 @@
         <v>44673</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33901,7 +33901,7 @@
         <v>44624</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45547</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45176</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45614</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34193,7 +34193,7 @@
         <v>45107</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34266,7 +34266,7 @@
         <v>44620</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34339,7 +34339,7 @@
         <v>45215</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34412,7 +34412,7 @@
         <v>45609</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34485,7 +34485,7 @@
         <v>44621</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34558,7 +34558,7 @@
         <v>44614</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34631,7 +34631,7 @@
         <v>45210</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45215</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>45147</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>45034</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45138</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45713</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>45090</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>44820</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>45820</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45635</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45793</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45579</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>45574</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45574</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>45580</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>44984</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>45323</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>45307</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>45244</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>45574</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45007</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>45245</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45608</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45211</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>44657</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45827</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45684</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45831</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>44609</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>45831</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45832</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>45183</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45183</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45117</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>44749</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>45461</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37274,7 +37274,7 @@
         <v>45953</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>44728</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>44728</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45173</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>44545</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>44655</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>45226</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>45119</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>45062</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>44700</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45181</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38077,7 +38077,7 @@
         <v>45009</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>44993</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>44705</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>45096</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>45838</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45434</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45610</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45674</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>44852</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38739,7 +38739,7 @@
         <v>45093</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38812,7 +38812,7 @@
         <v>45839</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38885,7 +38885,7 @@
         <v>44998</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38958,7 +38958,7 @@
         <v>45547</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39031,7 +39031,7 @@
         <v>44753</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39104,7 +39104,7 @@
         <v>45164</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39177,7 +39177,7 @@
         <v>45164</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>45197</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>44951</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45841</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39469,7 +39469,7 @@
         <v>45841</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39542,7 +39542,7 @@
         <v>45552</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45972</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45677</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39766,7 +39766,7 @@
         <v>45264</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39839,7 +39839,7 @@
         <v>45117</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45629</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39985,7 +39985,7 @@
         <v>44748</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45236</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>45331</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45701</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45099</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45303</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45469</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45238</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45617</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45109</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45109</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>45302</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45121</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>45751</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45775</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45722</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>44994</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>44804</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>44495</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>44505</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>45306</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>45684</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>45090</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>45062</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45314</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>44804</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>45644</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41956,7 +41956,7 @@
         <v>45176</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>45078</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>45036</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42175,7 +42175,7 @@
         <v>45366</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42248,7 +42248,7 @@
         <v>44756</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42321,7 +42321,7 @@
         <v>44901</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>44901</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>45035</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42540,7 +42540,7 @@
         <v>45267</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>44529</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42686,7 +42686,7 @@
         <v>45399</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42759,7 +42759,7 @@
         <v>45873</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45873</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42905,7 +42905,7 @@
         <v>44904</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42978,7 +42978,7 @@
         <v>44867</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43051,7 +43051,7 @@
         <v>45979</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>44930</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>44950</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45167</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>45188</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43416,7 +43416,7 @@
         <v>45710</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43489,7 +43489,7 @@
         <v>45874</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43562,7 +43562,7 @@
         <v>44831</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>44831</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43708,7 +43708,7 @@
         <v>45980</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45873</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43854,7 +43854,7 @@
         <v>44522</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43932,7 +43932,7 @@
         <v>45082</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45877</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44078,7 +44078,7 @@
         <v>44937</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44151,7 +44151,7 @@
         <v>45188</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>45772</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44297,7 +44297,7 @@
         <v>45327</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44375,7 +44375,7 @@
         <v>45462</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44448,7 +44448,7 @@
         <v>45272</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44521,7 +44521,7 @@
         <v>45264</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44594,7 +44594,7 @@
         <v>45881</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44667,7 +44667,7 @@
         <v>45881</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44740,7 +44740,7 @@
         <v>44991</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>44991</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44886,7 +44886,7 @@
         <v>45247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45247</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>44988</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>45110</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45178,7 +45178,7 @@
         <v>45244</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45201</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45324,7 +45324,7 @@
         <v>44748</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45397,7 +45397,7 @@
         <v>45063</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45470,7 +45470,7 @@
         <v>45982</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45543,7 +45543,7 @@
         <v>46098</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>44691</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45303</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>46101</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>45002</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>45616</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45981,7 +45981,7 @@
         <v>46101</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>44930</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>46104</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46200,7 +46200,7 @@
         <v>45429</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46273,7 +46273,7 @@
         <v>45201</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>44627</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46419,7 +46419,7 @@
         <v>45264</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46492,7 +46492,7 @@
         <v>46106</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45071</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45071</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45071</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>45574</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45260</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45386</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>44631</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45112</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>45735</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>45735</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47300,7 +47300,7 @@
         <v>46108</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>46108</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47446,7 +47446,7 @@
         <v>45412</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47519,7 +47519,7 @@
         <v>45466</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>46108</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>44790</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47738,7 +47738,7 @@
         <v>44984</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47811,7 +47811,7 @@
         <v>45371</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47884,7 +47884,7 @@
         <v>45406</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47957,7 +47957,7 @@
         <v>45082</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48030,7 +48030,7 @@
         <v>45082</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48103,7 +48103,7 @@
         <v>45106</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48176,7 +48176,7 @@
         <v>44916</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48249,7 +48249,7 @@
         <v>45261</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>45709</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48400,7 +48400,7 @@
         <v>46119</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48473,7 +48473,7 @@
         <v>44602</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48546,7 +48546,7 @@
         <v>45993</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48619,7 +48619,7 @@
         <v>46120</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48692,7 +48692,7 @@
         <v>44657</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48765,7 +48765,7 @@
         <v>46000</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>46120</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48911,7 +48911,7 @@
         <v>46132</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -48984,7 +48984,7 @@
         <v>44967</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>45572</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49130,7 +49130,7 @@
         <v>44628</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49203,7 +49203,7 @@
         <v>44967</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>46105</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49354,7 +49354,7 @@
         <v>46132</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49427,7 +49427,7 @@
         <v>46134</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49500,7 +49500,7 @@
         <v>44939</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49573,7 +49573,7 @@
         <v>44988</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49646,7 +49646,7 @@
         <v>45568</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45782</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49792,7 +49792,7 @@
         <v>45897</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>45992</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49938,7 +49938,7 @@
         <v>45553</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50016,7 +50016,7 @@
         <v>45803</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50089,7 +50089,7 @@
         <v>45188</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50162,7 +50162,7 @@
         <v>45897</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45924</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50308,7 +50308,7 @@
         <v>45062</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>45395</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50454,7 +50454,7 @@
         <v>45596</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>45755</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50600,7 +50600,7 @@
         <v>46010</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50673,7 +50673,7 @@
         <v>45742</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50746,7 +50746,7 @@
         <v>45908</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50819,7 +50819,7 @@
         <v>45884</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50892,7 +50892,7 @@
         <v>45474</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50965,7 +50965,7 @@
         <v>45933</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
         <v>45002</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51111,7 +51111,7 @@
         <v>45981</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51184,7 +51184,7 @@
         <v>46136</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51257,7 +51257,7 @@
         <v>46007</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51335,7 +51335,7 @@
         <v>45834</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51408,7 +51408,7 @@
         <v>45600</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51481,7 +51481,7 @@
         <v>45841</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51554,7 +51554,7 @@
         <v>46003</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51627,7 +51627,7 @@
         <v>44938</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51700,7 +51700,7 @@
         <v>45711</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51773,7 +51773,7 @@
         <v>44909</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51846,7 +51846,7 @@
         <v>46010</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51919,7 +51919,7 @@
         <v>44698</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>45331</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52065,7 +52065,7 @@
         <v>45331</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52138,7 +52138,7 @@
         <v>45331</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52211,7 +52211,7 @@
         <v>45926</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52284,7 +52284,7 @@
         <v>45155</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52357,7 +52357,7 @@
         <v>45890</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52430,7 +52430,7 @@
         <v>45299</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52503,7 +52503,7 @@
         <v>44509</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52576,7 +52576,7 @@
         <v>45726</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52649,7 +52649,7 @@
         <v>45176</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52722,7 +52722,7 @@
         <v>45359</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52795,7 +52795,7 @@
         <v>45036</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52868,7 +52868,7 @@
         <v>45384</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52941,7 +52941,7 @@
         <v>45447</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53014,7 +53014,7 @@
         <v>45902</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53087,7 +53087,7 @@
         <v>44818</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53160,7 +53160,7 @@
         <v>44930</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53233,7 +53233,7 @@
         <v>44631</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>45903</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53384,7 +53384,7 @@
         <v>44900</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53457,7 +53457,7 @@
         <v>45474</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53530,7 +53530,7 @@
         <v>44904</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53603,7 +53603,7 @@
         <v>45261</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53676,7 +53676,7 @@
         <v>45063</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53749,7 +53749,7 @@
         <v>44967</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>44967</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53900,7 +53900,7 @@
         <v>44518</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53973,7 +53973,7 @@
         <v>45873</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54046,7 +54046,7 @@
         <v>46031</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>45607</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54192,7 +54192,7 @@
         <v>45992</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>45547</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>45086</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54411,7 +54411,7 @@
         <v>45674</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54484,7 +54484,7 @@
         <v>45005</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54557,7 +54557,7 @@
         <v>45005</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54630,7 +54630,7 @@
         <v>46036</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54708,7 +54708,7 @@
         <v>45821</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54781,7 +54781,7 @@
         <v>46035</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54854,7 +54854,7 @@
         <v>45252</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54927,7 +54927,7 @@
         <v>45701</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55000,7 +55000,7 @@
         <v>45547</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55073,7 +55073,7 @@
         <v>46038</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55146,7 +55146,7 @@
         <v>46038</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55219,7 +55219,7 @@
         <v>46038</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55292,7 +55292,7 @@
         <v>45106</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55365,7 +55365,7 @@
         <v>44965</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55438,7 +55438,7 @@
         <v>44964</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55511,7 +55511,7 @@
         <v>44712</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55584,7 +55584,7 @@
         <v>45755</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55657,7 +55657,7 @@
         <v>45051</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55730,7 +55730,7 @@
         <v>44599</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55803,7 +55803,7 @@
         <v>45033</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55876,7 +55876,7 @@
         <v>46048</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55949,7 +55949,7 @@
         <v>45278</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56022,7 +56022,7 @@
         <v>45129</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>46031</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>44895</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56241,7 +56241,7 @@
         <v>44916</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>44972</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56387,7 +56387,7 @@
         <v>45601</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56460,7 +56460,7 @@
         <v>45904</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56533,7 +56533,7 @@
         <v>45758</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56611,7 +56611,7 @@
         <v>46063</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56684,7 +56684,7 @@
         <v>46063</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56757,7 +56757,7 @@
         <v>46148</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>46148</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>46149</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56976,7 +56976,7 @@
         <v>46154</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57049,7 +57049,7 @@
         <v>46078</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57122,7 +57122,7 @@
         <v>46083</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57195,7 +57195,7 @@
         <v>46083</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57268,7 +57268,7 @@
         <v>46083</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57341,7 +57341,7 @@
         <v>46083</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57414,7 +57414,7 @@
         <v>46043</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57492,7 +57492,7 @@
         <v>45902</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57565,7 +57565,7 @@
         <v>45700</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57638,7 +57638,7 @@
         <v>46086</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57711,7 +57711,7 @@
         <v>46090</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57784,7 +57784,7 @@
         <v>46160</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57857,7 +57857,7 @@
         <v>45574</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57930,7 +57930,7 @@
         <v>46162</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58003,7 +58003,7 @@
         <v>46162</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58076,7 +58076,7 @@
         <v>46167</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58149,7 +58149,7 @@
         <v>46167</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58222,7 +58222,7 @@
         <v>46168</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58295,7 +58295,7 @@
         <v>46168</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58368,7 +58368,7 @@
         <v>46168</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58441,7 +58441,7 @@
         <v>46167</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58514,7 +58514,7 @@
         <v>46167</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58587,7 +58587,7 @@
         <v>46171</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58665,7 +58665,7 @@
         <v>45629</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58738,7 +58738,7 @@
         <v>46175</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58811,7 +58811,7 @@
         <v>46175</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58884,7 +58884,7 @@
         <v>46176</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58957,7 +58957,7 @@
         <v>46177</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59030,7 +59030,7 @@
         <v>46175</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59103,7 +59103,7 @@
         <v>46181</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59176,7 +59176,7 @@
         <v>46182</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59249,7 +59249,7 @@
         <v>46146</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59322,7 +59322,7 @@
         <v>46135</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59395,7 +59395,7 @@
         <v>46182</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>46184</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59541,7 +59541,7 @@
         <v>46184</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>46182</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59687,7 +59687,7 @@
         <v>46188</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59760,7 +59760,7 @@
         <v>46190</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59833,7 +59833,7 @@
         <v>46189</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59906,7 +59906,7 @@
         <v>46197</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59979,7 +59979,7 @@
         <v>45426</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60052,7 +60052,7 @@
         <v>45418</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>46198</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60203,7 +60203,7 @@
         <v>46199</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60276,7 +60276,7 @@
         <v>46204</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60349,7 +60349,7 @@
         <v>46203</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60422,7 +60422,7 @@
         <v>46204</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60500,7 +60500,7 @@
         <v>46204</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60578,7 +60578,7 @@
         <v>46204</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60656,7 +60656,7 @@
         <v>46206</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60729,7 +60729,7 @@
         <v>46206</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60822,7 +60822,7 @@
         <v>46206</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60895,7 +60895,7 @@
         <v>46212</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60968,7 +60968,7 @@
         <v>46213</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61041,7 +61041,7 @@
         <v>46213</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61114,7 +61114,7 @@
         <v>46213</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61187,7 +61187,7 @@
         <v>46189</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61260,7 +61260,7 @@
         <v>46209</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61338,7 +61338,7 @@
         <v>46045</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61416,7 +61416,7 @@
         <v>46266</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61489,7 +61489,7 @@
         <v>46195</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61562,7 +61562,7 @@
         <v>46195</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61635,7 +61635,7 @@
         <v>46195</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61708,7 +61708,7 @@
         <v>46191</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61781,7 +61781,7 @@
         <v>46274</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61859,7 +61859,7 @@
         <v>45432</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61937,7 +61937,7 @@
         <v>46120</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>46279</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62083,7 +62083,7 @@
         <v>46202</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62156,7 +62156,7 @@
         <v>46244</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>46287</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62302,7 +62302,7 @@
         <v>46147</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
         <v>45978</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>46293</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>46293</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         <v>46293</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>46294</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62740,7 +62740,7 @@
         <v>46251</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>46300</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62891,7 +62891,7 @@
         <v>46120</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>46293</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -63037,7 +63037,7 @@
         <v>46301</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63110,7 +63110,7 @@
         <v>46044</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63188,7 +63188,7 @@
         <v>46303</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63261,7 +63261,7 @@
         <v>46031</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63334,7 +63334,7 @@
         <v>46303</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63407,7 +63407,7 @@
         <v>45113</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>46262</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63553,7 +63553,7 @@
         <v>46262</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63626,7 +63626,7 @@
         <v>46303</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>46260</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>46260</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>46260</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63918,7 +63918,7 @@
         <v>45950</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>46000</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -64064,7 +64064,7 @@
         <v>44672</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>44722</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45387</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>45387</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>45456</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>45602</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>44894</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64575,7 +64575,7 @@
         <v>45443</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64648,7 +64648,7 @@
         <v>44888</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64721,7 +64721,7 @@
         <v>44900</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64794,7 +64794,7 @@
         <v>45359</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64867,7 +64867,7 @@
         <v>45359</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64940,7 +64940,7 @@
         <v>45387</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -65013,7 +65013,7 @@
         <v>45128</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>45387</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45362</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65232,7 +65232,7 @@
         <v>45534</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65305,7 +65305,7 @@
         <v>44901</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65378,7 +65378,7 @@
         <v>44792</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         <v>45362</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         <v>45330</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65602,7 +65602,7 @@
         <v>44883</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65675,7 +65675,7 @@
         <v>45330</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65748,7 +65748,7 @@
         <v>44928</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>45477</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>44971</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>44900</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>44971</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>45230</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66186,7 +66186,7 @@
         <v>45730</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45665</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45727</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45665</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>45807</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45807</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46038</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>46042</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>46042</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>46042</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>46042</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>46045</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -67062,7 +67062,7 @@
         <v>46132</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67135,7 +67135,7 @@
         <v>46181</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -67208,7 +67208,7 @@
         <v>46188</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -67281,7 +67281,7 @@
         <v>46213</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44977</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44740</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>44992</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45565</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>46050</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44872</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>46300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>45387</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>45827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44599</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44756</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44578</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>44984</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>45580</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>45001</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45646</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44729</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>45322</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45406</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45546</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>46086</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>46213</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45461</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45341</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>44992</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>46289</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>46293</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46301</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45330</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>45467</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45153</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>46056</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44888</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44557</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44732</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>44620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44620</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44813</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44539</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44755</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44713</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44524</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44753</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44813</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44865</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44533</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44819</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44570</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44494</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44641</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44692</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44690</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44610</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44865</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44644</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44603</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44804</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44508</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44722</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>44511</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44879</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44875</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44532</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44879</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44494</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44489</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44529</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44631</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44648</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44798</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44620</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>44620</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>44636</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>44519</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44791</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44748</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44888</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>44820</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>44494</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>44509</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>44522</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44722</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44533</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44680</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44631</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>44523</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>44749</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44711</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44753</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44540</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44676</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44620</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44540</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44875</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44698</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44685</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44641</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44523</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>44712</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44596</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45075</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45775</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45477</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45395</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44967</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>44586</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45377</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44728</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44676</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45147</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45617</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>45362</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45082</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>44631</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45107</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45631</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45635</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45574</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45086</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45110</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45399</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44991</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>44939</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45089</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45091</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45034</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45637</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45310</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45117</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45117</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>45188</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45033</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45303</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44545</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44904</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45306</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45344</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44540</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45359</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45107</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45155</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45553</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44967</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45155</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45155</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44570</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45608</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45466</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45272</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45447</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45247</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44928</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>44529</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44558</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45164</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45164</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44509</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45107</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>44490</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>44928</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45244</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45071</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45246</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>44804</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44804</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44683</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44522</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45701</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>44749</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45701</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45019</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45033</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45244</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45610</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45580</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45362</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45194</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45461</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44818</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45014</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44900</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45366</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45455</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45475</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45181</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45710</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>44617</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>44937</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45029</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45702</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45173</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45274</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45327</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44753</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45394</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45176</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45085</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45394</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45323</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45097</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44883</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44984</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45152</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45034</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44938</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44881</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44951</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44691</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44545</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45203</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45154</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>44993</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45107</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45049</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45247</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44945</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44949</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45709</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45349</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45170</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45238</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45036</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44950</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>46031</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45897</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45887</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45890</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45903</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45240</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45553</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45897</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45742</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45834</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45103</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45908</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45933</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45755</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45722</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>46035</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45183</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45183</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44728</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45671</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45474</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45884</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44489</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44964</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45267</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45981</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45803</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45329</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>46136</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45896</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44631</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45299</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>45992</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44936</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44936</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45180</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46010</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>46010</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45924</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>45711</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45727</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>45278</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>44852</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>45758</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45467</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45467</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45467</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45904</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45443</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45646</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>45904</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45905</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45792</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45789</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45908</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45082</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45082</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44634</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45035</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45553</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45445</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45923</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45342</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45923</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44991</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45548</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>44904</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45062</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>44964</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45012</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45162</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45412</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44909</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>46148</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44928</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>46149</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45211</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44965</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45933</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44790</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45938</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45264</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44888</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45093</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44895</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45700</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45107</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45069</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45574</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>44935</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45631</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45002</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45408</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45229</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45953</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46043</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45191</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45902</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>46154</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44518</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45264</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45264</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>46160</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45618</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>45407</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45539</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44967</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44967</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45574</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44930</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45097</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45972</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>46162</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>46162</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45331</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44950</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44599</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45439</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>44988</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45688</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45432</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45727</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45979</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45412</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>44756</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>44953</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>46167</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>44599</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45002</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45980</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>46167</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45982</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45533</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45462</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44993</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45735</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>45735</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45568</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45325</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>46167</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>46167</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>44930</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45434</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45117</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45117</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45395</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45173</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45090</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>45082</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45201</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45993</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45552</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>46168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>46168</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>46168</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44657</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45629</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45062</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45077</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>44769</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>45600</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>46000</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45331</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44916</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45002</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45002</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45439</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>46171</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>46007</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44995</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45117</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45129</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45547</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45121</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45574</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45726</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>44930</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>45635</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45629</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44930</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45005</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45005</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45330</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44550</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>45261</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>46175</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>44495</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>45429</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44545</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45691</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>46031</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>45469</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>45106</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>45261</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46175</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>44705</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>46176</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46036</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>46038</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>46038</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>46038</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45609</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>46177</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>44831</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44831</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>44960</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>46182</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45356</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>46048</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45197</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>46182</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>46182</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>45007</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45408</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>44627</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>46175</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46181</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>45601</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45546</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>45307</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38729,7 +38729,7 @@
         <v>46184</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>46063</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46063</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>46135</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>46146</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45540</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>45540</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>46184</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>45300</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>44939</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>46188</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>44895</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>44916</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>44655</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44936</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44936</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>46078</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45160</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45401</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>44748</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45139</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>46190</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>44820</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>46083</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>46083</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>46083</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>45078</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45078</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>46083</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45106</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>46086</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45215</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45109</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>44673</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>46090</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>44945</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>44728</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45007</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>46189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>44907</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45684</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>46098</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>46104</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>46101</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45063</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>46101</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45644</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45302</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44820</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>46106</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>45215</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45245</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>46108</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>46108</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>44963</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>46198</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46108</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>46197</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45155</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>45085</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>45439</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>46120</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>46119</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>46199</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45034</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45394</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>44624</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44928</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45267</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45418</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45426</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45264</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>46120</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45314</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>46105</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>44875</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>44505</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45614</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>44620</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>46132</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45261</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>46132</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45384</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45436</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>46204</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>46204</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>46204</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45394</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>46204</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45782</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>46203</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>44911</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45902</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45992</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45596</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45821</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>45873</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45099</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>45755</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>46003</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>45155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45547</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>45841</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45579</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45568</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>45926</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45063</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45772</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45474</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>44838</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>46206</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>46206</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>46206</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45674</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45637</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45637</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>44700</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>45424</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45240</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>44524</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>46212</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45226</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45314</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>45009</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45540</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>44949</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>46213</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>46213</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45236</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>46213</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45614</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>46189</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>46045</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45110</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>44994</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46209</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>44621</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>44903</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>44489</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45201</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49097,7 +49097,7 @@
         <v>46191</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45436</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>45432</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45386</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45439</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>44628</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>44614</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>46120</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45119</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45152</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45680</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45574</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45215</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>46274</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>45547</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>44795</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45449</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>45449</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45240</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45240</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45166</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>44984</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45155</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45112</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>44960</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>44620</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>44867</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45188</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45370</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45411</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>46279</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>45559</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45329</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45406</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45091</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45546</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45264</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>44698</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>44627</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>44602</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45176</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>44904</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45051</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>44685</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>44685</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>46287</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45035</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>44949</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45138</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>44984</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>45062</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>44712</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>45176</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>45252</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45252</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53132,7 +53132,7 @@
         <v>45331</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45331</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45331</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45005</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>46244</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>46202</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>45117</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>44657</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>45303</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>44972</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>45109</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>44575</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45071</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45071</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>45392</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>45183</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>44950</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54373,7 +54373,7 @@
         <v>44988</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54446,7 +54446,7 @@
         <v>45071</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>45096</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54592,7 +54592,7 @@
         <v>46147</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>46293</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>44967</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45978</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>44901</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>44901</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>46293</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>46293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>45386</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45082</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45182</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45674</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45601</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>44998</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45188</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>46294</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45371</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>46251</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>45572</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>45327</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>44620</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>45755</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45607</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45713</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45124</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>46120</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56510,7 +56510,7 @@
         <v>45616</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56583,7 +56583,7 @@
         <v>45275</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45175</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56729,7 +56729,7 @@
         <v>45338</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>44748</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45646</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56948,7 +56948,7 @@
         <v>45574</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         <v>45562</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45615</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>45419</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>45519</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57313,7 +57313,7 @@
         <v>45089</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>45670</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>45602</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45553</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>46044</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45782</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57756,7 +57756,7 @@
         <v>45546</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45784</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57902,7 +57902,7 @@
         <v>45709</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57975,7 +57975,7 @@
         <v>46300</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58048,7 +58048,7 @@
         <v>45784</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58121,7 +58121,7 @@
         <v>45176</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>46301</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>44783</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58340,7 +58340,7 @@
         <v>45266</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58418,7 +58418,7 @@
         <v>45712</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58491,7 +58491,7 @@
         <v>45679</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58564,7 +58564,7 @@
         <v>45789</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45679</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58710,7 +58710,7 @@
         <v>45230</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58783,7 +58783,7 @@
         <v>44783</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45568</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58929,7 +58929,7 @@
         <v>45511</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45950</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59075,7 +59075,7 @@
         <v>45636</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59153,7 +59153,7 @@
         <v>46303</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59226,7 +59226,7 @@
         <v>45345</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         <v>45252</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59372,7 +59372,7 @@
         <v>45594</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>45345</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59518,7 +59518,7 @@
         <v>46303</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>46303</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45562</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59737,7 +59737,7 @@
         <v>45590</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59810,7 +59810,7 @@
         <v>45597</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59883,7 +59883,7 @@
         <v>45637</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59961,7 +59961,7 @@
         <v>45576</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>45565</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60107,7 +60107,7 @@
         <v>45524</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>46260</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>45670</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60326,7 +60326,7 @@
         <v>46293</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60399,7 +60399,7 @@
         <v>46260</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60472,7 +60472,7 @@
         <v>46260</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60545,7 +60545,7 @@
         <v>45113</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>46031</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60691,7 +60691,7 @@
         <v>45793</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60764,7 +60764,7 @@
         <v>45793</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>46307</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>46000</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>46148</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>45477</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61129,7 +61129,7 @@
         <v>45533</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61202,7 +61202,7 @@
         <v>45692</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>46262</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>46262</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45478</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61494,7 +61494,7 @@
         <v>45684</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61567,7 +61567,7 @@
         <v>45637</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>46266</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61718,7 +61718,7 @@
         <v>46308</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>46308</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61864,7 +61864,7 @@
         <v>45727</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61937,7 +61937,7 @@
         <v>46195</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>46195</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62083,7 +62083,7 @@
         <v>46195</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62156,7 +62156,7 @@
         <v>45811</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45793</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62302,7 +62302,7 @@
         <v>45820</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
         <v>45827</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>46310</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45831</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         <v>45831</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45832</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62740,7 +62740,7 @@
         <v>44609</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45838</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62891,7 +62891,7 @@
         <v>45839</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45434</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -63037,7 +63037,7 @@
         <v>45841</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63110,7 +63110,7 @@
         <v>45677</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63188,7 +63188,7 @@
         <v>45841</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63261,7 +63261,7 @@
         <v>45751</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63334,7 +63334,7 @@
         <v>45684</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63407,7 +63407,7 @@
         <v>45090</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>45644</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63553,7 +63553,7 @@
         <v>45873</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63626,7 +63626,7 @@
         <v>45873</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>45873</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>45874</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>45877</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63918,7 +63918,7 @@
         <v>45881</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>45881</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -64064,7 +64064,7 @@
         <v>45387</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45387</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45456</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>45602</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>44894</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>45443</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>44672</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64575,7 +64575,7 @@
         <v>44888</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64648,7 +64648,7 @@
         <v>44900</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64721,7 +64721,7 @@
         <v>45359</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64794,7 +64794,7 @@
         <v>45359</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64867,7 +64867,7 @@
         <v>44722</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64940,7 +64940,7 @@
         <v>45387</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -65013,7 +65013,7 @@
         <v>45128</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>45387</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45362</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65232,7 +65232,7 @@
         <v>45534</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65305,7 +65305,7 @@
         <v>44901</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65378,7 +65378,7 @@
         <v>44792</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         <v>45362</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         <v>45330</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65602,7 +65602,7 @@
         <v>44883</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65675,7 +65675,7 @@
         <v>45330</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65748,7 +65748,7 @@
         <v>44928</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>45477</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>44971</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>44900</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>44971</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>45230</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66186,7 +66186,7 @@
         <v>45730</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45665</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45727</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45665</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>45807</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45807</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46038</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>46042</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>46042</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>46042</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>46042</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>46045</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -67062,7 +67062,7 @@
         <v>46132</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67135,7 +67135,7 @@
         <v>46181</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -67208,7 +67208,7 @@
         <v>46188</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -67281,7 +67281,7 @@
         <v>46213</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>45061</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>44977</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>44740</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>44992</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45565</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45099</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45810</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>46050</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>44872</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>46300</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>45387</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>45827</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44599</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44756</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44578</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>44984</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>45103</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3572,7 +3572,7 @@
         <v>45580</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>45001</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45646</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>44729</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>45322</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>45406</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>44489</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45182</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>45546</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         <v>46086</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>46213</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>45461</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4842,7 +4842,7 @@
         <v>45341</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
         <v>44992</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5052,7 +5052,7 @@
         <v>46289</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>46293</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>46301</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45387</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45330</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>45467</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45153</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45555</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>45890</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>46056</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>44888</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6177,7 +6177,7 @@
         <v>44557</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>44732</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6396,7 +6396,7 @@
         <v>44875</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>44620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>44620</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         <v>44813</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>44875</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>44539</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6917,7 +6917,7 @@
         <v>44755</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
         <v>44713</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         <v>44489</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         <v>44524</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
         <v>44753</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7282,7 +7282,7 @@
         <v>44813</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
         <v>44865</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>44533</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7501,7 +7501,7 @@
         <v>44575</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         <v>44819</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>44570</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44494</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44641</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>44692</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7939,7 +7939,7 @@
         <v>44690</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8012,7 +8012,7 @@
         <v>44610</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44865</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         <v>44791</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44644</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         <v>44603</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         <v>44627</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>44804</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8523,7 +8523,7 @@
         <v>44789</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>44508</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>44546</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>44722</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44722</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44867</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>44511</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>44839</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>44879</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         <v>44791</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>44875</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9331,7 +9331,7 @@
         <v>44532</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44595</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>44879</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44494</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>44489</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>44529</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>44631</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44648</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>44798</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>44608</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>44620</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>44620</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>44636</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>44519</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>44791</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44748</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>44888</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>44820</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>44494</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>44509</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10801,7 +10801,7 @@
         <v>44522</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44722</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10947,7 +10947,7 @@
         <v>44533</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44698</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11093,7 +11093,7 @@
         <v>44680</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11166,7 +11166,7 @@
         <v>44631</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11239,7 +11239,7 @@
         <v>44523</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>44749</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44711</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>44753</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>44540</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>44676</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>44620</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44540</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11823,7 +11823,7 @@
         <v>44875</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11896,7 +11896,7 @@
         <v>44698</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11969,7 +11969,7 @@
         <v>44685</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         <v>44641</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12115,7 +12115,7 @@
         <v>44539</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12188,7 +12188,7 @@
         <v>44631</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12261,7 +12261,7 @@
         <v>44523</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         <v>44753</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12407,7 +12407,7 @@
         <v>44712</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44596</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45075</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>45274</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>45775</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45477</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45395</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>44967</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>44586</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>45377</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>44728</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45615</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>44676</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45147</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44895</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45617</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>45362</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44965</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45082</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>44631</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45107</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45631</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>45635</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45574</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45086</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45110</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>45399</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>44991</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>44939</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>45089</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>45091</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45034</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45637</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>45310</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>45117</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45117</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>45188</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>45033</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>45303</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44545</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>44904</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>45306</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>45344</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44540</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45359</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45107</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45155</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45553</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>44967</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45155</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16077,7 +16077,7 @@
         <v>45155</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16150,7 +16150,7 @@
         <v>44570</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         <v>45608</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16296,7 +16296,7 @@
         <v>45466</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45272</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>45447</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>45247</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>44928</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>44529</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44930</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>44558</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>45164</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45164</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>44509</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45107</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>44490</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>44928</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45244</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45071</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45246</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>44804</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44804</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>44683</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44522</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>45701</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>44749</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45701</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45019</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45033</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45244</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45610</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45580</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>45279</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45362</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45194</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45461</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>44818</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>45014</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>44900</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19007,7 +19007,7 @@
         <v>45366</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19080,7 +19080,7 @@
         <v>44971</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19153,7 +19153,7 @@
         <v>45455</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45475</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>45181</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19372,7 +19372,7 @@
         <v>45710</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>44617</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19518,7 +19518,7 @@
         <v>44937</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>45029</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>45702</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45173</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>45274</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>45327</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20034,7 +20034,7 @@
         <v>44753</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20107,7 +20107,7 @@
         <v>45394</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20180,7 +20180,7 @@
         <v>45176</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20253,7 +20253,7 @@
         <v>45085</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45394</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45323</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20472,7 +20472,7 @@
         <v>45097</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44883</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>44984</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45152</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>45034</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>44938</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44881</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20983,7 +20983,7 @@
         <v>44951</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45036</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21129,7 +21129,7 @@
         <v>44691</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>44545</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45203</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21348,7 +21348,7 @@
         <v>45154</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21421,7 +21421,7 @@
         <v>44993</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21494,7 +21494,7 @@
         <v>45107</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21567,7 +21567,7 @@
         <v>45049</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21640,7 +21640,7 @@
         <v>45247</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21713,7 +21713,7 @@
         <v>44945</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21786,7 +21786,7 @@
         <v>44949</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21859,7 +21859,7 @@
         <v>45709</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21937,7 +21937,7 @@
         <v>45349</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45170</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22083,7 +22083,7 @@
         <v>45238</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>45036</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22229,7 +22229,7 @@
         <v>44950</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>46031</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45897</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45887</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45890</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45903</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45240</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22745,7 +22745,7 @@
         <v>45553</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>45897</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22896,7 +22896,7 @@
         <v>45742</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>45834</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23042,7 +23042,7 @@
         <v>45103</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23115,7 +23115,7 @@
         <v>45908</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23188,7 +23188,7 @@
         <v>45933</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45755</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23334,7 +23334,7 @@
         <v>45722</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23407,7 +23407,7 @@
         <v>45210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23480,7 +23480,7 @@
         <v>46035</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45183</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23626,7 +23626,7 @@
         <v>45183</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>44728</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45671</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>45474</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45884</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>44489</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24064,7 +24064,7 @@
         <v>44964</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24137,7 +24137,7 @@
         <v>45267</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24210,7 +24210,7 @@
         <v>45260</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24283,7 +24283,7 @@
         <v>45981</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45803</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24429,7 +24429,7 @@
         <v>45329</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24507,7 +24507,7 @@
         <v>46136</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24580,7 +24580,7 @@
         <v>45896</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24653,7 +24653,7 @@
         <v>44631</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24726,7 +24726,7 @@
         <v>45299</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24799,7 +24799,7 @@
         <v>45992</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>44936</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24945,7 +24945,7 @@
         <v>44936</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25018,7 +25018,7 @@
         <v>45180</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>46010</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25164,7 +25164,7 @@
         <v>46010</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25237,7 +25237,7 @@
         <v>45924</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25310,7 +25310,7 @@
         <v>45711</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45727</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25456,7 +25456,7 @@
         <v>45278</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25529,7 +25529,7 @@
         <v>44852</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>45758</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45467</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25753,7 +25753,7 @@
         <v>45467</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>45467</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45904</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25972,7 +25972,7 @@
         <v>45443</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26045,7 +26045,7 @@
         <v>45646</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26118,7 +26118,7 @@
         <v>45904</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26196,7 +26196,7 @@
         <v>45905</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26269,7 +26269,7 @@
         <v>45792</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26342,7 +26342,7 @@
         <v>45789</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45908</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>45082</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>45082</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>44634</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45035</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45553</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>45445</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>45923</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>45342</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>45923</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>44991</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>45548</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>44904</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45062</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>44964</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>45012</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45162</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>45412</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>44909</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         <v>46148</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27875,7 +27875,7 @@
         <v>44928</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>46149</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45211</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28094,7 +28094,7 @@
         <v>44965</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45933</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44790</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45938</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45264</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44888</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45093</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44895</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>45700</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45107</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>45069</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>45574</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>44935</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         <v>45631</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29121,7 +29121,7 @@
         <v>45002</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29194,7 +29194,7 @@
         <v>45408</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>45229</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29340,7 +29340,7 @@
         <v>45953</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29413,7 +29413,7 @@
         <v>46043</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29491,7 +29491,7 @@
         <v>45191</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29564,7 +29564,7 @@
         <v>45902</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>46154</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29710,7 +29710,7 @@
         <v>45547</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29783,7 +29783,7 @@
         <v>44518</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29856,7 +29856,7 @@
         <v>45264</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>45264</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45106</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>46160</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30148,7 +30148,7 @@
         <v>45618</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>45407</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45539</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>44967</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>44967</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>45574</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44930</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45097</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45972</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30810,7 +30810,7 @@
         <v>46162</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30883,7 +30883,7 @@
         <v>46162</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30956,7 +30956,7 @@
         <v>45331</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>44950</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31102,7 +31102,7 @@
         <v>44599</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31175,7 +31175,7 @@
         <v>45439</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31248,7 +31248,7 @@
         <v>44988</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45688</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31394,7 +31394,7 @@
         <v>45432</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31467,7 +31467,7 @@
         <v>45727</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31540,7 +31540,7 @@
         <v>45979</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31613,7 +31613,7 @@
         <v>45412</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31686,7 +31686,7 @@
         <v>44756</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31759,7 +31759,7 @@
         <v>44953</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31832,7 +31832,7 @@
         <v>46167</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>44599</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>45002</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45980</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>46167</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45982</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>45533</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>45462</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>44993</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45735</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>45735</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32635,7 +32635,7 @@
         <v>45568</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>45325</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32781,7 +32781,7 @@
         <v>46167</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>46167</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>44930</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>45434</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45117</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45117</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45395</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>45173</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45090</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>45082</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45201</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>45993</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45552</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>46168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>46168</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>46168</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>44657</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45629</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45062</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45077</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>44769</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>45600</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>46000</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45331</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44916</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45002</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45002</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45439</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>46171</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34903,7 +34903,7 @@
         <v>46007</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>44995</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45117</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45129</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45547</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45121</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>45574</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45726</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>44930</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>45635</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35643,7 +35643,7 @@
         <v>45629</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35716,7 +35716,7 @@
         <v>44930</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45005</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45005</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35935,7 +35935,7 @@
         <v>45330</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36008,7 +36008,7 @@
         <v>44550</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36081,7 +36081,7 @@
         <v>45261</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>46175</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>44495</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>45429</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>44545</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45691</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36524,7 +36524,7 @@
         <v>46031</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>45469</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>45106</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>45261</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46175</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>44705</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>46176</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46036</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37113,7 +37113,7 @@
         <v>46038</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>46038</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37259,7 +37259,7 @@
         <v>46038</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37332,7 +37332,7 @@
         <v>45609</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37405,7 +37405,7 @@
         <v>46177</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37478,7 +37478,7 @@
         <v>44831</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37551,7 +37551,7 @@
         <v>44831</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>44960</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37697,7 +37697,7 @@
         <v>46182</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37770,7 +37770,7 @@
         <v>45356</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37848,7 +37848,7 @@
         <v>46048</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37921,7 +37921,7 @@
         <v>45197</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>46182</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>46182</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>45007</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45408</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>44627</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>46175</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46181</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>45601</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45546</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>45307</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38729,7 +38729,7 @@
         <v>46184</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>46063</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38875,7 +38875,7 @@
         <v>46063</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38948,7 +38948,7 @@
         <v>46135</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>46146</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45540</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>45540</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>46184</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>45300</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39386,7 +39386,7 @@
         <v>44939</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39459,7 +39459,7 @@
         <v>46188</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39532,7 +39532,7 @@
         <v>44895</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>44916</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39678,7 +39678,7 @@
         <v>44655</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39751,7 +39751,7 @@
         <v>44936</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>44936</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39897,7 +39897,7 @@
         <v>46078</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45160</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45401</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40116,7 +40116,7 @@
         <v>44748</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40189,7 +40189,7 @@
         <v>45139</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40262,7 +40262,7 @@
         <v>46190</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40335,7 +40335,7 @@
         <v>44820</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>46083</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>46083</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>46083</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40627,7 +40627,7 @@
         <v>45078</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45078</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>46083</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>45106</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>46086</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -40992,7 +40992,7 @@
         <v>45215</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41065,7 +41065,7 @@
         <v>45109</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>44673</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>46090</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>44945</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>44728</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45007</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>46189</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>44907</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>45684</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>46098</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>46104</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>46101</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45063</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>46101</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>45644</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45302</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42233,7 +42233,7 @@
         <v>44820</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>46106</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>45215</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45245</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>46108</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42603,7 +42603,7 @@
         <v>46108</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42676,7 +42676,7 @@
         <v>44963</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42749,7 +42749,7 @@
         <v>46198</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>46108</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42895,7 +42895,7 @@
         <v>46197</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42968,7 +42968,7 @@
         <v>45155</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43041,7 +43041,7 @@
         <v>45085</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43114,7 +43114,7 @@
         <v>45439</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43187,7 +43187,7 @@
         <v>46120</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>46119</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43333,7 +43333,7 @@
         <v>46199</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43406,7 +43406,7 @@
         <v>45034</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45394</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>44624</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44928</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>45267</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45418</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43849,7 +43849,7 @@
         <v>45426</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43922,7 +43922,7 @@
         <v>45264</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -43995,7 +43995,7 @@
         <v>46120</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45314</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>46105</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44214,7 +44214,7 @@
         <v>44875</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44287,7 +44287,7 @@
         <v>44505</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44360,7 +44360,7 @@
         <v>45614</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>44620</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>46132</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44584,7 +44584,7 @@
         <v>45261</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44657,7 +44657,7 @@
         <v>46132</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44730,7 +44730,7 @@
         <v>45384</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44803,7 +44803,7 @@
         <v>45436</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>46204</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44954,7 +44954,7 @@
         <v>46204</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45032,7 +45032,7 @@
         <v>46204</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45110,7 +45110,7 @@
         <v>45394</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45183,7 +45183,7 @@
         <v>46204</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45256,7 +45256,7 @@
         <v>45782</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>46134</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>46203</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45475,7 +45475,7 @@
         <v>44911</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45548,7 +45548,7 @@
         <v>45902</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45992</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45694,7 +45694,7 @@
         <v>45596</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45767,7 +45767,7 @@
         <v>45821</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45840,7 +45840,7 @@
         <v>45873</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45913,7 +45913,7 @@
         <v>45099</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>45755</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>46003</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>45155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>45547</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>45841</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>45579</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45568</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>45926</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45063</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>45772</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>45474</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>44838</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>46206</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46955,7 +46955,7 @@
         <v>46206</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47028,7 +47028,7 @@
         <v>46206</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47101,7 +47101,7 @@
         <v>45674</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47174,7 +47174,7 @@
         <v>45637</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47252,7 +47252,7 @@
         <v>45637</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47330,7 +47330,7 @@
         <v>44700</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47403,7 +47403,7 @@
         <v>45424</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47476,7 +47476,7 @@
         <v>45240</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>44524</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47622,7 +47622,7 @@
         <v>46212</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45226</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47768,7 +47768,7 @@
         <v>45314</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47841,7 +47841,7 @@
         <v>45009</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47919,7 +47919,7 @@
         <v>45540</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47992,7 +47992,7 @@
         <v>44949</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48065,7 +48065,7 @@
         <v>46213</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48138,7 +48138,7 @@
         <v>46213</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48211,7 +48211,7 @@
         <v>45236</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>46213</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45614</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>46189</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>46045</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48581,7 +48581,7 @@
         <v>45110</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48654,7 +48654,7 @@
         <v>44994</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48727,7 +48727,7 @@
         <v>46209</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48805,7 +48805,7 @@
         <v>44621</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48878,7 +48878,7 @@
         <v>44903</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48951,7 +48951,7 @@
         <v>44489</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49024,7 +49024,7 @@
         <v>45201</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49097,7 +49097,7 @@
         <v>46191</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49170,7 +49170,7 @@
         <v>45436</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>45432</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>45386</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45439</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>44628</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49540,7 +49540,7 @@
         <v>44614</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49613,7 +49613,7 @@
         <v>46120</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49686,7 +49686,7 @@
         <v>45119</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
         <v>45152</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49832,7 +49832,7 @@
         <v>45680</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45574</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45215</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50051,7 +50051,7 @@
         <v>46274</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>45547</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50202,7 +50202,7 @@
         <v>44795</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50275,7 +50275,7 @@
         <v>45449</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50348,7 +50348,7 @@
         <v>45449</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50421,7 +50421,7 @@
         <v>45240</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50494,7 +50494,7 @@
         <v>45240</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50567,7 +50567,7 @@
         <v>45166</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50640,7 +50640,7 @@
         <v>44984</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50713,7 +50713,7 @@
         <v>45155</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45112</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50859,7 +50859,7 @@
         <v>44960</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50932,7 +50932,7 @@
         <v>44620</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -51005,7 +51005,7 @@
         <v>44867</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51078,7 +51078,7 @@
         <v>45188</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45370</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45411</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>46279</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>45559</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>45329</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51526,7 +51526,7 @@
         <v>45406</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>45091</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>45546</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51745,7 +51745,7 @@
         <v>45264</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51818,7 +51818,7 @@
         <v>44698</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51891,7 +51891,7 @@
         <v>44627</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>44602</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>45176</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52110,7 +52110,7 @@
         <v>44904</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45051</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>44685</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>44685</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>46287</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>45035</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>44949</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45138</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52694,7 +52694,7 @@
         <v>44984</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52767,7 +52767,7 @@
         <v>45062</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52840,7 +52840,7 @@
         <v>44712</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52913,7 +52913,7 @@
         <v>45176</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>45252</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>45252</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53132,7 +53132,7 @@
         <v>45331</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53205,7 +53205,7 @@
         <v>45331</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53278,7 +53278,7 @@
         <v>45331</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45005</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>46244</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53497,7 +53497,7 @@
         <v>46202</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53570,7 +53570,7 @@
         <v>45117</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53643,7 +53643,7 @@
         <v>44657</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53716,7 +53716,7 @@
         <v>45303</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53789,7 +53789,7 @@
         <v>44972</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53862,7 +53862,7 @@
         <v>45109</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53935,7 +53935,7 @@
         <v>44575</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -54008,7 +54008,7 @@
         <v>45071</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54081,7 +54081,7 @@
         <v>45071</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54154,7 +54154,7 @@
         <v>45392</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54227,7 +54227,7 @@
         <v>45183</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54300,7 +54300,7 @@
         <v>44950</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54373,7 +54373,7 @@
         <v>44988</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54446,7 +54446,7 @@
         <v>45071</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54519,7 +54519,7 @@
         <v>45096</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54592,7 +54592,7 @@
         <v>46147</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54665,7 +54665,7 @@
         <v>46293</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54738,7 +54738,7 @@
         <v>44967</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45978</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>44901</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>44901</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>46293</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>46293</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55181,7 +55181,7 @@
         <v>45386</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55254,7 +55254,7 @@
         <v>45082</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>45182</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45674</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>45601</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>44998</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55619,7 +55619,7 @@
         <v>45188</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55692,7 +55692,7 @@
         <v>46294</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55765,7 +55765,7 @@
         <v>45371</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55838,7 +55838,7 @@
         <v>46251</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>45572</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>45327</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56067,7 +56067,7 @@
         <v>44620</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56145,7 +56145,7 @@
         <v>45755</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56218,7 +56218,7 @@
         <v>45607</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56291,7 +56291,7 @@
         <v>45713</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56364,7 +56364,7 @@
         <v>45124</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56437,7 +56437,7 @@
         <v>46120</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56510,7 +56510,7 @@
         <v>45616</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56583,7 +56583,7 @@
         <v>45275</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56656,7 +56656,7 @@
         <v>45175</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56729,7 +56729,7 @@
         <v>45338</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56802,7 +56802,7 @@
         <v>44748</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56875,7 +56875,7 @@
         <v>45646</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56948,7 +56948,7 @@
         <v>45574</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -57021,7 +57021,7 @@
         <v>45562</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57094,7 +57094,7 @@
         <v>45615</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57167,7 +57167,7 @@
         <v>45419</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57240,7 +57240,7 @@
         <v>45519</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57313,7 +57313,7 @@
         <v>45089</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>45670</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>45602</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45553</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>46044</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57683,7 +57683,7 @@
         <v>45782</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57756,7 +57756,7 @@
         <v>45546</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45784</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57902,7 +57902,7 @@
         <v>45709</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57975,7 +57975,7 @@
         <v>46300</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58048,7 +58048,7 @@
         <v>45784</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58121,7 +58121,7 @@
         <v>45176</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58194,7 +58194,7 @@
         <v>46301</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58267,7 +58267,7 @@
         <v>44783</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58340,7 +58340,7 @@
         <v>45266</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58418,7 +58418,7 @@
         <v>45712</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58491,7 +58491,7 @@
         <v>45679</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58564,7 +58564,7 @@
         <v>45789</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45679</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58710,7 +58710,7 @@
         <v>45230</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58783,7 +58783,7 @@
         <v>44783</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45568</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58929,7 +58929,7 @@
         <v>45511</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45950</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59075,7 +59075,7 @@
         <v>45636</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59153,7 +59153,7 @@
         <v>46303</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59226,7 +59226,7 @@
         <v>45345</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59299,7 +59299,7 @@
         <v>45252</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59372,7 +59372,7 @@
         <v>45594</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59445,7 +59445,7 @@
         <v>45345</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59518,7 +59518,7 @@
         <v>46303</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59591,7 +59591,7 @@
         <v>46303</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59664,7 +59664,7 @@
         <v>45562</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59737,7 +59737,7 @@
         <v>45590</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59810,7 +59810,7 @@
         <v>45597</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59883,7 +59883,7 @@
         <v>45637</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59961,7 +59961,7 @@
         <v>45576</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -60034,7 +60034,7 @@
         <v>45565</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60107,7 +60107,7 @@
         <v>45524</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>46260</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>45670</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60326,7 +60326,7 @@
         <v>46293</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60399,7 +60399,7 @@
         <v>46260</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60472,7 +60472,7 @@
         <v>46260</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60545,7 +60545,7 @@
         <v>45113</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>46031</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60691,7 +60691,7 @@
         <v>45793</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60764,7 +60764,7 @@
         <v>45793</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60837,7 +60837,7 @@
         <v>46307</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60910,7 +60910,7 @@
         <v>46000</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60983,7 +60983,7 @@
         <v>46148</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61056,7 +61056,7 @@
         <v>45477</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61129,7 +61129,7 @@
         <v>45533</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61202,7 +61202,7 @@
         <v>45692</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61275,7 +61275,7 @@
         <v>46262</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61348,7 +61348,7 @@
         <v>46262</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61421,7 +61421,7 @@
         <v>45478</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61494,7 +61494,7 @@
         <v>45684</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61567,7 +61567,7 @@
         <v>45637</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61645,7 +61645,7 @@
         <v>46266</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61718,7 +61718,7 @@
         <v>46308</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61791,7 +61791,7 @@
         <v>46308</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61864,7 +61864,7 @@
         <v>45727</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61937,7 +61937,7 @@
         <v>46195</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -62010,7 +62010,7 @@
         <v>46195</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62083,7 +62083,7 @@
         <v>46195</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62156,7 +62156,7 @@
         <v>45811</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62229,7 +62229,7 @@
         <v>45793</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62302,7 +62302,7 @@
         <v>45820</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62375,7 +62375,7 @@
         <v>45827</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62448,7 +62448,7 @@
         <v>46310</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62521,7 +62521,7 @@
         <v>45831</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62594,7 +62594,7 @@
         <v>45831</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62667,7 +62667,7 @@
         <v>45832</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62740,7 +62740,7 @@
         <v>44609</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62818,7 +62818,7 @@
         <v>45838</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62891,7 +62891,7 @@
         <v>45839</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62964,7 +62964,7 @@
         <v>45434</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -63037,7 +63037,7 @@
         <v>45841</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63110,7 +63110,7 @@
         <v>45677</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63188,7 +63188,7 @@
         <v>45841</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63261,7 +63261,7 @@
         <v>45751</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63334,7 +63334,7 @@
         <v>45684</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63407,7 +63407,7 @@
         <v>45090</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63480,7 +63480,7 @@
         <v>45644</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63553,7 +63553,7 @@
         <v>45873</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63626,7 +63626,7 @@
         <v>45873</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63699,7 +63699,7 @@
         <v>45873</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63772,7 +63772,7 @@
         <v>45874</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63845,7 +63845,7 @@
         <v>45877</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63918,7 +63918,7 @@
         <v>45881</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63991,7 +63991,7 @@
         <v>45881</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -64064,7 +64064,7 @@
         <v>45387</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64137,7 +64137,7 @@
         <v>45387</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64210,7 +64210,7 @@
         <v>45456</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64283,7 +64283,7 @@
         <v>45602</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64356,7 +64356,7 @@
         <v>44894</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>45443</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>44672</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64575,7 +64575,7 @@
         <v>44888</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64648,7 +64648,7 @@
         <v>44900</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64721,7 +64721,7 @@
         <v>45359</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64794,7 +64794,7 @@
         <v>45359</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64867,7 +64867,7 @@
         <v>44722</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64940,7 +64940,7 @@
         <v>45387</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -65013,7 +65013,7 @@
         <v>45128</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -65086,7 +65086,7 @@
         <v>45387</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65159,7 +65159,7 @@
         <v>45362</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65232,7 +65232,7 @@
         <v>45534</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65305,7 +65305,7 @@
         <v>44901</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65378,7 +65378,7 @@
         <v>44792</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65456,7 +65456,7 @@
         <v>45362</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65529,7 +65529,7 @@
         <v>45330</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65602,7 +65602,7 @@
         <v>44883</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65675,7 +65675,7 @@
         <v>45330</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65748,7 +65748,7 @@
         <v>44928</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65821,7 +65821,7 @@
         <v>45477</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65894,7 +65894,7 @@
         <v>44971</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65967,7 +65967,7 @@
         <v>44900</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -66040,7 +66040,7 @@
         <v>44971</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66113,7 +66113,7 @@
         <v>45230</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66186,7 +66186,7 @@
         <v>45730</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66259,7 +66259,7 @@
         <v>45665</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66332,7 +66332,7 @@
         <v>45727</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66405,7 +66405,7 @@
         <v>45665</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66478,7 +66478,7 @@
         <v>45807</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66551,7 +66551,7 @@
         <v>45807</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66624,7 +66624,7 @@
         <v>46038</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66697,7 +66697,7 @@
         <v>46042</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66770,7 +66770,7 @@
         <v>46042</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66843,7 +66843,7 @@
         <v>46042</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66916,7 +66916,7 @@
         <v>46042</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66989,7 +66989,7 @@
         <v>46045</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -67062,7 +67062,7 @@
         <v>46132</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67135,7 +67135,7 @@
         <v>46181</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -67208,7 +67208,7 @@
         <v>46188</v>
       </c>
       <c r="E886" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -67281,7 +67281,7 @@
         <v>46213</v>
       </c>
       <c r="E887" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>44740</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45061</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>44992</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45565</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45387</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>46050</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46300</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45810</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>44872</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44599</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44756</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44578</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45646</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44984</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>45341</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45322</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45461</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>46289</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>46293</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>46086</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44992</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>46301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>45001</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>44729</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45580</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45103</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45406</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45387</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45330</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45467</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45153</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45555</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45890</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>46056</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44888</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44557</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44732</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44620</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>44813</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>44875</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44539</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>44755</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44713</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44524</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44865</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44753</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44533</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44819</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44570</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44641</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44690</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44865</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44791</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44644</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44603</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44627</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44804</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44789</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>44508</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>44546</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44722</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44867</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44511</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44879</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>44791</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44875</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>44532</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44879</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44494</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44529</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44648</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>44631</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>44798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44608</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>44620</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>44620</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44636</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>44519</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44791</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44748</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44888</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44494</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44509</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44533</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44722</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44522</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44698</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44680</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44631</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44523</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44749</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44711</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44753</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44540</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44676</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44620</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44540</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44875</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44698</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44685</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44641</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44539</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44631</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44753</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44523</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45568</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45240</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44712</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45671</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45267</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45887</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44596</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45188</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45338</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45412</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45062</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45395</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45553</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45362</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45002</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45329</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45173</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44769</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45600</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>44820</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>44938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44909</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>44698</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>45331</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45331</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45331</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45155</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44728</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44509</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>45359</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45036</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45646</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45443</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>44875</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>45384</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45447</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>44818</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45904</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>44930</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>45180</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45792</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45789</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45905</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>45908</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>44631</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44900</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45474</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45574</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44904</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45261</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>46162</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>44967</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>44518</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45607</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45547</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>45086</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45674</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>46162</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45005</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45005</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45252</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>46167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>46167</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45701</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45395</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>46168</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45547</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>46168</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45923</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>46168</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>45923</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>46167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>46167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45702</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45548</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44965</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44964</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>44712</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>46171</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45097</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45629</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45091</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45051</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44599</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45033</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45933</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>46175</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45129</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44895</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44916</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>44972</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45938</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45601</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>46175</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45680</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45252</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>46176</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45139</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45300</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45117</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45117</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>46177</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45082</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45646</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45449</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45449</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44888</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44883</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45394</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45089</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45117</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45117</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46175</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45377</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>46181</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46182</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46146</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46135</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>46182</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>46184</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45953</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45215</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45394</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45035</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45401</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>46184</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45439</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>46182</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44984</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45688</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45279</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45331</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45467</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45467</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45467</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45455</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45240</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>46188</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>44949</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>46190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45601</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45574</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>46189</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45972</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45356</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>46197</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45755</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45727</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45426</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44935</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45034</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45002</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45418</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45124</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44928</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>46198</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>44960</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>46199</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>46204</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>45553</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>45979</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44634</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45394</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>46203</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>46204</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46204</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>46204</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45477</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45462</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45982</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45439</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45691</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45559</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45637</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45637</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45533</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44903</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>45615</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>46206</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45540</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>46206</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45386</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>46212</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45194</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>46213</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45085</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45445</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>46213</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45993</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>46213</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>44950</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45327</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45432</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46189</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45434</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>46000</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45408</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45349</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>46209</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>46045</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45274</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45670</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>45562</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45419</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45519</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>45574</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45089</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45602</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>45615</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45782</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>46191</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45784</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45553</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>45432</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>46120</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45784</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45594</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>46007</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45252</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45590</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>46279</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45546</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45679</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45709</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45176</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45670</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45679</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44783</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45726</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45568</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45562</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45511</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45636</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45597</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45524</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45576</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>45565</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>44783</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45230</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45789</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45712</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45345</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45637</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45345</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>46031</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>46036</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45793</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>46038</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>46038</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>46038</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45154</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45436</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45152</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45793</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>46202</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>46244</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>46048</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45692</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>46287</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45478</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45533</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45477</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45637</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45684</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45727</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>44545</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>46147</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45978</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>46293</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45811</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>46063</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>46063</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>46293</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>46293</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46294</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45820</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45793</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45310</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>46251</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>46078</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45827</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>46083</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>45831</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>46083</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>46083</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>46083</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>44609</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45831</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45832</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45475</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>46086</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45838</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45434</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>46090</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45839</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45841</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45841</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>46098</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>46101</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>46300</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>46120</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>46101</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45436</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46104</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46293</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45005</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>46106</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45751</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>46301</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>46044</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>46108</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>46108</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>46108</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>44936</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>44936</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>46303</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>45684</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>46031</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45090</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45246</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45644</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>46303</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>46119</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>46120</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45113</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>46303</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>46260</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>46260</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45644</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45873</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45873</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45874</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>46260</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45873</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45950</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>46120</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>46132</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45394</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45877</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>46307</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45881</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45881</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>46105</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>46132</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>44911</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45329</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>44895</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45540</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>46134</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>46262</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45362</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>46262</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>45782</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45897</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>46000</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46148</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>45992</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45553</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44907</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>45539</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45803</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>46308</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>45897</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45924</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>44599</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45596</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45755</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46308</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46010</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45742</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>45908</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45884</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45474</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45933</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>45981</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>46136</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45834</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44930</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45841</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>46003</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>46266</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>45711</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>46010</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>44995</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45926</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45155</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45890</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>46310</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45299</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>46195</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>46195</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>46195</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45902</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>46314</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45903</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>44928</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45063</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45007</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>44971</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45873</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45012</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45014</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>44676</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44950</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44965</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44945</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45821</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45264</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45264</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44939</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>46035</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45029</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>46304</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45755</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45240</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>44936</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>44936</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45278</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45568</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>44617</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>46031</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45155</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45155</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>44620</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>46274</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45614</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>46317</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45439</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45904</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45758</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45637</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44928</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45071</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45344</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>46148</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>44928</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45162</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>44963</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45091</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>46149</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>44685</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44685</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>44993</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>46154</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>45182</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45077</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>44673</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45614</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45107</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>44620</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>46043</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45902</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45700</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45034</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>46160</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45579</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45574</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45574</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45580</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>44984</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45323</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45307</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45007</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45608</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45461</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44545</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45119</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45062</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45009</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>44993</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45096</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45610</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45674</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45093</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>44998</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45547</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>44951</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47922,7 +47922,7 @@
         <v>45552</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45629</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>44748</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45701</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         <v>45099</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45469</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45617</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>45121</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45722</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44994</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>44495</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>44505</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45062</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45078</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>45036</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45035</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>44529</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>44930</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45167</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45188</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>45710</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>44937</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>45188</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45772</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>44991</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>44991</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>45247</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45247</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>44988</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45110</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>45244</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45063</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45002</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>44930</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>44627</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45264</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45071</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45071</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45071</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45260</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>44631</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45112</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45735</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51061,7 +51061,7 @@
         <v>45735</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51134,7 +51134,7 @@
         <v>45466</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44790</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51280,7 +51280,7 @@
         <v>45082</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45082</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>45106</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>44916</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51572,7 +51572,7 @@
         <v>45261</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         <v>45709</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45439</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>45229</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45407</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>45075</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45110</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52093,7 +52093,7 @@
         <v>45107</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45261</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52239,7 +52239,7 @@
         <v>45103</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>45183</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>45034</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>45170</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>44895</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>45330</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52677,7 +52677,7 @@
         <v>44960</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52750,7 +52750,7 @@
         <v>44967</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45370</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45240</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>44953</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>44904</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45325</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45107</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>44949</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>44949</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45002</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45314</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45392</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45069</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>45275</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>44838</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>44545</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>44945</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>44524</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>44881</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>45424</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45019</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>44930</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45049</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45097</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45546</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>44964</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45166</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45546</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>44558</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>44540</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>45342</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>44575</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>44620</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45160</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>45274</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55315,7 +55315,7 @@
         <v>45155</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>45155</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>45635</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>45540</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55612,7 +55612,7 @@
         <v>45631</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>44795</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45033</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>44570</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>44550</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55977,7 +55977,7 @@
         <v>45107</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>44586</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45631</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45152</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>45078</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45727</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>44683</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45618</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45408</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45175</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45203</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45082</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>45191</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>45106</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45085</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>45107</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>44627</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>44624</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45547</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45176</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>45215</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57510,7 +57510,7 @@
         <v>45609</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>44621</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>44614</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>45210</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>45215</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57875,7 +57875,7 @@
         <v>45147</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>45138</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58021,7 +58021,7 @@
         <v>45713</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58094,7 +58094,7 @@
         <v>45090</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>44820</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>45635</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58318,7 +58318,7 @@
         <v>45244</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58391,7 +58391,7 @@
         <v>45574</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58464,7 +58464,7 @@
         <v>45245</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58537,7 +58537,7 @@
         <v>45211</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>44657</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58683,7 +58683,7 @@
         <v>45684</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58756,7 +58756,7 @@
         <v>45183</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58829,7 +58829,7 @@
         <v>45183</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>45117</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>44749</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>44728</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>44728</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59194,7 +59194,7 @@
         <v>45173</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59267,7 +59267,7 @@
         <v>44655</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59340,7 +59340,7 @@
         <v>45226</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>44700</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>45181</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>44705</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59632,7 +59632,7 @@
         <v>44852</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>44753</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45164</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>45164</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45197</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>45264</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>45117</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45236</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45331</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>45303</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>45238</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45109</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>45109</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>45302</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>45775</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>44804</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60800,7 +60800,7 @@
         <v>45306</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>45314</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>44804</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61019,7 +61019,7 @@
         <v>45176</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         <v>45366</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61165,7 +61165,7 @@
         <v>44756</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61238,7 +61238,7 @@
         <v>44901</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61311,7 +61311,7 @@
         <v>44901</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61384,7 +61384,7 @@
         <v>45267</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61457,7 +61457,7 @@
         <v>45399</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61530,7 +61530,7 @@
         <v>44904</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61603,7 +61603,7 @@
         <v>44867</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61676,7 +61676,7 @@
         <v>44950</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>44831</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>44831</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61895,7 +61895,7 @@
         <v>44522</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61973,7 +61973,7 @@
         <v>45082</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62046,7 +62046,7 @@
         <v>45327</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45272</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62197,7 +62197,7 @@
         <v>45264</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62270,7 +62270,7 @@
         <v>45201</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>44748</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>44691</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>45303</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62562,7 +62562,7 @@
         <v>45616</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45429</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62708,7 +62708,7 @@
         <v>45201</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62781,7 +62781,7 @@
         <v>45574</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62854,7 +62854,7 @@
         <v>45386</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62927,7 +62927,7 @@
         <v>45412</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -63000,7 +63000,7 @@
         <v>44984</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45371</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63146,7 +63146,7 @@
         <v>45406</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63219,7 +63219,7 @@
         <v>44602</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63292,7 +63292,7 @@
         <v>44657</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63365,7 +63365,7 @@
         <v>44967</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63438,7 +63438,7 @@
         <v>45572</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63511,7 +63511,7 @@
         <v>44628</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63584,7 +63584,7 @@
         <v>44967</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63662,7 +63662,7 @@
         <v>44939</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63735,7 +63735,7 @@
         <v>44988</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63808,7 +63808,7 @@
         <v>44672</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63881,7 +63881,7 @@
         <v>44722</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63954,7 +63954,7 @@
         <v>45387</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -64027,7 +64027,7 @@
         <v>45387</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64100,7 +64100,7 @@
         <v>45456</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64173,7 +64173,7 @@
         <v>45602</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64246,7 +64246,7 @@
         <v>44894</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64319,7 +64319,7 @@
         <v>45443</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64392,7 +64392,7 @@
         <v>44888</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64465,7 +64465,7 @@
         <v>44900</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>45359</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64611,7 +64611,7 @@
         <v>45359</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>45387</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64757,7 +64757,7 @@
         <v>45128</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>45387</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>45362</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>45534</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>44901</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>44792</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45362</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>45330</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>44883</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>45330</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>44928</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65565,7 +65565,7 @@
         <v>45477</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         <v>44971</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>44900</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>44971</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>45230</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65930,7 +65930,7 @@
         <v>45730</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>45665</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>45727</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45665</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66222,7 +66222,7 @@
         <v>45807</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66295,7 +66295,7 @@
         <v>45807</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66368,7 +66368,7 @@
         <v>46038</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66441,7 +66441,7 @@
         <v>46042</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66514,7 +66514,7 @@
         <v>46042</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66587,7 +66587,7 @@
         <v>46042</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66660,7 +66660,7 @@
         <v>46042</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>46045</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66806,7 +66806,7 @@
         <v>46132</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66879,7 +66879,7 @@
         <v>46181</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66952,7 +66952,7 @@
         <v>46188</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>46213</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67098,7 +67098,7 @@
         <v>46314</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>

--- a/Översikt TINGSRYD.xlsx
+++ b/Översikt TINGSRYD.xlsx
@@ -601,7 +601,7 @@
         <v>45208</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>44582</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
         <v>45128</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -960,7 +960,7 @@
         <v>46196</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1069,7 +1069,7 @@
         <v>44740</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>45061</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
         <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1402,7 +1402,7 @@
         <v>45705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         <v>46155</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>44992</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>45565</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>44900</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>46239</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>45387</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         <v>46050</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46300</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>45810</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>44872</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         <v>45099</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>44756</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3025,7 +3025,7 @@
         <v>44599</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>44756</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>44578</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3357,7 +3357,7 @@
         <v>45646</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>44984</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>45341</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         <v>45322</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>46213</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45461</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>46289</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>46293</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>46086</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>44992</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>46301</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         <v>45001</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4631,7 +4631,7 @@
         <v>44729</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4736,7 +4736,7 @@
         <v>45580</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>45103</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>45546</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45182</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45406</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>45387</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45330</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45467</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>45153</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
         <v>45555</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>45890</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>46056</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44888</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44557</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44732</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44841</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44875</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44620</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44620</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>44813</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6593,7 +6593,7 @@
         <v>44508</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>44875</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         <v>44539</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6812,7 +6812,7 @@
         <v>44755</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>44713</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         <v>44524</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44865</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44753</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44533</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44575</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         <v>44819</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>44570</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         <v>44494</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7615,7 +7615,7 @@
         <v>44641</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         <v>44692</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>44690</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>44865</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7907,7 +7907,7 @@
         <v>44610</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7980,7 +7980,7 @@
         <v>44791</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
         <v>44644</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8126,7 +8126,7 @@
         <v>44603</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8199,7 +8199,7 @@
         <v>44627</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>44804</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44789</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8418,7 +8418,7 @@
         <v>44508</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8491,7 +8491,7 @@
         <v>44546</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8564,7 +8564,7 @@
         <v>44722</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8637,7 +8637,7 @@
         <v>44722</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>44867</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8783,7 +8783,7 @@
         <v>44511</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8856,7 +8856,7 @@
         <v>44839</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>44879</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9007,7 +9007,7 @@
         <v>44791</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         <v>44875</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>44532</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         <v>44879</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9299,7 +9299,7 @@
         <v>44595</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>44494</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>44529</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44648</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>44631</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>44798</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>44608</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>44620</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>44620</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9966,7 +9966,7 @@
         <v>44636</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>44519</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>44791</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44748</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>44888</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44820</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>44494</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44509</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>44533</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44722</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44522</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44698</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10842,7 +10842,7 @@
         <v>44680</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>44631</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44523</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11061,7 +11061,7 @@
         <v>44749</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44711</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11207,7 +11207,7 @@
         <v>44753</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>44540</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>44676</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>44620</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44540</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>44875</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>44698</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44685</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44641</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44539</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44631</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>44753</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>44523</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45568</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45240</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>44712</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45671</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45267</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45887</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44596</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12667,7 +12667,7 @@
         <v>45188</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>45338</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12813,7 +12813,7 @@
         <v>45411</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45412</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45062</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45395</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45553</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45362</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45002</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45329</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45173</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13480,7 +13480,7 @@
         <v>44769</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>45896</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13626,7 +13626,7 @@
         <v>45600</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13699,7 +13699,7 @@
         <v>44820</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>44938</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13845,7 +13845,7 @@
         <v>44909</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>44698</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13991,7 +13991,7 @@
         <v>45331</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14064,7 +14064,7 @@
         <v>45331</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14137,7 +14137,7 @@
         <v>45331</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45155</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44728</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>44509</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45176</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>45359</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>45036</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>45646</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14721,7 +14721,7 @@
         <v>45443</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>44875</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14867,7 +14867,7 @@
         <v>45384</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14940,7 +14940,7 @@
         <v>45447</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>44818</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15086,7 +15086,7 @@
         <v>45904</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15164,7 +15164,7 @@
         <v>44930</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15237,7 +15237,7 @@
         <v>45180</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15310,7 +15310,7 @@
         <v>45792</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45789</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>45905</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15529,7 +15529,7 @@
         <v>45908</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15602,7 +15602,7 @@
         <v>44631</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44900</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>45474</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45574</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15894,7 +15894,7 @@
         <v>44904</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15967,7 +15967,7 @@
         <v>45261</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16040,7 +16040,7 @@
         <v>46162</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44967</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16186,7 +16186,7 @@
         <v>44967</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16264,7 +16264,7 @@
         <v>44518</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45607</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16410,7 +16410,7 @@
         <v>45547</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16483,7 +16483,7 @@
         <v>45086</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16556,7 +16556,7 @@
         <v>45674</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16629,7 +16629,7 @@
         <v>46162</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>45005</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16775,7 +16775,7 @@
         <v>45005</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>45252</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>46167</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16994,7 +16994,7 @@
         <v>46167</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17067,7 +17067,7 @@
         <v>45701</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45395</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>46168</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>45547</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17359,7 +17359,7 @@
         <v>46168</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45923</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17505,7 +17505,7 @@
         <v>46168</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>45923</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17651,7 +17651,7 @@
         <v>46167</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17724,7 +17724,7 @@
         <v>46167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17797,7 +17797,7 @@
         <v>45702</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17870,7 +17870,7 @@
         <v>45548</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17943,7 +17943,7 @@
         <v>45106</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18016,7 +18016,7 @@
         <v>44965</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>44964</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18162,7 +18162,7 @@
         <v>44712</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18235,7 +18235,7 @@
         <v>46171</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18313,7 +18313,7 @@
         <v>45097</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45629</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18459,7 +18459,7 @@
         <v>45091</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45051</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>44599</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>45033</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18751,7 +18751,7 @@
         <v>45933</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18824,7 +18824,7 @@
         <v>46175</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>45129</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18970,7 +18970,7 @@
         <v>44895</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19043,7 +19043,7 @@
         <v>44916</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>44972</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
         <v>45938</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19262,7 +19262,7 @@
         <v>45601</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19335,7 +19335,7 @@
         <v>46175</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19408,7 +19408,7 @@
         <v>45680</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19481,7 +19481,7 @@
         <v>45252</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19554,7 +19554,7 @@
         <v>46176</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19627,7 +19627,7 @@
         <v>45139</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
         <v>45300</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19773,7 +19773,7 @@
         <v>45117</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>45117</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>46177</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45082</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45646</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45449</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45449</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
         <v>44888</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20357,7 +20357,7 @@
         <v>44883</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20430,7 +20430,7 @@
         <v>45394</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20503,7 +20503,7 @@
         <v>45089</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>45117</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20649,7 +20649,7 @@
         <v>45117</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20722,7 +20722,7 @@
         <v>46175</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>45377</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>46181</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>46182</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46146</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46135</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>46182</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>46184</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>45953</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45215</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45394</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21525,7 +21525,7 @@
         <v>45035</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21598,7 +21598,7 @@
         <v>45401</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21671,7 +21671,7 @@
         <v>46184</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21744,7 +21744,7 @@
         <v>45439</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21817,7 +21817,7 @@
         <v>46182</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>44984</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>45688</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22036,7 +22036,7 @@
         <v>45279</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22109,7 +22109,7 @@
         <v>45331</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45467</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45467</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45467</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22401,7 +22401,7 @@
         <v>45455</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22474,7 +22474,7 @@
         <v>45240</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>46188</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22620,7 +22620,7 @@
         <v>44949</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22693,7 +22693,7 @@
         <v>46190</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22766,7 +22766,7 @@
         <v>45601</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22839,7 +22839,7 @@
         <v>45574</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22912,7 +22912,7 @@
         <v>46189</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22985,7 +22985,7 @@
         <v>45972</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
         <v>45356</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23136,7 +23136,7 @@
         <v>46197</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23209,7 +23209,7 @@
         <v>45755</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23282,7 +23282,7 @@
         <v>45727</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45426</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23428,7 +23428,7 @@
         <v>44935</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23501,7 +23501,7 @@
         <v>45034</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45002</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23647,7 +23647,7 @@
         <v>45418</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45124</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>44928</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23871,7 +23871,7 @@
         <v>46198</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23944,7 +23944,7 @@
         <v>44960</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24017,7 +24017,7 @@
         <v>46199</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24090,7 +24090,7 @@
         <v>46204</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24163,7 +24163,7 @@
         <v>45553</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>45979</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45980</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24382,7 +24382,7 @@
         <v>44634</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24455,7 +24455,7 @@
         <v>45394</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>46203</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24601,7 +24601,7 @@
         <v>46204</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>46204</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24757,7 +24757,7 @@
         <v>46204</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24835,7 +24835,7 @@
         <v>45477</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24908,7 +24908,7 @@
         <v>45462</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>45982</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25054,7 +25054,7 @@
         <v>45439</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>45691</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25205,7 +25205,7 @@
         <v>45559</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25278,7 +25278,7 @@
         <v>45637</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25356,7 +25356,7 @@
         <v>45637</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45533</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25507,7 +25507,7 @@
         <v>44903</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25580,7 +25580,7 @@
         <v>45615</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>46206</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25726,7 +25726,7 @@
         <v>46206</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25819,7 +25819,7 @@
         <v>45540</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25892,7 +25892,7 @@
         <v>46206</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25965,7 +25965,7 @@
         <v>45386</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26038,7 +26038,7 @@
         <v>46212</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45194</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>46213</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>45085</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26330,7 +26330,7 @@
         <v>45445</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26403,7 +26403,7 @@
         <v>46213</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26476,7 +26476,7 @@
         <v>45993</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26549,7 +26549,7 @@
         <v>46213</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26622,7 +26622,7 @@
         <v>44950</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26695,7 +26695,7 @@
         <v>45327</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26773,7 +26773,7 @@
         <v>45432</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>46189</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26919,7 +26919,7 @@
         <v>45434</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>46000</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45408</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27138,7 +27138,7 @@
         <v>45349</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27211,7 +27211,7 @@
         <v>46209</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27289,7 +27289,7 @@
         <v>46045</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27367,7 +27367,7 @@
         <v>45274</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27440,7 +27440,7 @@
         <v>45670</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         <v>45562</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27586,7 +27586,7 @@
         <v>45419</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45519</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>45574</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>45089</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27878,7 +27878,7 @@
         <v>45602</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27951,7 +27951,7 @@
         <v>45615</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28024,7 +28024,7 @@
         <v>45782</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>46191</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45784</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45553</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28316,7 +28316,7 @@
         <v>45432</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28394,7 +28394,7 @@
         <v>46120</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28467,7 +28467,7 @@
         <v>45784</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45594</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>46007</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28691,7 +28691,7 @@
         <v>45252</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28764,7 +28764,7 @@
         <v>45590</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28837,7 +28837,7 @@
         <v>46279</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>45546</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28983,7 +28983,7 @@
         <v>45679</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45709</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29129,7 +29129,7 @@
         <v>45176</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29202,7 +29202,7 @@
         <v>45670</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45679</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>44783</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29421,7 +29421,7 @@
         <v>45726</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29494,7 +29494,7 @@
         <v>45568</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29567,7 +29567,7 @@
         <v>45562</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>45511</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29713,7 +29713,7 @@
         <v>45636</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29791,7 +29791,7 @@
         <v>45597</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45524</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29937,7 +29937,7 @@
         <v>45576</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>45565</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30083,7 +30083,7 @@
         <v>44783</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30156,7 +30156,7 @@
         <v>45230</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30229,7 +30229,7 @@
         <v>45266</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45789</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30380,7 +30380,7 @@
         <v>45712</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30453,7 +30453,7 @@
         <v>45345</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45637</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30604,7 +30604,7 @@
         <v>45345</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30677,7 +30677,7 @@
         <v>46031</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>46036</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45793</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30901,7 +30901,7 @@
         <v>46038</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30974,7 +30974,7 @@
         <v>46038</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31047,7 +31047,7 @@
         <v>46038</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31120,7 +31120,7 @@
         <v>45154</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45436</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45152</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45793</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>46202</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>46244</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>46048</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>45692</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>46287</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45478</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45533</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
         <v>45477</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31996,7 +31996,7 @@
         <v>45637</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32074,7 +32074,7 @@
         <v>45684</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32147,7 +32147,7 @@
         <v>45727</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32220,7 +32220,7 @@
         <v>44545</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32293,7 +32293,7 @@
         <v>46147</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45978</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32439,7 +32439,7 @@
         <v>46293</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45811</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32585,7 +32585,7 @@
         <v>46063</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>46063</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>46293</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>46293</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32877,7 +32877,7 @@
         <v>46294</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32950,7 +32950,7 @@
         <v>45820</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33023,7 +33023,7 @@
         <v>45793</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33096,7 +33096,7 @@
         <v>45310</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>46251</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>46078</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45827</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33393,7 +33393,7 @@
         <v>46083</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33466,7 +33466,7 @@
         <v>45831</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33539,7 +33539,7 @@
         <v>46083</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33612,7 +33612,7 @@
         <v>46083</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33685,7 +33685,7 @@
         <v>46083</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>44609</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45831</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45832</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33982,7 +33982,7 @@
         <v>45475</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34055,7 +34055,7 @@
         <v>46086</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34128,7 +34128,7 @@
         <v>45838</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34201,7 +34201,7 @@
         <v>45434</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>46090</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34347,7 +34347,7 @@
         <v>45839</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>45841</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45841</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>46098</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45677</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34717,7 +34717,7 @@
         <v>46101</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>46300</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34863,7 +34863,7 @@
         <v>46120</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>46101</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45436</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>46104</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>46293</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>45005</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>46106</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45751</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>46301</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35525,7 +35525,7 @@
         <v>46044</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>46108</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35676,7 +35676,7 @@
         <v>46108</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35749,7 +35749,7 @@
         <v>46108</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>44936</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35895,7 +35895,7 @@
         <v>44936</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35968,7 +35968,7 @@
         <v>46303</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36041,7 +36041,7 @@
         <v>45684</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36114,7 +36114,7 @@
         <v>46031</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45090</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36260,7 +36260,7 @@
         <v>45246</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36333,7 +36333,7 @@
         <v>45644</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36406,7 +36406,7 @@
         <v>46303</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>46119</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>46120</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36625,7 +36625,7 @@
         <v>45113</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>46303</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36771,7 +36771,7 @@
         <v>46260</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36844,7 +36844,7 @@
         <v>46260</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45644</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36990,7 +36990,7 @@
         <v>45873</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37063,7 +37063,7 @@
         <v>45873</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37136,7 +37136,7 @@
         <v>45874</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>46260</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45873</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>45950</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>46120</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37501,7 +37501,7 @@
         <v>46132</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37574,7 +37574,7 @@
         <v>45394</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37647,7 +37647,7 @@
         <v>45877</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37720,7 +37720,7 @@
         <v>46307</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>45881</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>45881</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>46105</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>46132</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>44911</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38158,7 +38158,7 @@
         <v>45329</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>44895</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38309,7 +38309,7 @@
         <v>45540</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38382,7 +38382,7 @@
         <v>46134</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38455,7 +38455,7 @@
         <v>46262</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38528,7 +38528,7 @@
         <v>45362</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>46262</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>45782</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45897</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>46000</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>46148</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>45992</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45553</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>44907</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>45539</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45803</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>46308</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>45897</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45924</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>44599</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45596</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45755</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39774,7 +39774,7 @@
         <v>46308</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39847,7 +39847,7 @@
         <v>46010</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45742</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39993,7 +39993,7 @@
         <v>45908</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>45884</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40139,7 +40139,7 @@
         <v>45474</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40212,7 +40212,7 @@
         <v>45933</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40285,7 +40285,7 @@
         <v>45981</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>46136</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>45834</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>44930</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40577,7 +40577,7 @@
         <v>45841</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40650,7 +40650,7 @@
         <v>46003</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>46266</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40796,7 +40796,7 @@
         <v>45711</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>46010</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40942,7 +40942,7 @@
         <v>44995</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45926</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>45155</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45890</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41234,7 +41234,7 @@
         <v>46310</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41307,7 +41307,7 @@
         <v>45299</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41380,7 +41380,7 @@
         <v>46195</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41453,7 +41453,7 @@
         <v>46195</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41526,7 +41526,7 @@
         <v>46195</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41599,7 +41599,7 @@
         <v>45902</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>46314</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41745,7 +41745,7 @@
         <v>45903</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41823,7 +41823,7 @@
         <v>44928</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41896,7 +41896,7 @@
         <v>45063</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41969,7 +41969,7 @@
         <v>45007</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>44971</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42115,7 +42115,7 @@
         <v>45873</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45992</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42261,7 +42261,7 @@
         <v>45012</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42334,7 +42334,7 @@
         <v>45014</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42407,7 +42407,7 @@
         <v>44676</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>44950</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44965</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42631,7 +42631,7 @@
         <v>44945</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>45821</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42777,7 +42777,7 @@
         <v>45264</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45264</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>44939</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>46035</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>45029</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43142,7 +43142,7 @@
         <v>46304</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43215,7 +43215,7 @@
         <v>45755</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>45240</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>44936</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43434,7 +43434,7 @@
         <v>44936</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43507,7 +43507,7 @@
         <v>45278</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43580,7 +43580,7 @@
         <v>45568</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>44617</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43726,7 +43726,7 @@
         <v>46031</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43799,7 +43799,7 @@
         <v>45155</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43872,7 +43872,7 @@
         <v>45155</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -43945,7 +43945,7 @@
         <v>44620</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44023,7 +44023,7 @@
         <v>46274</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45614</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44174,7 +44174,7 @@
         <v>46317</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -44247,7 +44247,7 @@
         <v>45439</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -44320,7 +44320,7 @@
         <v>45904</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -44393,7 +44393,7 @@
         <v>45758</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -44471,7 +44471,7 @@
         <v>45637</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -44549,7 +44549,7 @@
         <v>44928</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -44622,7 +44622,7 @@
         <v>45071</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -44695,7 +44695,7 @@
         <v>45344</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -44768,7 +44768,7 @@
         <v>46148</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -44841,7 +44841,7 @@
         <v>44928</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -44914,7 +44914,7 @@
         <v>45162</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -44987,7 +44987,7 @@
         <v>44963</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -45060,7 +45060,7 @@
         <v>45091</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -45133,7 +45133,7 @@
         <v>46149</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -45206,7 +45206,7 @@
         <v>44685</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -45279,7 +45279,7 @@
         <v>44685</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -45352,7 +45352,7 @@
         <v>44993</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -45425,7 +45425,7 @@
         <v>46154</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -45498,7 +45498,7 @@
         <v>45182</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45077</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -45644,7 +45644,7 @@
         <v>44673</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45614</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>45107</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>44620</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -45936,7 +45936,7 @@
         <v>46043</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -46014,7 +46014,7 @@
         <v>45902</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -46087,7 +46087,7 @@
         <v>45700</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -46160,7 +46160,7 @@
         <v>45034</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>46160</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -46306,7 +46306,7 @@
         <v>45579</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -46379,7 +46379,7 @@
         <v>45574</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -46452,7 +46452,7 @@
         <v>45574</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -46525,7 +46525,7 @@
         <v>45580</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>44984</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>45323</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -46744,7 +46744,7 @@
         <v>45307</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -46822,7 +46822,7 @@
         <v>45007</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -46895,7 +46895,7 @@
         <v>45608</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -46968,7 +46968,7 @@
         <v>45461</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44545</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -47114,7 +47114,7 @@
         <v>45119</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -47187,7 +47187,7 @@
         <v>45062</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>45009</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -47338,7 +47338,7 @@
         <v>44993</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45096</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>45610</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45674</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45093</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -47703,7 +47703,7 @@
         <v>44998</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>45547</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>44951</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -47922,7 +47922,7 @@
         <v>45552</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -47995,7 +47995,7 @@
         <v>45629</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>44748</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45701</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -48214,7 +48214,7 @@
         <v>45099</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -48287,7 +48287,7 @@
         <v>45469</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -48360,7 +48360,7 @@
         <v>45617</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>45121</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45722</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>44994</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>44495</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>44505</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>45062</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45078</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -48944,7 +48944,7 @@
         <v>45036</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -49017,7 +49017,7 @@
         <v>45035</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -49090,7 +49090,7 @@
         <v>44529</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -49163,7 +49163,7 @@
         <v>44930</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -49236,7 +49236,7 @@
         <v>45167</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -49309,7 +49309,7 @@
         <v>45188</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -49382,7 +49382,7 @@
         <v>45710</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>44937</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -49528,7 +49528,7 @@
         <v>45188</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45772</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -49674,7 +49674,7 @@
         <v>44991</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -49747,7 +49747,7 @@
         <v>44991</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -49820,7 +49820,7 @@
         <v>45247</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -49893,7 +49893,7 @@
         <v>45247</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -49966,7 +49966,7 @@
         <v>44988</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -50039,7 +50039,7 @@
         <v>45110</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -50112,7 +50112,7 @@
         <v>45244</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45063</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -50258,7 +50258,7 @@
         <v>45002</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -50331,7 +50331,7 @@
         <v>44930</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -50404,7 +50404,7 @@
         <v>44627</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>45264</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>45071</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45071</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45071</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>45260</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -50842,7 +50842,7 @@
         <v>44631</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -50915,7 +50915,7 @@
         <v>45112</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -50988,7 +50988,7 @@
         <v>45735</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -51061,7 +51061,7 @@
         <v>45735</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -51134,7 +51134,7 @@
         <v>45466</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>44790</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -51280,7 +51280,7 @@
         <v>45082</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -51353,7 +51353,7 @@
         <v>45082</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -51426,7 +51426,7 @@
         <v>45106</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -51499,7 +51499,7 @@
         <v>44916</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -51572,7 +51572,7 @@
         <v>45261</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -51645,7 +51645,7 @@
         <v>45709</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -51723,7 +51723,7 @@
         <v>45439</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -51796,7 +51796,7 @@
         <v>45229</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>45407</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -51942,7 +51942,7 @@
         <v>45075</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -52020,7 +52020,7 @@
         <v>45110</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -52093,7 +52093,7 @@
         <v>45107</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -52166,7 +52166,7 @@
         <v>45261</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -52239,7 +52239,7 @@
         <v>45103</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -52312,7 +52312,7 @@
         <v>45183</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -52385,7 +52385,7 @@
         <v>45034</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -52458,7 +52458,7 @@
         <v>45170</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -52531,7 +52531,7 @@
         <v>44895</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>45330</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -52677,7 +52677,7 @@
         <v>44960</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -52750,7 +52750,7 @@
         <v>44967</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -52828,7 +52828,7 @@
         <v>45370</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -52901,7 +52901,7 @@
         <v>45240</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -52974,7 +52974,7 @@
         <v>44953</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
         <v>44904</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -53120,7 +53120,7 @@
         <v>45325</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -53193,7 +53193,7 @@
         <v>45107</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -53266,7 +53266,7 @@
         <v>44949</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -53339,7 +53339,7 @@
         <v>44949</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -53412,7 +53412,7 @@
         <v>45002</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -53485,7 +53485,7 @@
         <v>45314</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -53558,7 +53558,7 @@
         <v>45392</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -53631,7 +53631,7 @@
         <v>45069</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>45275</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>44838</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -53850,7 +53850,7 @@
         <v>44545</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -53923,7 +53923,7 @@
         <v>44945</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -53996,7 +53996,7 @@
         <v>44524</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -54069,7 +54069,7 @@
         <v>44881</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
         <v>45424</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45019</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>44930</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45049</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>45097</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>45546</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -54580,7 +54580,7 @@
         <v>44964</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -54653,7 +54653,7 @@
         <v>45166</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -54726,7 +54726,7 @@
         <v>45546</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -54799,7 +54799,7 @@
         <v>44558</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -54872,7 +54872,7 @@
         <v>44540</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>45342</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -55018,7 +55018,7 @@
         <v>44575</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -55091,7 +55091,7 @@
         <v>44620</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45160</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>45274</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -55315,7 +55315,7 @@
         <v>45155</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>45155</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>45635</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>45540</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -55612,7 +55612,7 @@
         <v>45631</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -55685,7 +55685,7 @@
         <v>44795</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -55758,7 +55758,7 @@
         <v>45033</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -55831,7 +55831,7 @@
         <v>44570</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -55904,7 +55904,7 @@
         <v>44550</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -55977,7 +55977,7 @@
         <v>45107</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -56050,7 +56050,7 @@
         <v>44586</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -56123,7 +56123,7 @@
         <v>45631</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45152</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -56269,7 +56269,7 @@
         <v>45078</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -56342,7 +56342,7 @@
         <v>45727</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>44683</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>45618</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -56561,7 +56561,7 @@
         <v>45408</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -56634,7 +56634,7 @@
         <v>45175</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -56707,7 +56707,7 @@
         <v>45203</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -56780,7 +56780,7 @@
         <v>45082</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -56853,7 +56853,7 @@
         <v>45191</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -56926,7 +56926,7 @@
         <v>45106</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -56999,7 +56999,7 @@
         <v>45085</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -57072,7 +57072,7 @@
         <v>45107</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -57145,7 +57145,7 @@
         <v>44627</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -57218,7 +57218,7 @@
         <v>44624</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -57291,7 +57291,7 @@
         <v>45547</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -57364,7 +57364,7 @@
         <v>45176</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -57437,7 +57437,7 @@
         <v>45215</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -57510,7 +57510,7 @@
         <v>45609</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -57583,7 +57583,7 @@
         <v>44621</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -57656,7 +57656,7 @@
         <v>44614</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -57729,7 +57729,7 @@
         <v>45210</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -57802,7 +57802,7 @@
         <v>45215</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -57875,7 +57875,7 @@
         <v>45147</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -57948,7 +57948,7 @@
         <v>45138</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -58021,7 +58021,7 @@
         <v>45713</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -58094,7 +58094,7 @@
         <v>45090</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>44820</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -58240,7 +58240,7 @@
         <v>45635</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -58318,7 +58318,7 @@
         <v>45244</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -58391,7 +58391,7 @@
         <v>45574</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -58464,7 +58464,7 @@
         <v>45245</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -58537,7 +58537,7 @@
         <v>45211</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>44657</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -58683,7 +58683,7 @@
         <v>45684</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -58756,7 +58756,7 @@
         <v>45183</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -58829,7 +58829,7 @@
         <v>45183</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -58902,7 +58902,7 @@
         <v>45117</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -58975,7 +58975,7 @@
         <v>44749</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -59048,7 +59048,7 @@
         <v>44728</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -59121,7 +59121,7 @@
         <v>44728</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -59194,7 +59194,7 @@
         <v>45173</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -59267,7 +59267,7 @@
         <v>44655</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -59340,7 +59340,7 @@
         <v>45226</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -59413,7 +59413,7 @@
         <v>44700</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -59486,7 +59486,7 @@
         <v>45181</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -59559,7 +59559,7 @@
         <v>44705</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -59632,7 +59632,7 @@
         <v>44852</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -59705,7 +59705,7 @@
         <v>44753</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -59778,7 +59778,7 @@
         <v>45164</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -59851,7 +59851,7 @@
         <v>45164</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -59924,7 +59924,7 @@
         <v>45197</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -59997,7 +59997,7 @@
         <v>45264</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -60070,7 +60070,7 @@
         <v>45117</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -60143,7 +60143,7 @@
         <v>45236</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -60216,7 +60216,7 @@
         <v>45331</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -60289,7 +60289,7 @@
         <v>45303</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>45238</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -60435,7 +60435,7 @@
         <v>45109</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -60508,7 +60508,7 @@
         <v>45109</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>45302</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>45775</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -60727,7 +60727,7 @@
         <v>44804</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -60800,7 +60800,7 @@
         <v>45306</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -60873,7 +60873,7 @@
         <v>45314</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -60946,7 +60946,7 @@
         <v>44804</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -61019,7 +61019,7 @@
         <v>45176</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -61092,7 +61092,7 @@
         <v>45366</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -61165,7 +61165,7 @@
         <v>44756</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -61238,7 +61238,7 @@
         <v>44901</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -61311,7 +61311,7 @@
         <v>44901</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -61384,7 +61384,7 @@
         <v>45267</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -61457,7 +61457,7 @@
         <v>45399</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -61530,7 +61530,7 @@
         <v>44904</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -61603,7 +61603,7 @@
         <v>44867</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -61676,7 +61676,7 @@
         <v>44950</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -61749,7 +61749,7 @@
         <v>44831</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -61822,7 +61822,7 @@
         <v>44831</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -61895,7 +61895,7 @@
         <v>44522</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -61973,7 +61973,7 @@
         <v>45082</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -62046,7 +62046,7 @@
         <v>45327</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -62124,7 +62124,7 @@
         <v>45272</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -62197,7 +62197,7 @@
         <v>45264</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -62270,7 +62270,7 @@
         <v>45201</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -62343,7 +62343,7 @@
         <v>44748</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>44691</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -62489,7 +62489,7 @@
         <v>45303</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -62562,7 +62562,7 @@
         <v>45616</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -62635,7 +62635,7 @@
         <v>45429</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -62708,7 +62708,7 @@
         <v>45201</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -62781,7 +62781,7 @@
         <v>45574</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -62854,7 +62854,7 @@
         <v>45386</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -62927,7 +62927,7 @@
         <v>45412</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -63000,7 +63000,7 @@
         <v>44984</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45371</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -63146,7 +63146,7 @@
         <v>45406</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -63219,7 +63219,7 @@
         <v>44602</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -63292,7 +63292,7 @@
         <v>44657</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -63365,7 +63365,7 @@
         <v>44967</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -63438,7 +63438,7 @@
         <v>45572</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -63511,7 +63511,7 @@
         <v>44628</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -63584,7 +63584,7 @@
         <v>44967</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -63662,7 +63662,7 @@
         <v>44939</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -63735,7 +63735,7 @@
         <v>44988</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -63808,7 +63808,7 @@
         <v>44672</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -63881,7 +63881,7 @@
         <v>44722</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -63954,7 +63954,7 @@
         <v>45387</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -64027,7 +64027,7 @@
         <v>45387</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -64100,7 +64100,7 @@
         <v>45456</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -64173,7 +64173,7 @@
         <v>45602</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -64246,7 +64246,7 @@
         <v>44894</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -64319,7 +64319,7 @@
         <v>45443</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
@@ -64392,7 +64392,7 @@
         <v>44888</v>
       </c>
       <c r="E848" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
@@ -64465,7 +64465,7 @@
         <v>44900</v>
       </c>
       <c r="E849" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -64538,7 +64538,7 @@
         <v>45359</v>
       </c>
       <c r="E850" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
@@ -64611,7 +64611,7 @@
         <v>45359</v>
       </c>
       <c r="E851" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
@@ -64684,7 +64684,7 @@
         <v>45387</v>
       </c>
       <c r="E852" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -64757,7 +64757,7 @@
         <v>45128</v>
       </c>
       <c r="E853" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
@@ -64830,7 +64830,7 @@
         <v>45387</v>
       </c>
       <c r="E854" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
@@ -64903,7 +64903,7 @@
         <v>45362</v>
       </c>
       <c r="E855" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -64976,7 +64976,7 @@
         <v>45534</v>
       </c>
       <c r="E856" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -65049,7 +65049,7 @@
         <v>44901</v>
       </c>
       <c r="E857" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
@@ -65122,7 +65122,7 @@
         <v>44792</v>
       </c>
       <c r="E858" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
@@ -65200,7 +65200,7 @@
         <v>45362</v>
       </c>
       <c r="E859" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
@@ -65273,7 +65273,7 @@
         <v>45330</v>
       </c>
       <c r="E860" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -65346,7 +65346,7 @@
         <v>44883</v>
       </c>
       <c r="E861" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -65419,7 +65419,7 @@
         <v>45330</v>
       </c>
       <c r="E862" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -65492,7 +65492,7 @@
         <v>44928</v>
       </c>
       <c r="E863" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
@@ -65565,7 +65565,7 @@
         <v>45477</v>
       </c>
       <c r="E864" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
@@ -65638,7 +65638,7 @@
         <v>44971</v>
       </c>
       <c r="E865" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
@@ -65711,7 +65711,7 @@
         <v>44900</v>
       </c>
       <c r="E866" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -65784,7 +65784,7 @@
         <v>44971</v>
       </c>
       <c r="E867" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -65857,7 +65857,7 @@
         <v>45230</v>
       </c>
       <c r="E868" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
@@ -65930,7 +65930,7 @@
         <v>45730</v>
       </c>
       <c r="E869" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>45665</v>
       </c>
       <c r="E870" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -66076,7 +66076,7 @@
         <v>45727</v>
       </c>
       <c r="E871" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
@@ -66149,7 +66149,7 @@
         <v>45665</v>
       </c>
       <c r="E872" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -66222,7 +66222,7 @@
         <v>45807</v>
       </c>
       <c r="E873" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -66295,7 +66295,7 @@
         <v>45807</v>
       </c>
       <c r="E874" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -66368,7 +66368,7 @@
         <v>46038</v>
       </c>
       <c r="E875" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -66441,7 +66441,7 @@
         <v>46042</v>
       </c>
       <c r="E876" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -66514,7 +66514,7 @@
         <v>46042</v>
       </c>
       <c r="E877" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -66587,7 +66587,7 @@
         <v>46042</v>
       </c>
       <c r="E878" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -66660,7 +66660,7 @@
         <v>46042</v>
       </c>
       <c r="E879" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
@@ -66733,7 +66733,7 @@
         <v>46045</v>
       </c>
       <c r="E880" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
@@ -66806,7 +66806,7 @@
         <v>46132</v>
       </c>
       <c r="E881" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -66879,7 +66879,7 @@
         <v>46181</v>
       </c>
       <c r="E882" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F882" t="inlineStr">
         <is>
@@ -66952,7 +66952,7 @@
         <v>46188</v>
       </c>
       <c r="E883" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -67025,7 +67025,7 @@
         <v>46213</v>
       </c>
       <c r="E884" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
@@ -67098,7 +67098,7 @@
         <v>46314</v>
       </c>
       <c r="E885" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
